--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44454</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45638</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4173-2022</t>
+          <t>A 62152-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44588</v>
+        <v>46006</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -1228,10 +1228,10 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
@@ -1241,35 +1241,35 @@
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
         <v/>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
         <v>45944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>45944</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 62152-2025</t>
+          <t>A 35974-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46006</v>
+        <v>46266</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1561,266 +1561,266 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa
+Klippfrullania
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35974-2026 artfynd.xlsx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35974-2026 karta.png", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35974-2026 georefererad karta.tif", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35974-2026 FSC-klagomål.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35974-2026 FSC-klagomål mail.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35974-2026 tillsynsbegäran.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35974-2026 tillsynsbegäran mail.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 6043-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönpyrola
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 4173-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44588</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 6043-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45336</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönpyrola
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 35974-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Grov fjädermossa
-Klippfrullania
-Västlig hakmossa</t>
-        </is>
-      </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35974-2026 artfynd.xlsx", "A 35974-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35974-2026 karta.png", "A 35974-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35974-2026 georefererad karta.tif", "A 35974-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35974-2026 FSC-klagomål.docx", "A 35974-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35974-2026 FSC-klagomål mail.docx", "A 35974-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35974-2026 tillsynsbegäran.docx", "A 35974-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35974-2026 tillsynsbegäran mail.docx", "A 35974-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
         <v/>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
         <v>43962</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44571</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 9839-2026</t>
+          <t>A 9001-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46072</v>
+        <v>45713</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>2</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2098,268 +2098,268 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9839-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 48687-2025</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45936</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>6.4</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Blåsippa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9001-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45713</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="Z17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
         <v/>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
         <v>44974</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10764-2024</t>
+          <t>A 33772-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45369</v>
+        <v>45133</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8.300000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2546,42 +2546,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24514-2024</t>
+          <t>A 12238-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2595,10 +2599,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45458</v>
+        <v>45729</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2615,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>10.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2651,42 +2655,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15667-2024</t>
+          <t>A 50607-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2700,10 +2708,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45404</v>
+        <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2716,16 +2724,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>14.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2740,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2756,42 +2764,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 50607-2025</t>
+          <t>A 15667-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2805,10 +2813,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45945</v>
+        <v>45404</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2821,17 +2829,17 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>14.5</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -2845,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2861,35 +2869,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
     </row>
@@ -2913,7 +2921,7 @@
         <v>46100</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3018,7 +3026,7 @@
         <v>46100</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3114,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 53485-2023</t>
+          <t>A 64707-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3120,10 +3128,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45230</v>
+        <v>45281</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3135,8 +3143,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>11.9</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3148,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3160,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3172,50 +3185,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12238-2025</t>
+          <t>A 53485-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3229,10 +3242,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45729</v>
+        <v>45230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3245,7 +3258,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>10.6</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3285,46 +3298,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33772-2023</t>
+          <t>A 10764-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3338,10 +3351,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45133</v>
+        <v>45369</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3354,7 +3367,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3363,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3378,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3394,46 +3407,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6128-2026</t>
+          <t>A 24514-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3447,10 +3456,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46054</v>
+        <v>45458</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3463,7 +3472,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3499,46 +3508,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 64707-2023</t>
+          <t>A 6128-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3552,10 +3561,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45281</v>
+        <v>46054</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3567,13 +3576,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3585,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3597,10 +3601,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3613,39 +3617,35 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
-        <v/>
-      </c>
-      <c r="Z29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         <v>46264</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45733</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>45282</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44651</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>44865</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44533</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>44585</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>44740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>44865</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>44511</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>44499</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>44494</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>44525</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44457</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44606</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>44848</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>44865</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44764</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>44510</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5170,7 +5170,7 @@
         <v>44526</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>44851</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>44722</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 49242-2021</t>
+          <t>A 70164-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44453</v>
+        <v>44533</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5445,7 +5445,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 70164-2021</t>
+          <t>A 59917-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44533</v>
+        <v>44494</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5518,7 +5518,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59917-2021</t>
+          <t>A 4395-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44494</v>
+        <v>44588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4395-2022</t>
+          <t>A 53761-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44588</v>
+        <v>45615</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31388-2022</t>
+          <t>A 3178-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44774</v>
+        <v>45316</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5693,8 +5693,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>8.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5737,7 +5742,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30701-2022</t>
+          <t>A 61626-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5751,10 +5756,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44763</v>
+        <v>45646</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5767,7 +5772,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>7.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5810,7 +5815,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 55712-2022</t>
+          <t>A 12945-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5824,10 +5829,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44885</v>
+        <v>45385</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5840,7 +5845,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5883,7 +5888,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 46371-2022</t>
+          <t>A 52262-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5897,10 +5902,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44848</v>
+        <v>45217</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5912,13 +5917,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5961,7 +5961,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 54374-2022</t>
+          <t>A 16989-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44879</v>
+        <v>45033</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5990,8 +5990,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6034,7 +6039,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 29327-2024</t>
+          <t>A 55712-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6048,10 +6053,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45483</v>
+        <v>44885</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6064,7 +6069,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6107,7 +6112,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 44523-2023</t>
+          <t>A 10470-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6121,10 +6126,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45189</v>
+        <v>45366</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6137,7 +6142,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6180,7 +6185,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41991-2022</t>
+          <t>A 9695-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6194,10 +6199,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44830</v>
+        <v>45716</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6210,7 +6215,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6253,7 +6258,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 72625-2021</t>
+          <t>A 14079-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6267,10 +6272,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44546</v>
+        <v>45739</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6283,7 +6288,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6326,7 +6331,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8060-2026</t>
+          <t>A 49554-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6340,10 +6345,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46063</v>
+        <v>45596</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6356,7 +6361,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6399,7 +6404,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33118-2023</t>
+          <t>A 11897-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6413,10 +6418,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45126</v>
+        <v>45728</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6429,7 +6434,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6472,7 +6477,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33131-2023</t>
+          <t>A 29329-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6486,10 +6491,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45126</v>
+        <v>45483</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6502,7 +6507,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6545,7 +6550,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8051-2026</t>
+          <t>A 26233-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6559,10 +6564,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46063</v>
+        <v>45805</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6574,8 +6579,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6618,7 +6628,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8058-2026</t>
+          <t>A 26270-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6632,10 +6642,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46063</v>
+        <v>45805</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6648,7 +6658,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6691,7 +6701,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15695-2025</t>
+          <t>A 61252-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6705,10 +6715,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45748</v>
+        <v>45645</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6721,7 +6731,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6764,7 +6774,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45578-2024</t>
+          <t>A 15552-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6778,10 +6788,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45578</v>
+        <v>45018</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6794,7 +6804,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6837,7 +6847,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 33569-2025</t>
+          <t>A 13890-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6851,10 +6861,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45841</v>
+        <v>44649</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6867,7 +6877,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6910,7 +6920,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 33586-2025</t>
+          <t>A 39001-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6924,10 +6934,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45841</v>
+        <v>45548</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6940,7 +6950,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6983,7 +6993,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33580-2025</t>
+          <t>A 30701-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6997,10 +7007,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45841</v>
+        <v>44763</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7013,7 +7023,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7056,7 +7066,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26277-2025</t>
+          <t>A 880-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7070,10 +7080,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45805</v>
+        <v>46029</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7086,7 +7096,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7129,7 +7139,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33536-2025</t>
+          <t>A 1945-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7143,10 +7153,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45841</v>
+        <v>46035</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7159,7 +7169,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7202,7 +7212,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13325-2022</t>
+          <t>A 1608-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7216,10 +7226,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44645</v>
+        <v>46034</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7232,7 +7242,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7275,7 +7285,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 44319-2025</t>
+          <t>A 2322-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7289,10 +7299,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45916</v>
+        <v>46036</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7305,7 +7315,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7348,7 +7358,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16223-2025</t>
+          <t>A 2324-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7362,10 +7372,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45750</v>
+        <v>46036</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7378,7 +7388,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7421,7 +7431,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59383-2024</t>
+          <t>A 52950-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7435,10 +7445,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45638</v>
+        <v>44875</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7450,13 +7460,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7499,7 +7504,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 10457-2023</t>
+          <t>A 40369-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7513,10 +7518,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44987</v>
+        <v>45555</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7529,7 +7534,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7572,7 +7577,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 10850-2026</t>
+          <t>A 44319-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7586,10 +7591,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46078</v>
+        <v>45916</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7602,7 +7607,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7645,7 +7650,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17525-2025</t>
+          <t>A 6379-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7659,10 +7664,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45757</v>
+        <v>46055</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7675,7 +7680,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7718,7 +7723,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 53761-2024</t>
+          <t>A 44529-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7732,10 +7737,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45615</v>
+        <v>45189</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7748,7 +7753,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7791,7 +7796,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50626-2025</t>
+          <t>A 33569-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7805,10 +7810,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45945</v>
+        <v>45841</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7820,13 +7825,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>14</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7869,7 +7869,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16989-2023</t>
+          <t>A 33586-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7883,10 +7883,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45033</v>
+        <v>45841</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7898,13 +7898,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7947,7 +7942,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 50578-2025</t>
+          <t>A 33536-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7961,10 +7956,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45945</v>
+        <v>45841</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7977,7 +7972,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8020,7 +8015,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 50797-2025</t>
+          <t>A 33580-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8034,10 +8029,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45946</v>
+        <v>45841</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8050,7 +8045,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8093,7 +8088,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44529-2023</t>
+          <t>A 26277-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8107,10 +8102,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45189</v>
+        <v>45805</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8123,7 +8118,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8166,7 +8161,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 14440-2026</t>
+          <t>A 55733-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8180,10 +8175,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46100</v>
+        <v>45232</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8196,7 +8191,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8239,7 +8234,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14456-2026</t>
+          <t>A 7545-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8253,10 +8248,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46100</v>
+        <v>46059</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8269,7 +8264,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8312,7 +8307,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14465-2026</t>
+          <t>A 7466-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8326,10 +8321,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46100</v>
+        <v>46059</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8341,8 +8336,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.7</v>
+        <v>6.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8385,7 +8385,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 14462-2026</t>
+          <t>A 8051-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8399,10 +8399,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46100</v>
+        <v>46063</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8458,7 +8458,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33745-2023</t>
+          <t>A 8058-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8472,10 +8472,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45133</v>
+        <v>46063</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8531,7 +8531,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14437-2026</t>
+          <t>A 8060-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46100</v>
+        <v>46063</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8604,7 +8604,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 54126-2025</t>
+          <t>A 52852-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8618,10 +8618,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45964</v>
+        <v>45610</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8677,7 +8677,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29329-2024</t>
+          <t>A 16223-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8691,10 +8691,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45483</v>
+        <v>45750</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2982-2025</t>
+          <t>A 10850-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45678</v>
+        <v>46078</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8823,7 +8823,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 55830-2025</t>
+          <t>A 50626-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8837,10 +8837,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45972</v>
+        <v>45945</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8852,8 +8852,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8896,7 +8901,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20476-2023</t>
+          <t>A 25884-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8910,10 +8915,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45057</v>
+        <v>45085</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8926,7 +8931,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8969,7 +8974,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 19134-2025</t>
+          <t>A 50578-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8979,14 +8984,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45764</v>
+        <v>45945</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8999,7 +9004,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9042,7 +9047,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 50401-2021</t>
+          <t>A 17525-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9056,10 +9061,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44459</v>
+        <v>45757</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9072,7 +9077,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9115,7 +9120,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 11897-2025</t>
+          <t>A 50797-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9129,10 +9134,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45728</v>
+        <v>45946</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9145,7 +9150,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9188,7 +9193,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 22560-2023</t>
+          <t>A 50603-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9202,10 +9207,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45071</v>
+        <v>45600</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9218,7 +9223,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9261,7 +9266,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 58226-2025</t>
+          <t>A 20476-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9275,10 +9280,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45985</v>
+        <v>45057</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9291,7 +9296,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9334,7 +9339,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 50034-2022</t>
+          <t>A 50401-2021</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9348,10 +9353,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44865</v>
+        <v>44459</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9364,7 +9369,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9407,7 +9412,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14833-2026</t>
+          <t>A 14465-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9421,10 +9426,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46103</v>
+        <v>46100</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9437,7 +9442,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9480,7 +9485,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 57663-2025</t>
+          <t>A 14440-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9494,10 +9499,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45981</v>
+        <v>46100</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9510,7 +9515,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9553,7 +9558,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 12945-2024</t>
+          <t>A 14456-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9567,10 +9572,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45385</v>
+        <v>46100</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9583,7 +9588,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6.1</v>
+        <v>7.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9626,7 +9631,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 61898-2025</t>
+          <t>A 56024-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9640,10 +9645,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46003</v>
+        <v>45240</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9656,7 +9661,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9699,7 +9704,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 994-2024</t>
+          <t>A 14462-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9713,10 +9718,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45301</v>
+        <v>46100</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9729,7 +9734,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>6.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9772,7 +9777,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 3187-2024</t>
+          <t>A 50601-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9786,10 +9791,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45316</v>
+        <v>45600</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9801,13 +9806,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9850,7 +9850,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 31917-2025</t>
+          <t>A 14437-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9864,10 +9864,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45834</v>
+        <v>46100</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9923,7 +9923,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 39001-2024</t>
+          <t>A 54126-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45548</v>
+        <v>45964</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 880-2026</t>
+          <t>A 41991-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10010,10 +10010,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46029</v>
+        <v>44830</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10069,7 +10069,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 38983-2024</t>
+          <t>A 3187-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10083,10 +10083,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45548</v>
+        <v>45316</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10098,8 +10098,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10142,7 +10147,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29308-2025</t>
+          <t>A 14833-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10156,10 +10161,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45824</v>
+        <v>46103</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10172,7 +10177,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10215,7 +10220,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 1608-2026</t>
+          <t>A 55830-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10229,10 +10234,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46034</v>
+        <v>45972</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10245,7 +10250,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10288,7 +10293,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1945-2026</t>
+          <t>A 31917-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10302,10 +10307,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46035</v>
+        <v>45834</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10318,7 +10323,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10361,7 +10366,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 2322-2026</t>
+          <t>A 58226-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10375,10 +10380,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46036</v>
+        <v>45985</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10391,7 +10396,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10434,7 +10439,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 2324-2026</t>
+          <t>A 46371-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10448,10 +10453,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46036</v>
+        <v>44848</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10463,8 +10468,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10507,7 +10517,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 29300-2025</t>
+          <t>A 59383-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10521,10 +10531,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45824</v>
+        <v>45638</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10536,8 +10546,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10580,7 +10595,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 13109-2023</t>
+          <t>A 29308-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10594,10 +10609,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45002</v>
+        <v>45824</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10610,7 +10625,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10653,7 +10668,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 56130-2022</t>
+          <t>A 33745-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10663,14 +10678,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44886</v>
+        <v>45133</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10683,7 +10698,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10726,7 +10741,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 33747-2023</t>
+          <t>A 33559-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10740,10 +10755,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45133</v>
+        <v>45841</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10756,7 +10771,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10799,7 +10814,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 21333-2024</t>
+          <t>A 5326-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10813,10 +10828,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45440</v>
+        <v>45331</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10829,7 +10844,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10872,7 +10887,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 29195-2024</t>
+          <t>A 48688-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10886,10 +10901,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45482</v>
+        <v>45936</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10902,7 +10917,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10945,7 +10960,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 6379-2026</t>
+          <t>A 57663-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10959,10 +10974,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46055</v>
+        <v>45981</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10975,7 +10990,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11018,7 +11033,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33559-2025</t>
+          <t>A 61898-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11032,10 +11047,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45841</v>
+        <v>46003</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11048,7 +11063,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11091,7 +11106,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 56196-2025</t>
+          <t>A 2982-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11105,10 +11120,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45974</v>
+        <v>45678</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11121,7 +11136,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11164,7 +11179,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 56602-2023</t>
+          <t>A 60768-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11178,10 +11193,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45243</v>
+        <v>44907</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11194,7 +11209,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11237,7 +11252,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 7466-2026</t>
+          <t>A 29300-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11251,10 +11266,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46059</v>
+        <v>45824</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11266,13 +11281,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11315,7 +11325,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 7545-2026</t>
+          <t>A 20888-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11329,10 +11339,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46059</v>
+        <v>44701</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11345,7 +11355,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11388,7 +11398,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 7136-2022</t>
+          <t>A 37311-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11402,10 +11412,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44603</v>
+        <v>45876</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11418,7 +11428,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11461,7 +11471,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 48688-2025</t>
+          <t>A 56196-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11475,10 +11485,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45936</v>
+        <v>45974</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11491,7 +11501,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11534,7 +11544,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 37311-2025</t>
+          <t>A 21355-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11548,10 +11558,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45876</v>
+        <v>46142</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11564,7 +11574,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11607,7 +11617,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 50601-2024</t>
+          <t>A 45617-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11621,10 +11631,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45600</v>
+        <v>45579</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11637,7 +11647,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11680,7 +11690,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21355-2026</t>
+          <t>A 21755-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11694,10 +11704,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11710,7 +11720,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11753,7 +11763,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 67875-2021</t>
+          <t>A 21819-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11767,10 +11777,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44525</v>
+        <v>46150</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11783,7 +11793,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>15.5</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11826,7 +11836,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 16363-2024</t>
+          <t>A 21826-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11840,10 +11850,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45407</v>
+        <v>46150</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11856,7 +11866,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11899,7 +11909,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 21819-2026</t>
+          <t>A 21828-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11916,7 +11926,7 @@
         <v>46150</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11929,7 +11939,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11972,7 +11982,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 21833-2026</t>
+          <t>A 21839-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11989,7 +11999,7 @@
         <v>46150</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12002,7 +12012,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12045,7 +12055,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 21839-2026</t>
+          <t>A 21833-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12062,7 +12072,7 @@
         <v>46150</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12075,7 +12085,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12118,7 +12128,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 21755-2026</t>
+          <t>A 9983-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12132,10 +12142,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46149</v>
+        <v>44621</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12148,7 +12158,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12191,7 +12201,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 21826-2026</t>
+          <t>A 33131-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12205,10 +12215,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46150</v>
+        <v>45126</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12221,7 +12231,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12264,7 +12274,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 21828-2026</t>
+          <t>A 31388-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12278,10 +12288,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46150</v>
+        <v>44774</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12294,7 +12304,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12337,7 +12347,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 41072-2023</t>
+          <t>A 22321-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12351,10 +12361,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45170</v>
+        <v>46154</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12367,7 +12377,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>7.8</v>
+        <v>2.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12410,7 +12420,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 10470-2024</t>
+          <t>A 23027-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12424,10 +12434,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45366</v>
+        <v>46161</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12440,7 +12450,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12483,7 +12493,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 40369-2024</t>
+          <t>A 29195-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12497,10 +12507,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45555</v>
+        <v>45482</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12513,7 +12523,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>14.5</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12556,7 +12566,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 22321-2026</t>
+          <t>A 994-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12570,10 +12580,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46154</v>
+        <v>45301</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12586,7 +12596,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12629,7 +12639,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 52262-2023</t>
+          <t>A 28586-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12643,10 +12653,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45217</v>
+        <v>45819</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12659,7 +12669,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.7</v>
+        <v>7.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12702,7 +12712,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 23027-2026</t>
+          <t>A 26409-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12716,10 +12726,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46161</v>
+        <v>46182</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12732,7 +12742,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12775,7 +12785,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 38818-2024</t>
+          <t>A 28319-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12789,10 +12799,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45547</v>
+        <v>46196</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12805,7 +12815,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12848,7 +12858,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 8047-2024</t>
+          <t>A 22693-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12858,14 +12868,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45351</v>
+        <v>46156</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12878,7 +12888,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12921,7 +12931,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 28586-2025</t>
+          <t>A 29587-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12935,10 +12945,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45819</v>
+        <v>46204</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12951,7 +12961,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12994,7 +13004,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 25884-2023</t>
+          <t>A 10457-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13008,10 +13018,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45085</v>
+        <v>44987</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13024,7 +13034,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13067,7 +13077,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 54007-2024</t>
+          <t>A 50034-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13081,10 +13091,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45615</v>
+        <v>44865</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13097,7 +13107,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13140,7 +13150,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 20888-2022</t>
+          <t>A 35205-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13154,10 +13164,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44701</v>
+        <v>46260</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13170,7 +13180,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13213,7 +13223,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 54792-2023</t>
+          <t>A 57768-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13227,10 +13237,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45236</v>
+        <v>44892</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13243,7 +13253,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13286,7 +13296,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 26409-2026</t>
+          <t>A 35946-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13300,10 +13310,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46182</v>
+        <v>46266</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13316,7 +13326,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13359,7 +13369,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 11891-2025</t>
+          <t>A 16363-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13373,10 +13383,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45728</v>
+        <v>45407</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13389,7 +13399,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13432,7 +13442,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 3391-2024</t>
+          <t>A 15704-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13446,10 +13456,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45318</v>
+        <v>45748</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13461,13 +13471,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13510,7 +13515,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 21061-2022</t>
+          <t>A 72625-2021</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13524,10 +13529,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44704</v>
+        <v>44546</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13540,7 +13545,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13583,7 +13588,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 55733-2023</t>
+          <t>A 31837-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13597,10 +13602,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45232</v>
+        <v>46230</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13613,7 +13618,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13656,7 +13661,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 989-2024</t>
+          <t>A 37058-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13670,10 +13675,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45301</v>
+        <v>46273</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13686,7 +13691,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13729,7 +13734,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 29192-2024</t>
+          <t>A 19134-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13739,14 +13744,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45482</v>
+        <v>45764</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13759,7 +13764,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13802,7 +13807,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 57768-2022</t>
+          <t>A 33118-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13816,10 +13821,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44892</v>
+        <v>45126</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13832,7 +13837,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13875,7 +13880,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 28319-2026</t>
+          <t>A 38988-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13889,10 +13894,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46196</v>
+        <v>45548</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13905,7 +13910,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13948,7 +13953,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 22693-2026</t>
+          <t>A 60220-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13962,10 +13967,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46156</v>
+        <v>44903</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13978,7 +13983,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14021,7 +14026,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 15559-2023</t>
+          <t>A 11891-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14035,10 +14040,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45019</v>
+        <v>45728</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14051,7 +14056,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14094,7 +14099,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 9983-2022</t>
+          <t>A 37822-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14108,10 +14113,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44621</v>
+        <v>46279</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14124,7 +14129,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14167,7 +14172,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 20968-2023</t>
+          <t>A 15559-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14181,10 +14186,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45061</v>
+        <v>45019</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14197,7 +14202,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14240,7 +14245,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 29587-2026</t>
+          <t>A 54007-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14254,10 +14259,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46204</v>
+        <v>45615</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14270,7 +14275,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14313,7 +14318,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 60220-2022</t>
+          <t>A 33747-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14327,10 +14332,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44903</v>
+        <v>45133</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14343,7 +14348,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>8.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14386,7 +14391,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 45617-2024</t>
+          <t>A 44523-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14400,10 +14405,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45579</v>
+        <v>45189</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14416,7 +14421,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14459,7 +14464,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35205-2026</t>
+          <t>A 8047-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14469,14 +14474,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46260</v>
+        <v>45351</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14489,7 +14494,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14532,7 +14537,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 61252-2024</t>
+          <t>A 13109-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14546,10 +14551,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45645</v>
+        <v>45002</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14562,7 +14567,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14605,7 +14610,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 56024-2023</t>
+          <t>A 21333-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14619,10 +14624,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45240</v>
+        <v>45440</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14635,7 +14640,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14678,7 +14683,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 5326-2024</t>
+          <t>A 29192-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14692,10 +14697,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45331</v>
+        <v>45482</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14708,7 +14713,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14751,7 +14756,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 56677-2023</t>
+          <t>A 67875-2021</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14765,10 +14770,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45243</v>
+        <v>44525</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14781,7 +14786,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>15.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14824,7 +14829,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 35946-2026</t>
+          <t>A 38983-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14838,10 +14843,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46266</v>
+        <v>45548</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14854,7 +14859,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14897,7 +14902,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 60768-2022</t>
+          <t>A 29327-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14911,10 +14916,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44907</v>
+        <v>45483</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14927,7 +14932,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14970,7 +14975,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 52950-2022</t>
+          <t>A 56602-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14984,10 +14989,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44875</v>
+        <v>45243</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15000,7 +15005,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15043,7 +15048,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31837-2026</t>
+          <t>A 41072-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15057,10 +15062,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46230</v>
+        <v>45170</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15073,7 +15078,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15116,7 +15121,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 52852-2024</t>
+          <t>A 3391-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15130,10 +15135,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45610</v>
+        <v>45318</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15145,8 +15150,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15189,7 +15199,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 15704-2025</t>
+          <t>A 20968-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15203,10 +15213,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45748</v>
+        <v>45061</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15219,7 +15229,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15262,7 +15272,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 61626-2024</t>
+          <t>A 22560-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15276,10 +15286,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45646</v>
+        <v>45071</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15292,7 +15302,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>7.3</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15335,7 +15345,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 3178-2024</t>
+          <t>A 54792-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15349,10 +15359,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45316</v>
+        <v>45236</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15364,13 +15374,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15413,7 +15418,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 61249-2024</t>
+          <t>A 45578-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15427,10 +15432,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45645</v>
+        <v>45578</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15443,7 +15448,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15486,7 +15491,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 37058-2026</t>
+          <t>A 61249-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15500,10 +15505,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46273</v>
+        <v>45645</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15516,7 +15521,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15559,7 +15564,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 38988-2024</t>
+          <t>A 38818-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15573,10 +15578,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45548</v>
+        <v>45547</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15589,7 +15594,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15649,7 +15654,7 @@
         <v>45579</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15710,7 +15715,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 50603-2024</t>
+          <t>A 7136-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15724,10 +15729,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45600</v>
+        <v>44603</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15740,7 +15745,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15783,7 +15788,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 61250-2024</t>
+          <t>A 24991-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15797,10 +15802,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45645</v>
+        <v>45085</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15813,7 +15818,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15856,7 +15861,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 24991-2023</t>
+          <t>A 989-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15870,10 +15875,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45085</v>
+        <v>45301</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15886,7 +15891,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15929,7 +15934,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 46532-2024</t>
+          <t>A 61250-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15943,10 +15948,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45582</v>
+        <v>45645</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15959,7 +15964,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16002,7 +16007,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 49551-2024</t>
+          <t>A 13325-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16016,10 +16021,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45596</v>
+        <v>44645</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16032,7 +16037,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16075,7 +16080,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 9695-2025</t>
+          <t>A 56677-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16089,10 +16094,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45716</v>
+        <v>45243</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16105,7 +16110,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16148,7 +16153,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 14079-2025</t>
+          <t>A 56130-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16158,14 +16163,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45739</v>
+        <v>44886</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16178,7 +16183,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16221,7 +16226,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 11931-2025</t>
+          <t>A 21061-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16235,10 +16240,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45728</v>
+        <v>44704</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16251,7 +16256,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16294,7 +16299,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 14087-2025</t>
+          <t>A 54374-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16308,10 +16313,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45739</v>
+        <v>44879</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16324,7 +16329,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16367,7 +16372,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 49554-2024</t>
+          <t>A 15695-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16381,10 +16386,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45596</v>
+        <v>45748</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16397,7 +16402,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16440,7 +16445,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 26233-2025</t>
+          <t>A 49551-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16454,10 +16459,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45805</v>
+        <v>45596</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16469,13 +16474,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16518,7 +16518,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 26270-2025</t>
+          <t>A 46532-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16532,10 +16532,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45805</v>
+        <v>45582</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16591,7 +16591,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 13890-2022</t>
+          <t>A 11931-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16605,10 +16605,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44649</v>
+        <v>45728</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16664,7 +16664,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 15552-2023</t>
+          <t>A 14087-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16678,10 +16678,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45018</v>
+        <v>45739</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>45194</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>44788</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>46036</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE209"/>
+  <dimension ref="A1:AE208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 49356-2021</t>
+          <t>A 59406-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44454</v>
+        <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -963,20 +963,25 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>7.9</v>
+        <v>11.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -988,144 +993,21 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
         <v>4</v>
       </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>6</v>
-      </c>
       <c r="T5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="U5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Duvhök
-Vedflamlav
-Vedskivlav
-Blåmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 49356-2021 artfynd.xlsx", "A 49356-2021")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 49356-2021 karta.png", "A 49356-2021")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 49356-2021 georefererad karta.tif", "A 49356-2021")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 49356-2021 karta knärot.png", "A 49356-2021")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 49356-2021 FSC-klagomål.docx", "A 49356-2021")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 49356-2021 FSC-klagomål mail.docx", "A 49356-2021")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 49356-2021 tillsynsbegäran.docx", "A 49356-2021")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 49356-2021 tillsynsbegäran mail.docx", "A 49356-2021")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 49356-2021 prioriterade fågelarter.docx", "A 49356-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 59406-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45638</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" t="n">
-        <v>5</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Hasselsnok
 Sandödla
@@ -1133,39 +1015,150 @@
 Vanlig padda</t>
         </is>
       </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 59406-2024 artfynd.xlsx", "A 59406-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 59406-2024 karta.png", "A 59406-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 59406-2024 georefererad karta.tif", "A 59406-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 59406-2024 FSC-klagomål.docx", "A 59406-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 59406-2024 FSC-klagomål mail.docx", "A 59406-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 59406-2024 tillsynsbegäran.docx", "A 59406-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 59406-2024 tillsynsbegäran mail.docx", "A 59406-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 6043-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönpyrola
+Revlummer</t>
+        </is>
+      </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 59406-2024 artfynd.xlsx", "A 59406-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 59406-2024 karta.png", "A 59406-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 59406-2024 georefererad karta.tif", "A 59406-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 59406-2024 FSC-klagomål.docx", "A 59406-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 59406-2024 FSC-klagomål mail.docx", "A 59406-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 59406-2024 tillsynsbegäran.docx", "A 59406-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 59406-2024 tillsynsbegäran mail.docx", "A 59406-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 62152-2025</t>
+          <t>A 4173-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1179,10 +1172,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46006</v>
+        <v>44588</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1195,7 +1188,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -1228,10 +1221,10 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
@@ -1241,35 +1234,35 @@
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
         <v/>
       </c>
     </row>
@@ -1293,7 +1286,7 @@
         <v>45944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1404,7 +1397,7 @@
         <v>45944</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1498,7 +1491,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35974-2026</t>
+          <t>A 62152-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1512,10 +1505,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46266</v>
+        <v>46006</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1531,10 +1524,10 @@
         <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1561,179 +1554,179 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 35974-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grov fjädermossa
 Klippfrullania
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35974-2026 artfynd.xlsx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35974-2026 karta.png", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35974-2026 georefererad karta.tif", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35974-2026 FSC-klagomål.docx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35974-2026 FSC-klagomål mail.docx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35974-2026 tillsynsbegäran.docx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35974-2026 tillsynsbegäran mail.docx", "A 35974-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 6043-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45336</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönpyrola
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4173-2022</t>
+          <t>S 1028-2020</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44588</v>
+        <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1746,10 +1739,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.8</v>
+        <v>0.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -1758,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1770,10 +1763,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1782,163 +1775,158 @@
         <v>5</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S 1028-2020</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Åtgärd i nyckelbiotop</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>43962</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ryl
 Grönpyrola</t>
         </is>
       </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/S 1028-2020 artfynd.xlsx", "S 1028-2020")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/S 1028-2020 karta.png", "S 1028-2020")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/S 1028-2020 georefererad karta.tif", "S 1028-2020")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/S 1028-2020 karta knärot.png", "S 1028-2020")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/S 1028-2020 FSC-klagomål.docx", "S 1028-2020")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/S 1028-2020 FSC-klagomål mail.docx", "S 1028-2020")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/S 1028-2020 tillsynsbegäran.docx", "S 1028-2020")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/S 1028-2020 tillsynsbegäran mail.docx", "S 1028-2020")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 1013-2022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44571</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Skogssvingel</t>
+        </is>
+      </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/S 1028-2020 artfynd.xlsx", "S 1028-2020")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 1013-2022 artfynd.xlsx", "A 1013-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/S 1028-2020 karta.png", "S 1028-2020")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 1013-2022 karta.png", "A 1013-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/S 1028-2020 georefererad karta.tif", "S 1028-2020")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/S 1028-2020 karta knärot.png", "S 1028-2020")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 1013-2022 georefererad karta.tif", "A 1013-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/S 1028-2020 FSC-klagomål.docx", "S 1028-2020")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 1013-2022 FSC-klagomål.docx", "A 1013-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/S 1028-2020 FSC-klagomål mail.docx", "S 1028-2020")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 1013-2022 FSC-klagomål mail.docx", "A 1013-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/S 1028-2020 tillsynsbegäran.docx", "S 1028-2020")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 1013-2022 tillsynsbegäran.docx", "A 1013-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/S 1028-2020 tillsynsbegäran mail.docx", "S 1028-2020")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 1013-2022 tillsynsbegäran mail.docx", "A 1013-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1013-2022</t>
+          <t>A 9839-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1952,10 +1940,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44571</v>
+        <v>46072</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1968,16 +1956,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1992,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2004,47 +1992,47 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra
-Skogssvingel</t>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 1013-2022 artfynd.xlsx", "A 1013-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 1013-2022 karta.png", "A 1013-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 1013-2022 georefererad karta.tif", "A 1013-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 1013-2022 FSC-klagomål.docx", "A 1013-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 1013-2022 FSC-klagomål mail.docx", "A 1013-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 1013-2022 tillsynsbegäran.docx", "A 1013-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 1013-2022 tillsynsbegäran mail.docx", "A 1013-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 9001-2025</t>
+          <t>A 48687-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2046,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45713</v>
+        <v>45936</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,19 +2062,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2101,166 +2089,166 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9001-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45713</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
         <v>4</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="Z15">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9839-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 48687-2025</t>
+          <t>A 8291-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2274,10 +2262,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45936</v>
+        <v>44974</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2290,16 +2278,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.4</v>
+        <v>17.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2314,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2326,47 +2314,51 @@
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Backstarr
-Blåsippa</t>
+          <t>Spillkråka
+Revlummer</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8291-2023</t>
+          <t>A 15667-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2380,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44974</v>
+        <v>45404</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2396,16 +2388,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>17.3</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2420,63 +2412,58 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka
-Revlummer</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33772-2023</t>
+          <t>A 10764-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2490,10 +2477,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45133</v>
+        <v>45369</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2506,7 +2493,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2515,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2530,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2546,46 +2533,42 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12238-2025</t>
+          <t>A 24514-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2599,10 +2582,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45729</v>
+        <v>45458</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2615,7 +2598,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>10.6</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2655,46 +2638,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 50607-2025</t>
+          <t>A 64707-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2708,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45945</v>
+        <v>45281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2723,8 +2702,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>14.5</v>
+        <v>11.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2736,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2748,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2760,46 +2744,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15667-2024</t>
+          <t>A 14442-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2813,10 +2801,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45404</v>
+        <v>46100</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2829,19 +2817,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2856,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2865,46 +2853,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14442-2026</t>
+          <t>A 14455-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2921,7 +2909,7 @@
         <v>46100</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2934,7 +2922,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2946,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2958,10 +2946,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2974,42 +2962,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14455-2026</t>
+          <t>A 50607-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3023,10 +3011,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46100</v>
+        <v>45945</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3039,7 +3027,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3075,46 +3063,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 64707-2023</t>
+          <t>A 6128-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3128,10 +3116,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45281</v>
+        <v>46054</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3143,13 +3131,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3161,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3173,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3189,39 +3172,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
     </row>
@@ -3245,7 +3224,7 @@
         <v>45230</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3337,7 +3316,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 10764-2024</t>
+          <t>A 12238-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3351,10 +3330,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45369</v>
+        <v>45729</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3367,7 +3346,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>8.300000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3403,46 +3382,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 24514-2024</t>
+          <t>A 33772-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3456,10 +3439,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45458</v>
+        <v>45133</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3472,7 +3455,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3481,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3496,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3508,46 +3491,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 6128-2026</t>
+          <t>A 35813-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3561,10 +3548,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46054</v>
+        <v>46264</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3577,7 +3564,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>23.7</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3617,42 +3604,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35813-2026</t>
+          <t>A 12779-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3666,10 +3653,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46264</v>
+        <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3682,7 +3669,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>23.7</v>
+        <v>10.1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3722,59 +3709,63 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12779-2025 artfynd.xlsx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12779-2025 karta.png", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12779-2025 georefererad karta.tif", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12779-2025 FSC-klagomål.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12779-2025 FSC-klagomål mail.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12779-2025 tillsynsbegäran.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12779-2025 tillsynsbegäran mail.docx", "A 12779-2025")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12779-2025 prioriterade fågelarter.docx", "A 12779-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12779-2025</t>
+          <t>S 4586-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45733</v>
+        <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3786,8 +3777,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>10.1</v>
+        <v>11.9</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3799,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3811,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3827,63 +3823,63 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12779-2025 artfynd.xlsx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/S 4586-2023 artfynd.xlsx", "S 4586-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12779-2025 karta.png", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/S 4586-2023 karta.png", "S 4586-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12779-2025 georefererad karta.tif", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/S 4586-2023 georefererad karta.tif", "S 4586-2023")</f>
+        <v/>
+      </c>
+      <c r="Z31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/S 4586-2023 karta knärot.png", "S 4586-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12779-2025 FSC-klagomål.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/S 4586-2023 FSC-klagomål.docx", "S 4586-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12779-2025 FSC-klagomål mail.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/S 4586-2023 FSC-klagomål mail.docx", "S 4586-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12779-2025 tillsynsbegäran.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/S 4586-2023 tillsynsbegäran.docx", "S 4586-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12779-2025 tillsynsbegäran mail.docx", "A 12779-2025")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12779-2025 prioriterade fågelarter.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/S 4586-2023 tillsynsbegäran mail.docx", "S 4586-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S 4586-2023</t>
+          <t>A 14105-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45282</v>
+        <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3895,16 +3891,11 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>11.9</v>
+        <v>9.5</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3913,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3925,62 +3916,26 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/S 4586-2023 artfynd.xlsx", "S 4586-2023")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/S 4586-2023 karta.png", "S 4586-2023")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/S 4586-2023 georefererad karta.tif", "S 4586-2023")</f>
-        <v/>
-      </c>
-      <c r="Z32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/S 4586-2023 karta knärot.png", "S 4586-2023")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/S 4586-2023 FSC-klagomål.docx", "S 4586-2023")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/S 4586-2023 FSC-klagomål mail.docx", "S 4586-2023")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/S 4586-2023 tillsynsbegäran.docx", "S 4586-2023")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/S 4586-2023 tillsynsbegäran mail.docx", "S 4586-2023")</f>
-        <v/>
-      </c>
+      <c r="V32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 14105-2022</t>
+          <t>A 50227-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3994,10 +3949,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44651</v>
+        <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4010,7 +3965,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>9.5</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4053,7 +4008,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 50227-2022</t>
+          <t>A 70162-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4067,10 +4022,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44865</v>
+        <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4083,7 +4038,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4126,7 +4081,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 70162-2021</t>
+          <t>A 3372-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4140,10 +4095,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44533</v>
+        <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4156,7 +4111,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4199,7 +4154,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3372-2022</t>
+          <t>A 26926-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4213,10 +4168,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44585</v>
+        <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4229,7 +4184,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4272,7 +4227,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26926-2022</t>
+          <t>A 50007-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4286,10 +4241,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44740</v>
+        <v>44865</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4302,7 +4257,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4345,7 +4300,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50007-2022</t>
+          <t>A 64485-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4359,10 +4314,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44865</v>
+        <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4375,7 +4330,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.4</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4418,7 +4373,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64485-2021</t>
+          <t>A 61896-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4432,10 +4387,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44511</v>
+        <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4448,7 +4403,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4491,7 +4446,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 61896-2021</t>
+          <t>A 59872-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4505,10 +4460,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44499</v>
+        <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4521,7 +4476,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4564,7 +4519,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 59872-2021</t>
+          <t>A 68243-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4578,10 +4533,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44494</v>
+        <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4594,7 +4549,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4637,7 +4592,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 68243-2021</t>
+          <t>A 50202-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4651,10 +4606,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44525</v>
+        <v>44457</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4667,7 +4622,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4710,7 +4665,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50202-2021</t>
+          <t>A 7329-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4724,10 +4679,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44457</v>
+        <v>44606</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4740,7 +4695,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4783,7 +4738,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7329-2022</t>
+          <t>A 46436-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4797,10 +4752,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44606</v>
+        <v>44848</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4812,8 +4767,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4856,7 +4816,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 46436-2022</t>
+          <t>A 30731-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4870,10 +4830,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44848</v>
+        <v>44764</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4885,13 +4845,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4951,7 +4906,7 @@
         <v>44865</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5007,7 +4962,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30731-2022</t>
+          <t>A 64020-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5021,10 +4976,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44764</v>
+        <v>44510</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5037,7 +4992,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5080,7 +5035,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 64020-2021</t>
+          <t>A 68392-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5094,10 +5049,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44510</v>
+        <v>44526</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5110,7 +5065,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5153,7 +5108,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 68392-2021</t>
+          <t>A 46724-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5167,10 +5122,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44526</v>
+        <v>44851</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5183,7 +5138,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5226,7 +5181,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 46724-2022</t>
+          <t>A 23819-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5240,10 +5195,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44851</v>
+        <v>44722</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5256,7 +5211,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5299,7 +5254,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 23819-2022</t>
+          <t>A 55712-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5313,10 +5268,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44722</v>
+        <v>44885</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5329,7 +5284,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5389,7 +5344,7 @@
         <v>44533</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5462,7 +5417,7 @@
         <v>44494</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5535,7 +5490,7 @@
         <v>44588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5591,7 +5546,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 53761-2024</t>
+          <t>A 46371-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5605,10 +5560,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45615</v>
+        <v>44848</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5620,8 +5575,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5664,7 +5624,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3178-2024</t>
+          <t>A 54374-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5678,10 +5638,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45316</v>
+        <v>44879</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5693,13 +5653,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5742,7 +5697,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61626-2024</t>
+          <t>A 30701-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5756,10 +5711,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45646</v>
+        <v>44763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5772,7 +5727,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.3</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5815,7 +5770,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12945-2024</t>
+          <t>A 54792-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5829,10 +5784,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45385</v>
+        <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5845,7 +5800,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5888,7 +5843,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52262-2023</t>
+          <t>A 31388-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5902,10 +5857,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45217</v>
+        <v>44774</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5918,7 +5873,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5961,7 +5916,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16989-2023</t>
+          <t>A 17525-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5975,10 +5930,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45033</v>
+        <v>45757</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5988,11 +5943,6 @@
       <c r="G60" t="inlineStr">
         <is>
           <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -6039,7 +5989,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55712-2022</t>
+          <t>A 11891-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6053,10 +6003,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44885</v>
+        <v>45728</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6069,7 +6019,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6112,7 +6062,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10470-2024</t>
+          <t>A 3391-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6126,10 +6076,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45366</v>
+        <v>45318</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6141,8 +6091,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6185,7 +6140,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9695-2025</t>
+          <t>A 21061-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6199,10 +6154,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45716</v>
+        <v>44704</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6215,7 +6170,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6258,7 +6213,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14079-2025</t>
+          <t>A 55733-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6272,10 +6227,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45739</v>
+        <v>45232</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6288,7 +6243,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6331,7 +6286,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49554-2024</t>
+          <t>A 989-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6345,10 +6300,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45596</v>
+        <v>45301</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6361,7 +6316,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6404,7 +6359,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11897-2025</t>
+          <t>A 10850-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6418,10 +6373,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45728</v>
+        <v>46078</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6434,7 +6389,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6477,7 +6432,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29329-2024</t>
+          <t>A 72625-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6491,10 +6446,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45483</v>
+        <v>44546</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6507,7 +6462,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6550,7 +6505,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 26233-2025</t>
+          <t>A 29327-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6564,10 +6519,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45805</v>
+        <v>45483</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6579,13 +6534,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6628,7 +6578,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26270-2025</t>
+          <t>A 41991-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6642,10 +6592,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45805</v>
+        <v>44830</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6658,7 +6608,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6701,7 +6651,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61252-2024</t>
+          <t>A 44523-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6715,10 +6665,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45645</v>
+        <v>45189</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6731,7 +6681,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6774,7 +6724,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15552-2023</t>
+          <t>A 14440-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6788,10 +6738,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45018</v>
+        <v>46100</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6804,7 +6754,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6847,7 +6797,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13890-2022</t>
+          <t>A 14456-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6861,10 +6811,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44649</v>
+        <v>46100</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6877,7 +6827,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6920,7 +6870,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39001-2024</t>
+          <t>A 14465-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6934,10 +6884,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45548</v>
+        <v>46100</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6950,7 +6900,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6993,7 +6943,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30701-2022</t>
+          <t>A 14462-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7007,10 +6957,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44763</v>
+        <v>46100</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7023,7 +6973,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7066,7 +7016,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 880-2026</t>
+          <t>A 44319-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7080,10 +7030,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46029</v>
+        <v>45916</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7096,7 +7046,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7139,7 +7089,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 1945-2026</t>
+          <t>A 14437-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7153,10 +7103,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46035</v>
+        <v>46100</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7169,7 +7119,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7212,7 +7162,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1608-2026</t>
+          <t>A 33118-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7226,10 +7176,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46034</v>
+        <v>45126</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7242,7 +7192,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7285,7 +7235,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 2322-2026</t>
+          <t>A 33131-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7299,10 +7249,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46036</v>
+        <v>45126</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7315,7 +7265,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7358,7 +7308,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2324-2026</t>
+          <t>A 29192-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7372,10 +7322,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46036</v>
+        <v>45482</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7388,7 +7338,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7431,7 +7381,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52950-2022</t>
+          <t>A 57768-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7445,10 +7395,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44875</v>
+        <v>44892</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7461,7 +7411,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7504,7 +7454,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 40369-2024</t>
+          <t>A 14833-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7518,10 +7468,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45555</v>
+        <v>46103</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7534,7 +7484,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>14.5</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7577,7 +7527,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44319-2025</t>
+          <t>A 15695-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7591,10 +7541,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45916</v>
+        <v>45748</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7607,7 +7557,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7650,7 +7600,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 6379-2026</t>
+          <t>A 50626-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7664,10 +7614,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46055</v>
+        <v>45945</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7679,8 +7629,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7723,7 +7678,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44529-2023</t>
+          <t>A 50578-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7737,10 +7692,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45189</v>
+        <v>45945</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7753,7 +7708,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7796,7 +7751,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33569-2025</t>
+          <t>A 50797-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7810,10 +7765,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45841</v>
+        <v>45946</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7826,7 +7781,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7869,7 +7824,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33586-2025</t>
+          <t>A 45578-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7883,10 +7838,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45841</v>
+        <v>45578</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7899,7 +7854,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7942,7 +7897,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33536-2025</t>
+          <t>A 31917-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7956,10 +7911,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45841</v>
+        <v>45834</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7972,7 +7927,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8015,7 +7970,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 33580-2025</t>
+          <t>A 13325-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8029,10 +7984,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45841</v>
+        <v>44645</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8045,7 +8000,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8088,7 +8043,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26277-2025</t>
+          <t>A 29308-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8102,10 +8057,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45805</v>
+        <v>45824</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8118,7 +8073,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8161,7 +8116,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 55733-2023</t>
+          <t>A 54126-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8175,10 +8130,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45232</v>
+        <v>45964</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8191,7 +8146,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8234,7 +8189,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7545-2026</t>
+          <t>A 29300-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8248,10 +8203,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46059</v>
+        <v>45824</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8264,7 +8219,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8307,7 +8262,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 7466-2026</t>
+          <t>A 59383-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8321,10 +8276,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46059</v>
+        <v>45638</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8342,7 +8297,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.4</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8385,7 +8340,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8051-2026</t>
+          <t>A 55830-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8399,10 +8354,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46063</v>
+        <v>45972</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8415,7 +8370,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8458,7 +8413,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 8058-2026</t>
+          <t>A 10457-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8472,10 +8427,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46063</v>
+        <v>44987</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8488,7 +8443,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8531,7 +8486,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8060-2026</t>
+          <t>A 33559-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8545,10 +8500,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46063</v>
+        <v>45841</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8561,7 +8516,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8604,7 +8559,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 52852-2024</t>
+          <t>A 56196-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8618,10 +8573,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45610</v>
+        <v>45974</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8634,7 +8589,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>6.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8677,7 +8632,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16223-2025</t>
+          <t>A 48688-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8691,10 +8646,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45750</v>
+        <v>45936</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8707,7 +8662,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8750,7 +8705,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10850-2026</t>
+          <t>A 37311-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8764,10 +8719,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46078</v>
+        <v>45876</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8780,7 +8735,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8823,7 +8778,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50626-2025</t>
+          <t>A 58226-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8837,10 +8792,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45945</v>
+        <v>45985</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8852,13 +8807,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8901,7 +8851,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25884-2023</t>
+          <t>A 53761-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8915,10 +8865,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45085</v>
+        <v>45615</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8931,7 +8881,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8974,7 +8924,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50578-2025</t>
+          <t>A 21355-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8988,10 +8938,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45945</v>
+        <v>46142</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9004,7 +8954,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9047,7 +8997,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17525-2025</t>
+          <t>A 16989-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9061,10 +9011,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45757</v>
+        <v>45033</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9074,6 +9024,11 @@
       <c r="G102" t="inlineStr">
         <is>
           <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -9120,7 +9075,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 50797-2025</t>
+          <t>A 44529-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9134,10 +9089,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45946</v>
+        <v>45189</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9150,7 +9105,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9193,7 +9148,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 50603-2024</t>
+          <t>A 21819-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9207,10 +9162,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45600</v>
+        <v>46150</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9223,7 +9178,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9266,7 +9221,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 20476-2023</t>
+          <t>A 33745-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9280,10 +9235,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45057</v>
+        <v>45133</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9296,7 +9251,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9339,7 +9294,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 50401-2021</t>
+          <t>A 21833-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9353,10 +9308,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44459</v>
+        <v>46150</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9369,7 +9324,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9412,7 +9367,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14465-2026</t>
+          <t>A 57663-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9426,10 +9381,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46100</v>
+        <v>45981</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9442,7 +9397,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9485,7 +9440,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 14440-2026</t>
+          <t>A 21839-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9499,10 +9454,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46100</v>
+        <v>46150</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9515,7 +9470,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.2</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9558,7 +9513,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 14456-2026</t>
+          <t>A 15559-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9572,10 +9527,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46100</v>
+        <v>45019</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9588,7 +9543,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9631,7 +9586,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56024-2023</t>
+          <t>A 21755-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9645,10 +9600,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45240</v>
+        <v>46149</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9661,7 +9616,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9704,7 +9659,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 14462-2026</t>
+          <t>A 21826-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9718,10 +9673,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46100</v>
+        <v>46150</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9734,7 +9689,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>6.8</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9777,7 +9732,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 50601-2024</t>
+          <t>A 21828-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9791,10 +9746,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45600</v>
+        <v>46150</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9807,7 +9762,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9850,7 +9805,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 14437-2026</t>
+          <t>A 22321-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9864,10 +9819,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46100</v>
+        <v>46154</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9880,7 +9835,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9923,7 +9878,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 54126-2025</t>
+          <t>A 61898-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9937,10 +9892,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45964</v>
+        <v>46003</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9953,7 +9908,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9996,7 +9951,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 41991-2022</t>
+          <t>A 9983-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10010,10 +9965,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44830</v>
+        <v>44621</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10026,7 +9981,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10069,7 +10024,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3187-2024</t>
+          <t>A 29329-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10083,10 +10038,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45316</v>
+        <v>45483</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10098,13 +10053,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10147,7 +10097,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 14833-2026</t>
+          <t>A 2982-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10161,10 +10111,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46103</v>
+        <v>45678</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10177,7 +10127,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10220,7 +10170,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 55830-2025</t>
+          <t>A 20476-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10234,10 +10184,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45972</v>
+        <v>45057</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10250,7 +10200,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10293,7 +10243,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 31917-2025</t>
+          <t>A 19134-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10303,14 +10253,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45834</v>
+        <v>45764</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10323,7 +10273,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10366,7 +10316,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 58226-2025</t>
+          <t>A 20968-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10380,10 +10330,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45985</v>
+        <v>45061</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10396,7 +10346,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10439,7 +10389,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 46371-2022</t>
+          <t>A 50401-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10453,10 +10403,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44848</v>
+        <v>44459</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10468,13 +10418,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10517,7 +10462,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 59383-2024</t>
+          <t>A 23027-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10531,10 +10476,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45638</v>
+        <v>46161</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10546,13 +10491,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10595,7 +10535,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 29308-2025</t>
+          <t>A 11897-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10609,10 +10549,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45824</v>
+        <v>45728</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10625,7 +10565,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10668,7 +10608,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 33745-2023</t>
+          <t>A 880-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10682,10 +10622,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45133</v>
+        <v>46029</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10698,7 +10638,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10741,7 +10681,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 33559-2025</t>
+          <t>A 22560-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10755,10 +10695,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45841</v>
+        <v>45071</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10771,7 +10711,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10814,7 +10754,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 5326-2024</t>
+          <t>A 1608-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10828,10 +10768,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45331</v>
+        <v>46034</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10844,7 +10784,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10887,7 +10827,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 48688-2025</t>
+          <t>A 28586-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10901,10 +10841,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45936</v>
+        <v>45819</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10917,7 +10857,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10960,7 +10900,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 57663-2025</t>
+          <t>A 1945-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10974,10 +10914,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45981</v>
+        <v>46035</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10990,7 +10930,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11033,7 +10973,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61898-2025</t>
+          <t>A 2322-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11047,10 +10987,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46003</v>
+        <v>46036</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11063,7 +11003,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>5.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11106,7 +11046,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 2982-2025</t>
+          <t>A 2324-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11120,10 +11060,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45678</v>
+        <v>46036</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11136,7 +11076,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11179,7 +11119,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 60768-2022</t>
+          <t>A 50034-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11193,10 +11133,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44907</v>
+        <v>44865</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11209,7 +11149,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11252,7 +11192,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 29300-2025</t>
+          <t>A 12945-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11266,10 +11206,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45824</v>
+        <v>45385</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11282,7 +11222,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11325,7 +11265,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 20888-2022</t>
+          <t>A 994-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11339,10 +11279,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44701</v>
+        <v>45301</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11355,7 +11295,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11398,7 +11338,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 37311-2025</t>
+          <t>A 6379-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11412,10 +11352,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45876</v>
+        <v>46055</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11428,7 +11368,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11471,7 +11411,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 56196-2025</t>
+          <t>A 26409-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11485,10 +11425,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45974</v>
+        <v>46182</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11501,7 +11441,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11544,7 +11484,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 21355-2026</t>
+          <t>A 3187-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11558,10 +11498,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46142</v>
+        <v>45316</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11573,8 +11513,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11617,7 +11562,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 45617-2024</t>
+          <t>A 7466-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11631,10 +11576,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45579</v>
+        <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11646,8 +11591,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11690,7 +11640,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21755-2026</t>
+          <t>A 7545-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11704,10 +11654,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46149</v>
+        <v>46059</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11720,7 +11670,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11763,7 +11713,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 21819-2026</t>
+          <t>A 8060-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11777,10 +11727,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46150</v>
+        <v>46063</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11793,7 +11743,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11836,7 +11786,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 21826-2026</t>
+          <t>A 8051-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11850,10 +11800,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46150</v>
+        <v>46063</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11866,7 +11816,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11909,7 +11859,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 21828-2026</t>
+          <t>A 8058-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11923,10 +11873,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46150</v>
+        <v>46063</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11939,7 +11889,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11982,7 +11932,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 21839-2026</t>
+          <t>A 39001-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11996,10 +11946,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46150</v>
+        <v>45548</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12012,7 +11962,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12055,7 +12005,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 21833-2026</t>
+          <t>A 38983-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12069,10 +12019,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46150</v>
+        <v>45548</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12085,7 +12035,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12128,7 +12078,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 9983-2022</t>
+          <t>A 13109-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12142,10 +12092,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44621</v>
+        <v>45002</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12158,7 +12108,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12201,7 +12151,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33131-2023</t>
+          <t>A 56130-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12211,14 +12161,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45126</v>
+        <v>44886</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12231,7 +12181,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12274,7 +12224,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31388-2022</t>
+          <t>A 33747-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12288,10 +12238,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44774</v>
+        <v>45133</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12304,7 +12254,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12347,7 +12297,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 22321-2026</t>
+          <t>A 60220-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12361,10 +12311,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46154</v>
+        <v>44903</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12377,7 +12327,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12420,7 +12370,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 23027-2026</t>
+          <t>A 21333-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12434,10 +12384,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46161</v>
+        <v>45440</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12450,7 +12400,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12510,7 +12460,7 @@
         <v>45482</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12566,7 +12516,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 994-2024</t>
+          <t>A 45617-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12580,10 +12530,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45301</v>
+        <v>45579</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12596,7 +12546,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12639,7 +12589,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 28586-2025</t>
+          <t>A 28319-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12653,10 +12603,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45819</v>
+        <v>46196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12669,7 +12619,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>7.1</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12712,7 +12662,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26409-2026</t>
+          <t>A 22693-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12726,10 +12676,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46182</v>
+        <v>46156</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12742,7 +12692,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12785,7 +12735,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 28319-2026</t>
+          <t>A 56602-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12799,10 +12749,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46196</v>
+        <v>45243</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12815,7 +12765,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12858,7 +12808,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22693-2026</t>
+          <t>A 7136-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12872,10 +12822,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46156</v>
+        <v>44603</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12888,7 +12838,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12931,7 +12881,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 29587-2026</t>
+          <t>A 50601-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12945,10 +12895,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46204</v>
+        <v>45600</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12961,7 +12911,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13004,7 +12954,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 10457-2023</t>
+          <t>A 67875-2021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13018,10 +12968,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44987</v>
+        <v>44525</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13034,7 +12984,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.6</v>
+        <v>15.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13077,7 +13027,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 50034-2022</t>
+          <t>A 16363-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13091,10 +13041,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44865</v>
+        <v>45407</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13107,7 +13057,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13150,7 +13100,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 35205-2026</t>
+          <t>A 29587-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13164,10 +13114,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46260</v>
+        <v>46204</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13180,7 +13130,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13223,7 +13173,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 57768-2022</t>
+          <t>A 41072-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13237,10 +13187,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44892</v>
+        <v>45170</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13253,7 +13203,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>7.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13296,7 +13246,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35946-2026</t>
+          <t>A 10470-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13310,10 +13260,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46266</v>
+        <v>45366</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13326,7 +13276,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13369,7 +13319,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 16363-2024</t>
+          <t>A 61252-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13383,10 +13333,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45407</v>
+        <v>45645</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13399,7 +13349,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13442,7 +13392,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 15704-2025</t>
+          <t>A 40369-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13456,10 +13406,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45748</v>
+        <v>45555</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13472,7 +13422,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.7</v>
+        <v>14.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13515,7 +13465,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 72625-2021</t>
+          <t>A 56024-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13529,10 +13479,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44546</v>
+        <v>45240</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13545,7 +13495,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13588,7 +13538,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 31837-2026</t>
+          <t>A 5326-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13602,10 +13552,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46230</v>
+        <v>45331</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13618,7 +13568,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13661,7 +13611,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 37058-2026</t>
+          <t>A 56677-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13675,10 +13625,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46273</v>
+        <v>45243</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13691,7 +13641,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13734,7 +13684,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 19134-2025</t>
+          <t>A 52262-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13744,14 +13694,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45764</v>
+        <v>45217</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13764,7 +13714,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13807,7 +13757,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 33118-2023</t>
+          <t>A 38818-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13821,10 +13771,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45126</v>
+        <v>45547</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13837,7 +13787,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13880,7 +13830,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 38988-2024</t>
+          <t>A 8047-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13890,14 +13840,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45548</v>
+        <v>45351</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13910,7 +13860,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13953,7 +13903,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 60220-2022</t>
+          <t>A 35205-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13967,10 +13917,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44903</v>
+        <v>46260</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13983,7 +13933,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>8.300000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14026,7 +13976,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 11891-2025</t>
+          <t>A 25884-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14040,10 +13990,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45728</v>
+        <v>45085</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14056,7 +14006,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14099,7 +14049,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37822-2026</t>
+          <t>A 54007-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14113,10 +14063,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46279</v>
+        <v>45615</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14129,7 +14079,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14172,7 +14122,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 15559-2023</t>
+          <t>A 20888-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14186,10 +14136,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45019</v>
+        <v>44701</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14202,7 +14152,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14245,7 +14195,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 54007-2024</t>
+          <t>A 35946-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14259,10 +14209,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45615</v>
+        <v>46266</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14275,7 +14225,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14318,7 +14268,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 33747-2023</t>
+          <t>A 60768-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14332,10 +14282,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45133</v>
+        <v>44907</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14348,7 +14298,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14391,7 +14341,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 44523-2023</t>
+          <t>A 52950-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14405,10 +14355,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45189</v>
+        <v>44875</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14421,7 +14371,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14464,7 +14414,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 8047-2024</t>
+          <t>A 52852-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14474,14 +14424,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45351</v>
+        <v>45610</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14494,7 +14444,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14537,7 +14487,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 13109-2023</t>
+          <t>A 15704-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14551,10 +14501,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45002</v>
+        <v>45748</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14567,7 +14517,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14610,7 +14560,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 21333-2024</t>
+          <t>A 61626-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14624,10 +14574,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45440</v>
+        <v>45646</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14640,7 +14590,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14683,7 +14633,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 29192-2024</t>
+          <t>A 3178-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14697,10 +14647,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45482</v>
+        <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14712,8 +14662,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14756,7 +14711,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 67875-2021</t>
+          <t>A 61249-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14770,10 +14725,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44525</v>
+        <v>45645</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14786,7 +14741,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>15.5</v>
+        <v>4.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14829,7 +14784,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 38983-2024</t>
+          <t>A 31837-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14843,10 +14798,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45548</v>
+        <v>46230</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14859,7 +14814,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14902,7 +14857,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 29327-2024</t>
+          <t>A 38988-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14916,10 +14871,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45483</v>
+        <v>45548</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14932,7 +14887,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14975,7 +14930,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 56602-2023</t>
+          <t>A 37058-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14989,10 +14944,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45243</v>
+        <v>46273</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15005,7 +14960,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15048,7 +15003,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 41072-2023</t>
+          <t>A 45632-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15062,10 +15017,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45170</v>
+        <v>45579</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15077,8 +15032,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15121,7 +15081,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 3391-2024</t>
+          <t>A 50603-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15135,10 +15095,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45318</v>
+        <v>45600</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15150,13 +15110,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15199,7 +15154,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 20968-2023</t>
+          <t>A 61250-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15213,10 +15168,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45061</v>
+        <v>45645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15229,7 +15184,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15272,7 +15227,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 22560-2023</t>
+          <t>A 24991-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15286,10 +15241,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45071</v>
+        <v>45085</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15302,7 +15257,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15345,7 +15300,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 54792-2023</t>
+          <t>A 37822-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15359,10 +15314,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45236</v>
+        <v>46279</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15375,7 +15330,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>5.9</v>
+        <v>3.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15418,7 +15373,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 45578-2024</t>
+          <t>A 46532-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15432,10 +15387,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45578</v>
+        <v>45582</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15448,7 +15403,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15491,7 +15446,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 61249-2024</t>
+          <t>A 49551-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15505,10 +15460,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45645</v>
+        <v>45596</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15521,7 +15476,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15564,7 +15519,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 38818-2024</t>
+          <t>A 9695-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15578,10 +15533,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45547</v>
+        <v>45716</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15594,7 +15549,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15637,7 +15592,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 45632-2024</t>
+          <t>A 14079-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15651,10 +15606,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45579</v>
+        <v>45739</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15666,13 +15621,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15715,7 +15665,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 7136-2022</t>
+          <t>A 11931-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15729,10 +15679,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44603</v>
+        <v>45728</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15788,7 +15738,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24991-2023</t>
+          <t>A 14087-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15802,10 +15752,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45085</v>
+        <v>45739</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15818,7 +15768,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15861,7 +15811,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 989-2024</t>
+          <t>A 49554-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15875,10 +15825,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45301</v>
+        <v>45596</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15891,7 +15841,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15934,7 +15884,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 61250-2024</t>
+          <t>A 26233-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15948,10 +15898,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45645</v>
+        <v>45805</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15963,8 +15913,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16007,7 +15962,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 13325-2022</t>
+          <t>A 26270-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16021,10 +15976,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44645</v>
+        <v>45805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16037,7 +15992,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16080,7 +16035,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 56677-2023</t>
+          <t>A 13890-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16094,10 +16049,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45243</v>
+        <v>44649</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16110,7 +16065,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16153,7 +16108,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 56130-2022</t>
+          <t>A 15552-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16163,14 +16118,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44886</v>
+        <v>45018</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16183,7 +16138,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16226,7 +16181,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 21061-2022</t>
+          <t>A 33569-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16240,10 +16195,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44704</v>
+        <v>45841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16256,7 +16211,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16299,7 +16254,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 54374-2022</t>
+          <t>A 33586-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16313,10 +16268,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44879</v>
+        <v>45841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16329,7 +16284,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16372,7 +16327,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 15695-2025</t>
+          <t>A 33580-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16386,10 +16341,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45748</v>
+        <v>45841</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16402,7 +16357,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16445,7 +16400,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 49551-2024</t>
+          <t>A 26277-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16459,10 +16414,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45596</v>
+        <v>45805</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16475,7 +16430,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16518,7 +16473,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 46532-2024</t>
+          <t>A 33536-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16532,10 +16487,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45582</v>
+        <v>45841</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16548,7 +16503,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4.3</v>
+        <v>6.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16591,7 +16546,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 11931-2025</t>
+          <t>A 16223-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16605,10 +16560,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45728</v>
+        <v>45750</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16621,7 +16576,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.9</v>
+        <v>7.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16664,24 +16619,24 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 14087-2025</t>
+          <t>S 3201-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45739</v>
+        <v>45194</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16694,7 +16649,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16737,7 +16692,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>S 3201-2023</t>
+          <t>S 4468-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16747,87 +16702,87 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>44788</v>
+      </c>
+      <c r="E207" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="n">
+        <v>0</v>
+      </c>
+      <c r="V207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>S 85-2026</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D207" s="1" t="n">
-        <v>45194</v>
-      </c>
-      <c r="E207" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I207" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" t="n">
-        <v>0</v>
-      </c>
-      <c r="L207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M207" t="n">
-        <v>0</v>
-      </c>
-      <c r="N207" t="n">
-        <v>0</v>
-      </c>
-      <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="n">
-        <v>0</v>
-      </c>
-      <c r="T207" t="n">
-        <v>0</v>
-      </c>
-      <c r="U207" t="n">
-        <v>0</v>
-      </c>
-      <c r="V207" s="2" t="inlineStr"/>
-    </row>
-    <row r="208" ht="15" customHeight="1">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>S 4468-2022</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
-      </c>
       <c r="D208" s="1" t="n">
-        <v>44788</v>
+        <v>46036</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16840,7 +16795,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16879,79 +16834,6 @@
         <v>0</v>
       </c>
       <c r="V208" s="2" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>S 85-2026</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D209" s="1" t="n">
-        <v>46036</v>
-      </c>
-      <c r="E209" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I209" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J209" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" t="n">
-        <v>0</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0</v>
-      </c>
-      <c r="M209" t="n">
-        <v>0</v>
-      </c>
-      <c r="N209" t="n">
-        <v>0</v>
-      </c>
-      <c r="O209" t="n">
-        <v>0</v>
-      </c>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="n">
-        <v>0</v>
-      </c>
-      <c r="T209" t="n">
-        <v>0</v>
-      </c>
-      <c r="U209" t="n">
-        <v>0</v>
-      </c>
-      <c r="V209" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6043-2024</t>
+          <t>A 50432-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45336</v>
+        <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1104,498 +1104,498 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50432-2025 artfynd.xlsx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50432-2025 karta.png", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50432-2025 georefererad karta.tif", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50432-2025 FSC-klagomål.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50432-2025 FSC-klagomål mail.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50432-2025 tillsynsbegäran.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50432-2025 tillsynsbegäran mail.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50432-2025 prioriterade fågelarter.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 50437-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50437-2025 artfynd.xlsx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50437-2025 karta.png", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50437-2025 georefererad karta.tif", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50437-2025 FSC-klagomål.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50437-2025 FSC-klagomål mail.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50437-2025 tillsynsbegäran.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50437-2025 tillsynsbegäran mail.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50437-2025 prioriterade fågelarter.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 62152-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 6043-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>7</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U9" t="n">
         <v>7</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Grönpyrola
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 4173-2022</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>44588</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>2.8</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T10" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U10" t="n">
         <v>5</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 50432-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50432-2025 artfynd.xlsx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50432-2025 karta.png", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50432-2025 georefererad karta.tif", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50432-2025 FSC-klagomål.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50432-2025 FSC-klagomål mail.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50432-2025 tillsynsbegäran.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50432-2025 tillsynsbegäran mail.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50432-2025 prioriterade fågelarter.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 50437-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>5</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50437-2025 artfynd.xlsx", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50437-2025 karta.png", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50437-2025 georefererad karta.tif", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50437-2025 FSC-klagomål.docx", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50437-2025 FSC-klagomål mail.docx", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50437-2025 tillsynsbegäran.docx", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50437-2025 tillsynsbegäran mail.docx", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50437-2025 prioriterade fågelarter.docx", "A 50437-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 62152-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46006</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
         <v/>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44571</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 9839-2026</t>
+          <t>A 9001-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46072</v>
+        <v>45713</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>2</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1980,385 +1980,385 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9839-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 8291-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 48687-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45936</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>6.4</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Blåsippa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9001-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45713</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 8291-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 15667-2024</t>
+          <t>A 33772-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45404</v>
+        <v>45133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2424,46 +2424,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10764-2024</t>
+          <t>A 50607-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45369</v>
+        <v>45945</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,7 +2497,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8.300000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2529,46 +2533,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24514-2024</t>
+          <t>A 15667-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2582,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45458</v>
+        <v>45404</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2598,17 +2602,17 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -2622,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2638,42 +2642,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 64707-2023</t>
+          <t>A 12238-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2691,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45281</v>
+        <v>45729</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2702,13 +2706,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>11.9</v>
+        <v>10.6</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2720,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2732,10 +2731,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2744,50 +2743,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14442-2026</t>
+          <t>A 64707-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2801,10 +2800,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46100</v>
+        <v>45281</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,8 +2815,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>11.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2857,42 +2861,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14455-2026</t>
+          <t>A 53485-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2906,10 +2914,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46100</v>
+        <v>45230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2922,7 +2930,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2958,46 +2966,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 50607-2025</t>
+          <t>A 10764-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3011,10 +3023,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45945</v>
+        <v>45369</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3027,7 +3039,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>14.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3063,46 +3075,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6128-2026</t>
+          <t>A 14442-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3116,10 +3128,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46054</v>
+        <v>46100</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3132,7 +3144,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3144,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3156,10 +3168,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3172,42 +3184,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53485-2023</t>
+          <t>A 14455-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3221,10 +3233,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45230</v>
+        <v>46100</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,7 +3249,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3273,50 +3285,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12238-2025</t>
+          <t>A 24514-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3330,10 +3338,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45729</v>
+        <v>45458</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3346,7 +3354,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10.6</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3386,46 +3394,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33772-2023</t>
+          <t>A 6128-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3439,10 +3443,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45133</v>
+        <v>46054</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3455,7 +3459,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3464,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3479,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3495,39 +3499,35 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
         <v>46264</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>44865</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44457</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44606</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44848</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30731-2022</t>
+          <t>A 50020-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44764</v>
+        <v>44865</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50020-2022</t>
+          <t>A 30731-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44865</v>
+        <v>44764</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
         <v>44510</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44526</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44851</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44722</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 55712-2022</t>
+          <t>A 70164-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44885</v>
+        <v>44533</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 70164-2021</t>
+          <t>A 59917-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44533</v>
+        <v>44494</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59917-2021</t>
+          <t>A 4395-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44494</v>
+        <v>44588</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4395-2022</t>
+          <t>A 53761-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44588</v>
+        <v>45615</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46371-2022</t>
+          <t>A 61626-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44848</v>
+        <v>45646</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5575,13 +5575,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>5.1</v>
+        <v>7.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54374-2022</t>
+          <t>A 52262-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44879</v>
+        <v>45217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5654,7 +5649,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5697,7 +5692,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30701-2022</t>
+          <t>A 3178-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5711,10 +5706,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44763</v>
+        <v>45316</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5726,8 +5721,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>8.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 54792-2023</t>
+          <t>A 12945-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45236</v>
+        <v>45385</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 31388-2022</t>
+          <t>A 16989-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44774</v>
+        <v>45033</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5872,8 +5872,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5916,7 +5921,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17525-2025</t>
+          <t>A 10470-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5930,10 +5935,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45757</v>
+        <v>45366</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5946,7 +5951,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5989,7 +5994,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11891-2025</t>
+          <t>A 55712-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6003,10 +6008,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45728</v>
+        <v>44885</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6019,7 +6024,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6062,7 +6067,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 3391-2024</t>
+          <t>A 11897-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6076,10 +6081,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45318</v>
+        <v>45728</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6091,13 +6096,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 21061-2022</t>
+          <t>A 29329-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44704</v>
+        <v>45483</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6213,7 +6213,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55733-2023</t>
+          <t>A 61252-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45232</v>
+        <v>45645</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6286,7 +6286,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 989-2024</t>
+          <t>A 30701-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6300,10 +6300,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45301</v>
+        <v>44763</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6359,7 +6359,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10850-2026</t>
+          <t>A 49554-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6373,10 +6373,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46078</v>
+        <v>45596</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 72625-2021</t>
+          <t>A 39001-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44546</v>
+        <v>45548</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6505,7 +6505,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29327-2024</t>
+          <t>A 880-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45483</v>
+        <v>46029</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41991-2022</t>
+          <t>A 26233-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6592,10 +6592,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44830</v>
+        <v>45805</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6607,8 +6607,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6651,7 +6656,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44523-2023</t>
+          <t>A 26270-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6665,10 +6670,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45189</v>
+        <v>45805</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6681,7 +6686,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6724,7 +6729,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14440-2026</t>
+          <t>A 52950-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6738,10 +6743,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46100</v>
+        <v>44875</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6754,7 +6759,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6797,7 +6802,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 14456-2026</t>
+          <t>A 15552-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6811,10 +6816,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46100</v>
+        <v>45018</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6827,7 +6832,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.2</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6870,7 +6875,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14465-2026</t>
+          <t>A 13890-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6884,10 +6889,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46100</v>
+        <v>44649</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6900,7 +6905,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6943,7 +6948,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14462-2026</t>
+          <t>A 40369-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6957,10 +6962,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46100</v>
+        <v>45555</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6973,7 +6978,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7016,7 +7021,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 44319-2025</t>
+          <t>A 1945-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7030,10 +7035,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45916</v>
+        <v>46035</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7046,7 +7051,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7089,7 +7094,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14437-2026</t>
+          <t>A 44529-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7103,10 +7108,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46100</v>
+        <v>45189</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7119,7 +7124,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7162,7 +7167,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33118-2023</t>
+          <t>A 55733-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7176,10 +7181,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45126</v>
+        <v>45232</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7192,7 +7197,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7235,7 +7240,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33131-2023</t>
+          <t>A 1608-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7249,10 +7254,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45126</v>
+        <v>46034</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7265,7 +7270,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7308,7 +7313,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 29192-2024</t>
+          <t>A 2322-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7322,10 +7327,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45482</v>
+        <v>46036</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7338,7 +7343,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7381,7 +7386,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 57768-2022</t>
+          <t>A 2324-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7395,10 +7400,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44892</v>
+        <v>46036</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7411,7 +7416,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7454,7 +7459,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14833-2026</t>
+          <t>A 52852-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7468,10 +7473,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46103</v>
+        <v>45610</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7484,7 +7489,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7527,7 +7532,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15695-2025</t>
+          <t>A 44319-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7541,10 +7546,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45748</v>
+        <v>45916</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7557,7 +7562,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7600,7 +7605,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 50626-2025</t>
+          <t>A 33569-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7614,10 +7619,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45945</v>
+        <v>45841</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7629,13 +7634,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>14</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7678,7 +7678,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50578-2025</t>
+          <t>A 33586-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45945</v>
+        <v>45841</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7751,7 +7751,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50797-2025</t>
+          <t>A 33536-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7765,10 +7765,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45946</v>
+        <v>45841</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7824,7 +7824,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 45578-2024</t>
+          <t>A 33580-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45578</v>
+        <v>45841</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7897,7 +7897,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 31917-2025</t>
+          <t>A 26277-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7911,10 +7911,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45834</v>
+        <v>45805</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7970,7 +7970,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13325-2022</t>
+          <t>A 25884-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44645</v>
+        <v>45085</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8043,7 +8043,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 29308-2025</t>
+          <t>A 50603-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45824</v>
+        <v>45600</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8116,7 +8116,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 54126-2025</t>
+          <t>A 16223-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45964</v>
+        <v>45750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8189,7 +8189,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 29300-2025</t>
+          <t>A 20476-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45824</v>
+        <v>45057</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8262,7 +8262,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59383-2024</t>
+          <t>A 50626-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45638</v>
+        <v>45945</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8293,11 +8293,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>14</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 55830-2025</t>
+          <t>A 50578-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45972</v>
+        <v>45945</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8413,7 +8413,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10457-2023</t>
+          <t>A 50797-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44987</v>
+        <v>45946</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33559-2025</t>
+          <t>A 17525-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45841</v>
+        <v>45757</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8559,7 +8559,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56196-2025</t>
+          <t>A 50401-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8573,10 +8573,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45974</v>
+        <v>44459</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48688-2025</t>
+          <t>A 56024-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45936</v>
+        <v>45240</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 37311-2025</t>
+          <t>A 6379-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45876</v>
+        <v>46055</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 58226-2025</t>
+          <t>A 50601-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8792,10 +8792,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45985</v>
+        <v>45600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8851,7 +8851,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 53761-2024</t>
+          <t>A 7545-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8865,10 +8865,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45615</v>
+        <v>46059</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 21355-2026</t>
+          <t>A 7466-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46142</v>
+        <v>46059</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8953,8 +8953,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8997,7 +9002,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 16989-2023</t>
+          <t>A 8051-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9011,10 +9016,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45033</v>
+        <v>46063</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9026,13 +9031,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9075,7 +9075,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44529-2023</t>
+          <t>A 8058-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9089,10 +9089,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45189</v>
+        <v>46063</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9148,7 +9148,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21819-2026</t>
+          <t>A 54126-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9162,10 +9162,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46150</v>
+        <v>45964</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9221,7 +9221,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 33745-2023</t>
+          <t>A 41991-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45133</v>
+        <v>44830</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9294,7 +9294,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21833-2026</t>
+          <t>A 8060-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46150</v>
+        <v>46063</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9367,7 +9367,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57663-2025</t>
+          <t>A 3187-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45981</v>
+        <v>45316</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9396,8 +9396,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9440,7 +9445,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 21839-2026</t>
+          <t>A 55830-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9454,10 +9459,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46150</v>
+        <v>45972</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9470,7 +9475,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9513,7 +9518,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 15559-2023</t>
+          <t>A 46371-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9527,10 +9532,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45019</v>
+        <v>44848</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9542,8 +9547,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9586,7 +9596,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21755-2026</t>
+          <t>A 59383-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9600,10 +9610,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46149</v>
+        <v>45638</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9615,8 +9625,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9659,7 +9674,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 21826-2026</t>
+          <t>A 33745-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9673,10 +9688,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46150</v>
+        <v>45133</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9689,7 +9704,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9732,7 +9747,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21828-2026</t>
+          <t>A 58226-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9746,10 +9761,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46150</v>
+        <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9762,7 +9777,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9805,7 +9820,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 22321-2026</t>
+          <t>A 5326-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9819,10 +9834,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46154</v>
+        <v>45331</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9835,7 +9850,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9878,7 +9893,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61898-2025</t>
+          <t>A 10850-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9892,10 +9907,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46003</v>
+        <v>46078</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9951,7 +9966,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 9983-2022</t>
+          <t>A 2982-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9965,10 +9980,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44621</v>
+        <v>45678</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9981,7 +9996,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10024,7 +10039,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 29329-2024</t>
+          <t>A 57663-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10038,10 +10053,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45483</v>
+        <v>45981</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10054,7 +10069,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10097,7 +10112,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 2982-2025</t>
+          <t>A 61898-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10111,10 +10126,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45678</v>
+        <v>46003</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10127,7 +10142,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10170,7 +10185,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 20476-2023</t>
+          <t>A 60768-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10184,10 +10199,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45057</v>
+        <v>44907</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10200,7 +10215,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10243,7 +10258,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19134-2025</t>
+          <t>A 20888-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10253,14 +10268,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45764</v>
+        <v>44701</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10273,7 +10288,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10316,7 +10331,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20968-2023</t>
+          <t>A 14465-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10330,10 +10345,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45061</v>
+        <v>46100</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10346,7 +10361,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10389,7 +10404,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 50401-2021</t>
+          <t>A 14440-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10403,10 +10418,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44459</v>
+        <v>46100</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10419,7 +10434,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10462,7 +10477,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 23027-2026</t>
+          <t>A 14456-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10476,10 +10491,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46161</v>
+        <v>46100</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10492,7 +10507,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10535,7 +10550,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 11897-2025</t>
+          <t>A 14462-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10549,10 +10564,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45728</v>
+        <v>46100</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10565,7 +10580,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10608,7 +10623,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 880-2026</t>
+          <t>A 45617-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10622,10 +10637,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46029</v>
+        <v>45579</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10638,7 +10653,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10681,7 +10696,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 22560-2023</t>
+          <t>A 14437-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10695,10 +10710,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45071</v>
+        <v>46100</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10711,7 +10726,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10754,7 +10769,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 1608-2026</t>
+          <t>A 9983-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10768,10 +10783,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46034</v>
+        <v>44621</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10784,7 +10799,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10827,7 +10842,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 28586-2025</t>
+          <t>A 33131-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10841,10 +10856,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45819</v>
+        <v>45126</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10857,7 +10872,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10900,7 +10915,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 1945-2026</t>
+          <t>A 31388-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10914,10 +10929,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46035</v>
+        <v>44774</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10930,7 +10945,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10973,7 +10988,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 2322-2026</t>
+          <t>A 29195-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10987,10 +11002,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46036</v>
+        <v>45482</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11003,7 +11018,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11046,7 +11061,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 2324-2026</t>
+          <t>A 994-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11060,10 +11075,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46036</v>
+        <v>45301</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11076,7 +11091,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11119,7 +11134,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 50034-2022</t>
+          <t>A 14833-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11133,10 +11148,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44865</v>
+        <v>46103</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11149,7 +11164,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11192,7 +11207,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 12945-2024</t>
+          <t>A 31917-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11206,10 +11221,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45385</v>
+        <v>45834</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11222,7 +11237,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11265,7 +11280,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 994-2024</t>
+          <t>A 10457-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11279,10 +11294,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45301</v>
+        <v>44987</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11295,7 +11310,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11338,7 +11353,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 6379-2026</t>
+          <t>A 29308-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11352,10 +11367,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46055</v>
+        <v>45824</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11368,7 +11383,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11411,7 +11426,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 26409-2026</t>
+          <t>A 50034-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11425,10 +11440,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46182</v>
+        <v>44865</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11441,7 +11456,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11484,7 +11499,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 3187-2024</t>
+          <t>A 33559-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11498,10 +11513,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45316</v>
+        <v>45841</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11513,13 +11528,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11562,7 +11572,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 7466-2026</t>
+          <t>A 57768-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11576,10 +11586,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46059</v>
+        <v>44892</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11591,13 +11601,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11640,7 +11645,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7545-2026</t>
+          <t>A 48688-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11654,10 +11659,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46059</v>
+        <v>45936</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11670,7 +11675,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11713,7 +11718,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 8060-2026</t>
+          <t>A 16363-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11727,10 +11732,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46063</v>
+        <v>45407</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11743,7 +11748,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11786,7 +11791,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 8051-2026</t>
+          <t>A 15704-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11800,10 +11805,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46063</v>
+        <v>45748</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11816,7 +11821,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11859,7 +11864,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 8058-2026</t>
+          <t>A 72625-2021</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11873,10 +11878,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46063</v>
+        <v>44546</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11889,7 +11894,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11932,7 +11937,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 39001-2024</t>
+          <t>A 29300-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11946,10 +11951,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45548</v>
+        <v>45824</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11962,7 +11967,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12005,7 +12010,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 38983-2024</t>
+          <t>A 19134-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12015,14 +12020,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45548</v>
+        <v>45764</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12035,7 +12040,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12078,7 +12083,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 13109-2023</t>
+          <t>A 33118-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12092,10 +12097,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45002</v>
+        <v>45126</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12108,7 +12113,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12151,7 +12156,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 56130-2022</t>
+          <t>A 37311-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12161,14 +12166,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44886</v>
+        <v>45876</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12181,7 +12186,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12224,7 +12229,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33747-2023</t>
+          <t>A 38988-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12238,10 +12243,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45133</v>
+        <v>45548</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12254,7 +12259,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12314,7 +12319,7 @@
         <v>44903</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12370,7 +12375,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 21333-2024</t>
+          <t>A 56196-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12384,10 +12389,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45440</v>
+        <v>45974</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12400,7 +12405,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12443,7 +12448,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 29195-2024</t>
+          <t>A 11891-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12457,10 +12462,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45482</v>
+        <v>45728</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12473,7 +12478,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12516,7 +12521,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 45617-2024</t>
+          <t>A 21355-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12530,10 +12535,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45579</v>
+        <v>46142</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12546,7 +12551,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12589,7 +12594,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 28319-2026</t>
+          <t>A 15559-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12603,10 +12608,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46196</v>
+        <v>45019</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12619,7 +12624,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12662,7 +12667,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 22693-2026</t>
+          <t>A 54007-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12676,10 +12681,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46156</v>
+        <v>45615</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12692,7 +12697,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12735,7 +12740,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 56602-2023</t>
+          <t>A 33747-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12749,10 +12754,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45243</v>
+        <v>45133</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12765,7 +12770,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12808,7 +12813,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 7136-2022</t>
+          <t>A 21755-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12822,10 +12827,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44603</v>
+        <v>46149</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12838,7 +12843,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12881,7 +12886,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 50601-2024</t>
+          <t>A 21819-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12895,10 +12900,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45600</v>
+        <v>46150</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12911,7 +12916,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12954,7 +12959,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 67875-2021</t>
+          <t>A 21826-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12968,10 +12973,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44525</v>
+        <v>46150</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12984,7 +12989,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>15.5</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13027,7 +13032,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 16363-2024</t>
+          <t>A 21828-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13041,10 +13046,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45407</v>
+        <v>46150</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13057,7 +13062,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13100,7 +13105,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 29587-2026</t>
+          <t>A 21839-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13114,10 +13119,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46204</v>
+        <v>46150</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13130,7 +13135,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13173,7 +13178,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 41072-2023</t>
+          <t>A 21833-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13187,10 +13192,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45170</v>
+        <v>46150</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13203,7 +13208,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13246,7 +13251,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 10470-2024</t>
+          <t>A 44523-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13260,10 +13265,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45366</v>
+        <v>45189</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13276,7 +13281,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13319,7 +13324,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 61252-2024</t>
+          <t>A 22321-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13333,10 +13338,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45645</v>
+        <v>46154</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13349,7 +13354,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13392,7 +13397,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 40369-2024</t>
+          <t>A 23027-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13406,10 +13411,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45555</v>
+        <v>46161</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13422,7 +13427,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>14.5</v>
+        <v>4.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13465,7 +13470,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 56024-2023</t>
+          <t>A 8047-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13475,14 +13480,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45240</v>
+        <v>45351</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13495,7 +13500,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13538,7 +13543,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 5326-2024</t>
+          <t>A 28586-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13552,10 +13557,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45331</v>
+        <v>45819</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13568,7 +13573,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13611,7 +13616,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 56677-2023</t>
+          <t>A 13109-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13625,10 +13630,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45243</v>
+        <v>45002</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13641,7 +13646,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13684,7 +13689,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 52262-2023</t>
+          <t>A 21333-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13698,10 +13703,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45217</v>
+        <v>45440</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13714,7 +13719,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13757,7 +13762,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 38818-2024</t>
+          <t>A 29192-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13771,10 +13776,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45547</v>
+        <v>45482</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13787,7 +13792,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13830,7 +13835,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 8047-2024</t>
+          <t>A 67875-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13840,14 +13845,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45351</v>
+        <v>44525</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13860,7 +13865,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>15.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13903,7 +13908,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 35205-2026</t>
+          <t>A 26409-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13917,10 +13922,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46260</v>
+        <v>46182</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13933,7 +13938,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13976,7 +13981,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 25884-2023</t>
+          <t>A 38983-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13990,10 +13995,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45085</v>
+        <v>45548</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14006,7 +14011,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14049,7 +14054,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 54007-2024</t>
+          <t>A 29327-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14063,10 +14068,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45615</v>
+        <v>45483</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14079,7 +14084,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14122,7 +14127,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 20888-2022</t>
+          <t>A 28319-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14136,10 +14141,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44701</v>
+        <v>46196</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14152,7 +14157,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14195,7 +14200,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 35946-2026</t>
+          <t>A 56602-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14209,10 +14214,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46266</v>
+        <v>45243</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14225,7 +14230,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14268,7 +14273,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 60768-2022</t>
+          <t>A 22693-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14282,10 +14287,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44907</v>
+        <v>46156</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14298,7 +14303,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14341,7 +14346,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 52950-2022</t>
+          <t>A 41072-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14355,10 +14360,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44875</v>
+        <v>45170</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14371,7 +14376,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14414,7 +14419,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 52852-2024</t>
+          <t>A 3391-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14428,10 +14433,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45610</v>
+        <v>45318</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14443,8 +14448,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14487,7 +14497,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 15704-2025</t>
+          <t>A 20968-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14501,10 +14511,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45748</v>
+        <v>45061</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14517,7 +14527,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14560,7 +14570,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 61626-2024</t>
+          <t>A 29587-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14574,10 +14584,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45646</v>
+        <v>46204</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14590,7 +14600,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>7.3</v>
+        <v>2.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14633,7 +14643,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 3178-2024</t>
+          <t>A 22560-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14647,10 +14657,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45316</v>
+        <v>45071</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14662,13 +14672,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>8.6</v>
+        <v>1.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14711,7 +14716,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 61249-2024</t>
+          <t>A 54792-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14725,10 +14730,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45645</v>
+        <v>45236</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14741,7 +14746,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14784,7 +14789,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 31837-2026</t>
+          <t>A 45578-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14798,10 +14803,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46230</v>
+        <v>45578</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14814,7 +14819,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14857,7 +14862,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 38988-2024</t>
+          <t>A 61249-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14871,10 +14876,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45548</v>
+        <v>45645</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14887,7 +14892,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14930,7 +14935,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37058-2026</t>
+          <t>A 35205-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14944,10 +14949,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46273</v>
+        <v>46260</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14960,7 +14965,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15003,7 +15008,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 45632-2024</t>
+          <t>A 38818-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15017,10 +15022,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45579</v>
+        <v>45547</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15032,13 +15037,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>9.5</v>
+        <v>1.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 50603-2024</t>
+          <t>A 45632-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15095,10 +15095,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45600</v>
+        <v>45579</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15110,8 +15110,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.4</v>
+        <v>9.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15154,7 +15159,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 61250-2024</t>
+          <t>A 7136-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15168,10 +15173,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45645</v>
+        <v>44603</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15184,7 +15189,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15244,7 +15249,7 @@
         <v>45085</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15300,7 +15305,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37822-2026</t>
+          <t>A 35946-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15314,10 +15319,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15330,7 +15335,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15373,7 +15378,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 46532-2024</t>
+          <t>A 989-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15387,10 +15392,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45582</v>
+        <v>45301</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15403,7 +15408,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15446,7 +15451,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 49551-2024</t>
+          <t>A 61250-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15460,10 +15465,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45596</v>
+        <v>45645</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15476,7 +15481,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15519,7 +15524,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 9695-2025</t>
+          <t>A 13325-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15533,10 +15538,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45716</v>
+        <v>44645</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15549,7 +15554,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15592,7 +15597,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 14079-2025</t>
+          <t>A 31837-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15606,10 +15611,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45739</v>
+        <v>46230</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15622,7 +15627,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15665,7 +15670,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 11931-2025</t>
+          <t>A 56677-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15679,10 +15684,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45728</v>
+        <v>45243</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15695,7 +15700,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15738,7 +15743,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 14087-2025</t>
+          <t>A 56130-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15748,14 +15753,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45739</v>
+        <v>44886</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15768,7 +15773,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15811,7 +15816,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 49554-2024</t>
+          <t>A 21061-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15825,10 +15830,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45596</v>
+        <v>44704</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15841,7 +15846,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15884,7 +15889,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 26233-2025</t>
+          <t>A 54374-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15898,10 +15903,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45805</v>
+        <v>44879</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15913,13 +15918,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15962,7 +15962,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 26270-2025</t>
+          <t>A 37822-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15976,10 +15976,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45805</v>
+        <v>46279</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16035,7 +16035,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 13890-2022</t>
+          <t>A 15695-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16049,10 +16049,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44649</v>
+        <v>45748</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16108,7 +16108,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 15552-2023</t>
+          <t>A 49551-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45018</v>
+        <v>45596</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16181,7 +16181,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 33569-2025</t>
+          <t>A 46532-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16195,10 +16195,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45841</v>
+        <v>45582</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16254,7 +16254,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 33586-2025</t>
+          <t>A 37058-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16268,10 +16268,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45841</v>
+        <v>46273</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16327,7 +16327,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 33580-2025</t>
+          <t>A 11931-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16341,10 +16341,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45841</v>
+        <v>45728</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16400,7 +16400,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 26277-2025</t>
+          <t>A 14087-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16414,10 +16414,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45805</v>
+        <v>45739</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16473,7 +16473,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 33536-2025</t>
+          <t>A 9695-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16487,10 +16487,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45841</v>
+        <v>45716</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16546,7 +16546,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 16223-2025</t>
+          <t>A 14079-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16560,10 +16560,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45750</v>
+        <v>45739</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16636,7 +16636,7 @@
         <v>45194</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>44788</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>46036</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE208"/>
+  <dimension ref="A1:AE209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50432-2025</t>
+          <t>A 4173-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45944</v>
+        <v>44588</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1110,599 +1110,599 @@
         <v>3</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 50432-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Älg
 Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50432-2025 artfynd.xlsx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50432-2025 karta.png", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50432-2025 georefererad karta.tif", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50432-2025 FSC-klagomål.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50432-2025 FSC-klagomål mail.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50432-2025 tillsynsbegäran.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50432-2025 tillsynsbegäran mail.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50432-2025 prioriterade fågelarter.docx", "A 50432-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 50437-2025</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>45944</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>3.6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>3</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>5</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Älg
 Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50437-2025 artfynd.xlsx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50437-2025 karta.png", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50437-2025 georefererad karta.tif", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50437-2025 FSC-klagomål.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50437-2025 FSC-klagomål mail.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50437-2025 tillsynsbegäran.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50437-2025 tillsynsbegäran mail.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50437-2025 prioriterade fågelarter.docx", "A 50437-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 6043-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönpyrola
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35974-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa
+Klippfrullania
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35974-2026 artfynd.xlsx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35974-2026 karta.png", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35974-2026 georefererad karta.tif", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35974-2026 FSC-klagomål.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35974-2026 FSC-klagomål mail.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35974-2026 tillsynsbegäran.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35974-2026 tillsynsbegäran mail.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 62152-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46006</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>3.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T11" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 6043-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45336</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönpyrola
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 4173-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44588</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>5</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 35974-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grov fjädermossa
-Klippfrullania
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35974-2026 artfynd.xlsx", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35974-2026 karta.png", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35974-2026 georefererad karta.tif", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35974-2026 FSC-klagomål.docx", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35974-2026 FSC-klagomål mail.docx", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35974-2026 tillsynsbegäran.docx", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35974-2026 tillsynsbegäran mail.docx", "A 35974-2026")</f>
         <v/>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44571</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 9001-2025</t>
+          <t>A 9839-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45713</v>
+        <v>46072</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>2</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1980,385 +1980,385 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 48687-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9001-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45713</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9839-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 8291-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 8291-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 48687-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Backstarr
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33772-2023</t>
+          <t>A 15667-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45133</v>
+        <v>45404</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2424,50 +2424,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 50607-2025</t>
+          <t>A 10764-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2477,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45945</v>
+        <v>45369</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,7 +2493,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>14.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2533,46 +2529,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15667-2024</t>
+          <t>A 24514-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2582,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45404</v>
+        <v>45458</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2602,16 +2598,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2626,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2642,42 +2638,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12238-2025</t>
+          <t>A 14442-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2691,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45729</v>
+        <v>46100</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2707,7 +2703,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.6</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2719,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2731,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2743,50 +2739,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 64707-2023</t>
+          <t>A 14455-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2800,10 +2792,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45281</v>
+        <v>46100</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2815,13 +2807,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>11.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2833,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2845,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2861,39 +2848,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
-        <v/>
-      </c>
-      <c r="Z22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
     </row>
@@ -2917,7 +2900,7 @@
         <v>45230</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3009,7 +2992,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10764-2024</t>
+          <t>A 6128-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3023,10 +3006,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45369</v>
+        <v>46054</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3039,7 +3022,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>8.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3083,38 +3066,38 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14442-2026</t>
+          <t>A 50607-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3128,10 +3111,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46100</v>
+        <v>45945</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3144,7 +3127,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>14.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3156,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3168,10 +3151,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3180,46 +3163,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 14455-2026</t>
+          <t>A 33772-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3233,10 +3216,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46100</v>
+        <v>45133</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3249,7 +3232,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3258,7 +3241,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3273,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3289,42 +3272,46 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 24514-2024</t>
+          <t>A 35813-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3338,10 +3325,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45458</v>
+        <v>46264</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3354,7 +3341,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>23.7</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3390,46 +3377,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6128-2026</t>
+          <t>A 64707-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3443,10 +3430,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46054</v>
+        <v>45281</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3458,8 +3445,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3471,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3483,10 +3475,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3499,42 +3491,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
+        <v/>
+      </c>
+      <c r="Z28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35813-2026</t>
+          <t>A 12238-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3548,10 +3544,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46264</v>
+        <v>45729</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3564,7 +3560,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>23.7</v>
+        <v>10.6</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3600,39 +3596,43 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
         <v/>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
         <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>44865</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44457</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44606</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>44848</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44865</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44764</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44510</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44526</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44851</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44722</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44533</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44494</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44588</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53761-2024</t>
+          <t>A 31388-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45615</v>
+        <v>44774</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61626-2024</t>
+          <t>A 30701-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45646</v>
+        <v>44763</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.3</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52262-2023</t>
+          <t>A 55712-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45217</v>
+        <v>44885</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3178-2024</t>
+          <t>A 46371-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45316</v>
+        <v>44848</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12945-2024</t>
+          <t>A 54374-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45385</v>
+        <v>44879</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16989-2023</t>
+          <t>A 44523-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45033</v>
+        <v>45189</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5872,13 +5872,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5921,7 +5916,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10470-2024</t>
+          <t>A 29327-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5935,10 +5930,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45366</v>
+        <v>45483</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5951,7 +5946,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5994,7 +5989,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55712-2022</t>
+          <t>A 41991-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6008,10 +6003,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44885</v>
+        <v>44830</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6024,7 +6019,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6067,7 +6062,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11897-2025</t>
+          <t>A 72625-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6081,10 +6076,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45728</v>
+        <v>44546</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6097,7 +6092,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6140,7 +6135,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29329-2024</t>
+          <t>A 8060-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6154,10 +6149,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45483</v>
+        <v>46063</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6170,7 +6165,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6213,7 +6208,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61252-2024</t>
+          <t>A 8051-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6227,10 +6222,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45645</v>
+        <v>46063</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6243,7 +6238,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6286,7 +6281,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30701-2022</t>
+          <t>A 8058-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6300,10 +6295,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44763</v>
+        <v>46063</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6359,7 +6354,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 49554-2024</t>
+          <t>A 33118-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6373,10 +6368,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45596</v>
+        <v>45126</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6389,7 +6384,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6432,7 +6427,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39001-2024</t>
+          <t>A 33131-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6446,10 +6441,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45548</v>
+        <v>45126</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6462,7 +6457,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6505,7 +6500,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 880-2026</t>
+          <t>A 15695-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6519,10 +6514,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46029</v>
+        <v>45748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6535,7 +6530,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6578,7 +6573,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 26233-2025</t>
+          <t>A 10850-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6592,10 +6587,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45805</v>
+        <v>46078</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6607,13 +6602,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6656,7 +6646,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26270-2025</t>
+          <t>A 45578-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6670,10 +6660,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45805</v>
+        <v>45578</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6686,7 +6676,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6729,7 +6719,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52950-2022</t>
+          <t>A 13325-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6743,10 +6733,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44875</v>
+        <v>44645</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6759,7 +6749,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6802,7 +6792,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15552-2023</t>
+          <t>A 33569-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6816,10 +6806,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45018</v>
+        <v>45841</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6832,7 +6822,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6875,7 +6865,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13890-2022</t>
+          <t>A 33586-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6889,10 +6879,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44649</v>
+        <v>45841</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6905,7 +6895,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6948,7 +6938,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 40369-2024</t>
+          <t>A 33580-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6962,10 +6952,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45555</v>
+        <v>45841</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6978,7 +6968,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>14.5</v>
+        <v>2.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7021,7 +7011,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1945-2026</t>
+          <t>A 26277-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7035,10 +7025,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46035</v>
+        <v>45805</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7051,7 +7041,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7094,7 +7084,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 44529-2023</t>
+          <t>A 33536-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7108,10 +7098,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45189</v>
+        <v>45841</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7124,7 +7114,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.6</v>
+        <v>6.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7167,7 +7157,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 55733-2023</t>
+          <t>A 14440-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7181,10 +7171,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45232</v>
+        <v>46100</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7197,7 +7187,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7240,7 +7230,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1608-2026</t>
+          <t>A 14456-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7254,10 +7244,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46034</v>
+        <v>46100</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7270,7 +7260,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7313,7 +7303,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2322-2026</t>
+          <t>A 14465-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7327,10 +7317,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46036</v>
+        <v>46100</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7343,7 +7333,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7386,7 +7376,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2324-2026</t>
+          <t>A 14462-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7400,10 +7390,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46036</v>
+        <v>46100</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7416,7 +7406,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7459,7 +7449,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 52852-2024</t>
+          <t>A 59383-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7473,10 +7463,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45610</v>
+        <v>45638</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7488,8 +7478,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7532,7 +7527,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44319-2025</t>
+          <t>A 14437-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7546,10 +7541,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45916</v>
+        <v>46100</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7562,7 +7557,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7605,7 +7600,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33569-2025</t>
+          <t>A 10457-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7619,10 +7614,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45841</v>
+        <v>44987</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7635,7 +7630,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7678,7 +7673,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33586-2025</t>
+          <t>A 16223-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7692,10 +7687,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45841</v>
+        <v>45750</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7708,7 +7703,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7751,7 +7746,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33536-2025</t>
+          <t>A 53761-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7765,10 +7760,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45841</v>
+        <v>45615</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7781,7 +7776,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7824,7 +7819,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33580-2025</t>
+          <t>A 16989-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7838,10 +7833,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45841</v>
+        <v>45033</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7853,8 +7848,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7897,7 +7897,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 26277-2025</t>
+          <t>A 14833-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7911,10 +7911,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45805</v>
+        <v>46103</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7970,7 +7970,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 25884-2023</t>
+          <t>A 17525-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7984,10 +7984,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45085</v>
+        <v>45757</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8043,7 +8043,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 50603-2024</t>
+          <t>A 44529-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8057,10 +8057,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45600</v>
+        <v>45189</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8116,7 +8116,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16223-2025</t>
+          <t>A 44319-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45750</v>
+        <v>45916</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8189,7 +8189,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20476-2023</t>
+          <t>A 33745-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45057</v>
+        <v>45133</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8262,7 +8262,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 50626-2025</t>
+          <t>A 31917-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45945</v>
+        <v>45834</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8291,13 +8291,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>14</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8340,7 +8335,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50578-2025</t>
+          <t>A 29329-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8354,10 +8349,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45945</v>
+        <v>45483</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8370,7 +8365,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8413,7 +8408,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50797-2025</t>
+          <t>A 29308-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8427,10 +8422,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45946</v>
+        <v>45824</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8443,7 +8438,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8486,7 +8481,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17525-2025</t>
+          <t>A 2982-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8500,10 +8495,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45757</v>
+        <v>45678</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8516,7 +8511,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8559,7 +8554,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 50401-2021</t>
+          <t>A 20476-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8573,10 +8568,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44459</v>
+        <v>45057</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8589,7 +8584,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8632,7 +8627,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56024-2023</t>
+          <t>A 29300-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8646,10 +8641,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45240</v>
+        <v>45824</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8662,7 +8657,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8705,7 +8700,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6379-2026</t>
+          <t>A 19134-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8715,14 +8710,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46055</v>
+        <v>45764</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8735,7 +8730,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8778,7 +8773,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50601-2024</t>
+          <t>A 50401-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8792,10 +8787,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45600</v>
+        <v>44459</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8808,7 +8803,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8851,7 +8846,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 7545-2026</t>
+          <t>A 11897-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8865,10 +8860,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46059</v>
+        <v>45728</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8881,7 +8876,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8924,7 +8919,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7466-2026</t>
+          <t>A 33559-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8938,10 +8933,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46059</v>
+        <v>45841</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8953,13 +8948,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9002,7 +8992,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8051-2026</t>
+          <t>A 56196-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9016,10 +9006,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46063</v>
+        <v>45974</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9032,7 +9022,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9075,7 +9065,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8058-2026</t>
+          <t>A 22560-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9089,10 +9079,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46063</v>
+        <v>45071</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9105,7 +9095,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9148,7 +9138,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 54126-2025</t>
+          <t>A 48688-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9162,10 +9152,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45964</v>
+        <v>45936</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9178,7 +9168,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9221,7 +9211,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 41991-2022</t>
+          <t>A 37311-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9235,10 +9225,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44830</v>
+        <v>45876</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9251,7 +9241,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9294,7 +9284,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 8060-2026</t>
+          <t>A 50034-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9308,10 +9298,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46063</v>
+        <v>44865</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9324,7 +9314,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9367,7 +9357,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 3187-2024</t>
+          <t>A 21355-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9381,10 +9371,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45316</v>
+        <v>46142</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9396,13 +9386,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9445,7 +9430,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 55830-2025</t>
+          <t>A 12945-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9459,10 +9444,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45972</v>
+        <v>45385</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9475,7 +9460,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9518,7 +9503,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 46371-2022</t>
+          <t>A 21819-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9532,10 +9517,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44848</v>
+        <v>46150</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9547,13 +9532,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9596,7 +9576,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 59383-2024</t>
+          <t>A 21833-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9610,10 +9590,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45638</v>
+        <v>46150</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9625,13 +9605,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9674,7 +9649,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 33745-2023</t>
+          <t>A 994-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9688,10 +9663,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45133</v>
+        <v>45301</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9704,7 +9679,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9747,7 +9722,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 58226-2025</t>
+          <t>A 21839-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9761,10 +9736,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45985</v>
+        <v>46150</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9777,7 +9752,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9820,7 +9795,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 5326-2024</t>
+          <t>A 21755-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9834,10 +9809,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45331</v>
+        <v>46149</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9850,7 +9825,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9893,7 +9868,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10850-2026</t>
+          <t>A 21826-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9907,10 +9882,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46078</v>
+        <v>46150</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9923,7 +9898,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9966,7 +9941,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 2982-2025</t>
+          <t>A 21828-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9980,10 +9955,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45678</v>
+        <v>46150</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9996,7 +9971,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10039,7 +10014,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 57663-2025</t>
+          <t>A 3187-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10053,10 +10028,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45981</v>
+        <v>45316</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10068,8 +10043,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10112,7 +10092,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61898-2025</t>
+          <t>A 22321-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10126,10 +10106,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46003</v>
+        <v>46154</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10142,7 +10122,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10185,7 +10165,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 60768-2022</t>
+          <t>A 39001-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10199,10 +10179,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44907</v>
+        <v>45548</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10215,7 +10195,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10258,7 +10238,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20888-2022</t>
+          <t>A 38983-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10272,10 +10252,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44701</v>
+        <v>45548</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10288,7 +10268,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10331,7 +10311,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 14465-2026</t>
+          <t>A 23027-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10345,10 +10325,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46100</v>
+        <v>46161</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10361,7 +10341,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10404,7 +10384,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 14440-2026</t>
+          <t>A 13109-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10418,10 +10398,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46100</v>
+        <v>45002</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10434,7 +10414,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10477,7 +10457,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 14456-2026</t>
+          <t>A 28586-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10491,10 +10471,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46100</v>
+        <v>45819</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10507,7 +10487,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10550,7 +10530,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 14462-2026</t>
+          <t>A 56130-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10560,14 +10540,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46100</v>
+        <v>44886</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10580,7 +10560,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10623,7 +10603,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 45617-2024</t>
+          <t>A 33747-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10637,10 +10617,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45579</v>
+        <v>45133</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10653,7 +10633,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10696,7 +10676,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14437-2026</t>
+          <t>A 21333-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10710,10 +10690,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46100</v>
+        <v>45440</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10726,7 +10706,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10769,7 +10749,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 9983-2022</t>
+          <t>A 50626-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10783,10 +10763,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44621</v>
+        <v>45945</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10798,8 +10778,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>14</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10842,7 +10827,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 33131-2023</t>
+          <t>A 29195-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10856,10 +10841,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45126</v>
+        <v>45482</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10915,7 +10900,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31388-2022</t>
+          <t>A 56602-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10929,10 +10914,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44774</v>
+        <v>45243</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10945,7 +10930,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10988,7 +10973,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 29195-2024</t>
+          <t>A 50578-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11002,10 +10987,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45482</v>
+        <v>45945</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11018,7 +11003,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11061,7 +11046,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 994-2024</t>
+          <t>A 50797-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11075,10 +11060,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45301</v>
+        <v>45946</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11091,7 +11076,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11134,7 +11119,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 14833-2026</t>
+          <t>A 7136-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11148,10 +11133,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46103</v>
+        <v>44603</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11164,7 +11149,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11207,7 +11192,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 31917-2025</t>
+          <t>A 26409-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11221,10 +11206,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45834</v>
+        <v>46182</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11237,7 +11222,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11280,7 +11265,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 10457-2023</t>
+          <t>A 50601-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11294,10 +11279,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44987</v>
+        <v>45600</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11310,7 +11295,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11353,7 +11338,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 29308-2025</t>
+          <t>A 67875-2021</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11367,10 +11352,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45824</v>
+        <v>44525</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11383,7 +11368,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.6</v>
+        <v>15.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11426,7 +11411,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 50034-2022</t>
+          <t>A 16363-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11440,10 +11425,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44865</v>
+        <v>45407</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11456,7 +11441,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11499,7 +11484,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 33559-2025</t>
+          <t>A 41072-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11513,10 +11498,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45841</v>
+        <v>45170</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11529,7 +11514,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11572,7 +11557,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 57768-2022</t>
+          <t>A 10470-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11586,10 +11571,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44892</v>
+        <v>45366</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11602,7 +11587,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11645,7 +11630,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 48688-2025</t>
+          <t>A 40369-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11659,10 +11644,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45936</v>
+        <v>45555</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11675,7 +11660,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11718,7 +11703,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 16363-2024</t>
+          <t>A 54126-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11732,10 +11717,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45407</v>
+        <v>45964</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11748,7 +11733,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11791,7 +11776,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 15704-2025</t>
+          <t>A 28319-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11805,10 +11790,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45748</v>
+        <v>46196</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11821,7 +11806,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11864,7 +11849,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 72625-2021</t>
+          <t>A 22693-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11878,10 +11863,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44546</v>
+        <v>46156</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11894,7 +11879,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11937,7 +11922,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 29300-2025</t>
+          <t>A 55830-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11951,10 +11936,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45824</v>
+        <v>45972</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11967,7 +11952,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12010,7 +11995,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 19134-2025</t>
+          <t>A 52262-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12020,14 +12005,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45764</v>
+        <v>45217</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12040,7 +12025,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12083,7 +12068,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 33118-2023</t>
+          <t>A 38818-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12097,10 +12082,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45126</v>
+        <v>45547</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12113,7 +12098,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12156,7 +12141,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 37311-2025</t>
+          <t>A 8047-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12166,14 +12151,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45876</v>
+        <v>45351</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12186,7 +12171,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12229,7 +12214,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 38988-2024</t>
+          <t>A 25884-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12243,10 +12228,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45548</v>
+        <v>45085</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12259,7 +12244,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12302,7 +12287,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 60220-2022</t>
+          <t>A 54007-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12316,10 +12301,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44903</v>
+        <v>45615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12332,7 +12317,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12375,7 +12360,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 56196-2025</t>
+          <t>A 20888-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12389,10 +12374,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45974</v>
+        <v>44701</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12405,7 +12390,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12448,7 +12433,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 11891-2025</t>
+          <t>A 29587-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12462,10 +12447,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45728</v>
+        <v>46204</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12478,7 +12463,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12521,7 +12506,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21355-2026</t>
+          <t>A 58226-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12535,10 +12520,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46142</v>
+        <v>45985</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12551,7 +12536,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12594,7 +12579,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 15559-2023</t>
+          <t>A 54792-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12608,10 +12593,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45019</v>
+        <v>45236</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12624,7 +12609,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12667,7 +12652,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 54007-2024</t>
+          <t>A 11891-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12681,10 +12666,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45615</v>
+        <v>45728</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12697,7 +12682,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12740,7 +12725,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 33747-2023</t>
+          <t>A 3391-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12754,10 +12739,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45133</v>
+        <v>45318</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12769,8 +12754,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12813,7 +12803,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 21755-2026</t>
+          <t>A 21061-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12827,10 +12817,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46149</v>
+        <v>44704</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12843,7 +12833,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12886,7 +12876,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 21819-2026</t>
+          <t>A 55733-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12900,10 +12890,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46150</v>
+        <v>45232</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12916,7 +12906,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12959,7 +12949,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 21826-2026</t>
+          <t>A 35205-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12973,10 +12963,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46150</v>
+        <v>46260</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12989,7 +12979,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13032,7 +13022,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 21828-2026</t>
+          <t>A 57663-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13046,10 +13036,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46150</v>
+        <v>45981</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13062,7 +13052,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13105,7 +13095,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 21839-2026</t>
+          <t>A 989-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13119,10 +13109,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46150</v>
+        <v>45301</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13135,7 +13125,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13178,7 +13168,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 21833-2026</t>
+          <t>A 35946-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13192,10 +13182,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46150</v>
+        <v>46266</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13208,7 +13198,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13251,7 +13241,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 44523-2023</t>
+          <t>A 61898-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13265,10 +13255,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45189</v>
+        <v>46003</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13281,7 +13271,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13324,7 +13314,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 22321-2026</t>
+          <t>A 31837-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13338,10 +13328,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46154</v>
+        <v>46230</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13354,7 +13344,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13397,7 +13387,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 23027-2026</t>
+          <t>A 29192-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13411,10 +13401,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46161</v>
+        <v>45482</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13427,7 +13417,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13470,7 +13460,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 8047-2024</t>
+          <t>A 57768-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13480,14 +13470,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45351</v>
+        <v>44892</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13500,7 +13490,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13543,7 +13533,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 28586-2025</t>
+          <t>A 37822-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13557,10 +13547,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45819</v>
+        <v>46279</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13573,7 +13563,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13616,7 +13606,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 13109-2023</t>
+          <t>A 880-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13630,10 +13620,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45002</v>
+        <v>46029</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13646,7 +13636,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13689,7 +13679,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 21333-2024</t>
+          <t>A 37058-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13703,10 +13693,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45440</v>
+        <v>46273</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13719,7 +13709,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13762,7 +13752,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 29192-2024</t>
+          <t>A 15559-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13776,10 +13766,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45482</v>
+        <v>45019</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13792,7 +13782,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13835,7 +13825,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 67875-2021</t>
+          <t>A 1608-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13849,10 +13839,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44525</v>
+        <v>46034</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13865,7 +13855,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>15.5</v>
+        <v>0.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13908,7 +13898,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 26409-2026</t>
+          <t>A 38350-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13922,10 +13912,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46182</v>
+        <v>46282</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13937,8 +13927,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13981,7 +13976,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 38983-2024</t>
+          <t>A 9983-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13995,10 +13990,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45548</v>
+        <v>44621</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14011,7 +14006,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14054,7 +14049,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 29327-2024</t>
+          <t>A 20968-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14068,10 +14063,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45483</v>
+        <v>45061</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14084,7 +14079,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14127,7 +14122,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 28319-2026</t>
+          <t>A 1945-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14141,10 +14136,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46196</v>
+        <v>46035</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14157,7 +14152,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14200,7 +14195,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 56602-2023</t>
+          <t>A 2322-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14214,10 +14209,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45243</v>
+        <v>46036</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14230,7 +14225,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14273,7 +14268,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 22693-2026</t>
+          <t>A 2324-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14287,10 +14282,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46156</v>
+        <v>46036</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14303,7 +14298,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14346,7 +14341,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 41072-2023</t>
+          <t>A 60220-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14360,10 +14355,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45170</v>
+        <v>44903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14376,7 +14371,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14419,7 +14414,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 3391-2024</t>
+          <t>A 6379-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14433,10 +14428,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45318</v>
+        <v>46055</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14448,13 +14443,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14497,7 +14487,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 20968-2023</t>
+          <t>A 45617-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14511,10 +14501,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45061</v>
+        <v>45579</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14527,7 +14517,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14570,7 +14560,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 29587-2026</t>
+          <t>A 7466-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14584,10 +14574,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46204</v>
+        <v>46059</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14599,8 +14589,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14643,7 +14638,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 22560-2023</t>
+          <t>A 7545-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14657,10 +14652,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45071</v>
+        <v>46059</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14673,7 +14668,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14716,7 +14711,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 54792-2023</t>
+          <t>A 61252-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14730,10 +14725,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45236</v>
+        <v>45645</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14746,7 +14741,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14789,7 +14784,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 45578-2024</t>
+          <t>A 56024-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14803,10 +14798,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45578</v>
+        <v>45240</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14819,7 +14814,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14862,7 +14857,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 61249-2024</t>
+          <t>A 5326-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14876,10 +14871,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45645</v>
+        <v>45331</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14892,7 +14887,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14935,7 +14930,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35205-2026</t>
+          <t>A 56677-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14949,10 +14944,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46260</v>
+        <v>45243</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14965,7 +14960,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15008,7 +15003,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 38818-2024</t>
+          <t>A 60768-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15022,10 +15017,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45547</v>
+        <v>44907</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15038,7 +15033,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.9</v>
+        <v>10</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15081,7 +15076,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 45632-2024</t>
+          <t>A 52950-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15095,10 +15090,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45579</v>
+        <v>44875</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15110,13 +15105,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15159,7 +15149,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 7136-2022</t>
+          <t>A 52852-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15173,10 +15163,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44603</v>
+        <v>45610</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15189,7 +15179,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15232,7 +15222,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 24991-2023</t>
+          <t>A 15704-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15246,10 +15236,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45085</v>
+        <v>45748</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15262,7 +15252,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15305,7 +15295,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 35946-2026</t>
+          <t>A 61626-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15319,10 +15309,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46266</v>
+        <v>45646</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15335,7 +15325,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.7</v>
+        <v>7.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15378,7 +15368,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 989-2024</t>
+          <t>A 3178-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15392,10 +15382,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45301</v>
+        <v>45316</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15407,8 +15397,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.5</v>
+        <v>8.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15451,7 +15446,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 61250-2024</t>
+          <t>A 61249-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15468,7 +15463,7 @@
         <v>45645</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15481,7 +15476,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15524,7 +15519,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 13325-2022</t>
+          <t>A 38988-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15538,10 +15533,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44645</v>
+        <v>45548</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15554,7 +15549,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15597,7 +15592,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 31837-2026</t>
+          <t>A 45632-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15611,10 +15606,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46230</v>
+        <v>45579</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15626,8 +15621,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>2.1</v>
+        <v>9.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15670,7 +15670,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 56677-2023</t>
+          <t>A 50603-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15684,10 +15684,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45243</v>
+        <v>45600</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15743,7 +15743,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 56130-2022</t>
+          <t>A 61250-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15753,14 +15753,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44886</v>
+        <v>45645</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15816,7 +15816,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 21061-2022</t>
+          <t>A 24991-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15830,10 +15830,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44704</v>
+        <v>45085</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15889,7 +15889,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 54374-2022</t>
+          <t>A 46532-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15903,10 +15903,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44879</v>
+        <v>45582</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15962,7 +15962,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 37822-2026</t>
+          <t>A 49551-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15976,10 +15976,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46279</v>
+        <v>45596</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16035,7 +16035,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 15695-2025</t>
+          <t>A 9695-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16049,10 +16049,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45748</v>
+        <v>45716</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16108,7 +16108,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 49551-2024</t>
+          <t>A 14079-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45596</v>
+        <v>45739</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16181,7 +16181,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 46532-2024</t>
+          <t>A 11931-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16195,10 +16195,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45582</v>
+        <v>45728</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16254,7 +16254,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 37058-2026</t>
+          <t>A 14087-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16268,10 +16268,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46273</v>
+        <v>45739</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16327,7 +16327,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 11931-2025</t>
+          <t>A 49554-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16341,10 +16341,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45728</v>
+        <v>45596</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16400,7 +16400,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 14087-2025</t>
+          <t>A 26233-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16414,10 +16414,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45739</v>
+        <v>45805</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16429,8 +16429,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16473,7 +16478,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 9695-2025</t>
+          <t>A 26270-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16487,10 +16492,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45716</v>
+        <v>45805</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16503,7 +16508,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16546,7 +16551,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 14079-2025</t>
+          <t>A 13890-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16560,10 +16565,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45739</v>
+        <v>44649</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16576,7 +16581,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16619,24 +16624,24 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>S 3201-2023</t>
+          <t>A 15552-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45194</v>
+        <v>45018</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16649,7 +16654,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16692,148 +16697,221 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
+          <t>S 3201-2023</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>45194</v>
+      </c>
+      <c r="E207" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="n">
+        <v>0</v>
+      </c>
+      <c r="V207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208" ht="15" customHeight="1">
+      <c r="A208" t="inlineStr">
+        <is>
           <t>S 4468-2022</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>Skogsbilväg</t>
         </is>
       </c>
-      <c r="D207" s="1" t="n">
+      <c r="D208" s="1" t="n">
         <v>44788</v>
       </c>
-      <c r="E207" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I207" t="n">
+      <c r="E208" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
         <v>0.5</v>
       </c>
-      <c r="J207" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" t="n">
-        <v>0</v>
-      </c>
-      <c r="L207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M207" t="n">
-        <v>0</v>
-      </c>
-      <c r="N207" t="n">
-        <v>0</v>
-      </c>
-      <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="n">
-        <v>0</v>
-      </c>
-      <c r="T207" t="n">
-        <v>0</v>
-      </c>
-      <c r="U207" t="n">
-        <v>0</v>
-      </c>
-      <c r="V207" s="2" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
+      <c r="V208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>S 85-2026</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D208" s="1" t="n">
+      <c r="D209" s="1" t="n">
         <v>46036</v>
       </c>
-      <c r="E208" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I208" t="n">
+      <c r="E209" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
         <v>0.2</v>
       </c>
-      <c r="J208" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" t="n">
-        <v>0</v>
-      </c>
-      <c r="M208" t="n">
-        <v>0</v>
-      </c>
-      <c r="N208" t="n">
-        <v>0</v>
-      </c>
-      <c r="O208" t="n">
-        <v>0</v>
-      </c>
-      <c r="P208" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="n">
-        <v>0</v>
-      </c>
-      <c r="T208" t="n">
-        <v>0</v>
-      </c>
-      <c r="U208" t="n">
-        <v>0</v>
-      </c>
-      <c r="V208" s="2" t="inlineStr"/>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4173-2022</t>
+          <t>A 50432-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44588</v>
+        <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1110,388 +1110,388 @@
         <v>3</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50432-2025 artfynd.xlsx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50432-2025 karta.png", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50432-2025 georefererad karta.tif", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50432-2025 FSC-klagomål.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50432-2025 FSC-klagomål mail.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50432-2025 tillsynsbegäran.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50432-2025 tillsynsbegäran mail.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50432-2025 prioriterade fågelarter.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 50437-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
         <v>5</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>5</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50437-2025 artfynd.xlsx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50437-2025 karta.png", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50437-2025 georefererad karta.tif", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50437-2025 FSC-klagomål.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50437-2025 FSC-klagomål mail.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50437-2025 tillsynsbegäran.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50437-2025 tillsynsbegäran mail.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50437-2025 prioriterade fågelarter.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 6043-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönpyrola
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 62152-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 50432-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50432-2025 artfynd.xlsx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50432-2025 karta.png", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50432-2025 georefererad karta.tif", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50432-2025 FSC-klagomål.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50432-2025 FSC-klagomål mail.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50432-2025 tillsynsbegäran.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50432-2025 tillsynsbegäran mail.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50432-2025 prioriterade fågelarter.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 50437-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>5</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50437-2025 artfynd.xlsx", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50437-2025 karta.png", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50437-2025 georefererad karta.tif", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50437-2025 FSC-klagomål.docx", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50437-2025 FSC-klagomål mail.docx", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50437-2025 tillsynsbegäran.docx", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50437-2025 tillsynsbegäran mail.docx", "A 50437-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50437-2025 prioriterade fågelarter.docx", "A 50437-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 6043-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45336</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönpyrola
-Revlummer</t>
-        </is>
-      </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35974-2026</t>
+          <t>A 4173-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46266</v>
+        <v>44588</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1521,13 +1521,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1554,155 +1554,155 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 35974-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grov fjädermossa
 Klippfrullania
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35974-2026 artfynd.xlsx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35974-2026 karta.png", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35974-2026 georefererad karta.tif", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35974-2026 FSC-klagomål.docx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35974-2026 FSC-klagomål mail.docx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35974-2026 tillsynsbegäran.docx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35974-2026 tillsynsbegäran mail.docx", "A 35974-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 62152-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46006</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
         <v/>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44571</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 9839-2026</t>
+          <t>A 8291-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46072</v>
+        <v>44974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>17.3</v>
       </c>
       <c r="J14" t="n">
         <v>2</v>
@@ -1992,373 +1992,373 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9001-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45713</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9839-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 48687-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45936</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>6.4</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Blåsippa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9001-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45713</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 8291-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 15667-2024</t>
+          <t>A 33772-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45404</v>
+        <v>45133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2424,46 +2424,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10764-2024</t>
+          <t>A 64707-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45369</v>
+        <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2492,8 +2496,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>8.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2505,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2517,10 +2526,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2533,42 +2542,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24514-2024</t>
+          <t>A 15667-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2582,10 +2595,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45458</v>
+        <v>45404</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2598,17 +2611,17 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -2622,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2638,42 +2651,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14442-2026</t>
+          <t>A 53485-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2700,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46100</v>
+        <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2727,10 +2740,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2739,46 +2752,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14455-2026</t>
+          <t>A 10764-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2792,10 +2809,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46100</v>
+        <v>45369</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2808,7 +2825,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2848,42 +2865,42 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 53485-2023</t>
+          <t>A 24514-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2897,10 +2914,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45230</v>
+        <v>45458</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2913,7 +2930,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2953,46 +2970,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6128-2026</t>
+          <t>A 50607-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3006,10 +3019,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46054</v>
+        <v>45945</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3022,7 +3035,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>14.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3058,46 +3071,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 50607-2025</t>
+          <t>A 6128-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3111,10 +3124,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45945</v>
+        <v>46054</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3127,7 +3140,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>14.5</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3163,46 +3176,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33772-2023</t>
+          <t>A 12238-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3216,10 +3229,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45133</v>
+        <v>45729</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3232,7 +3245,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.2</v>
+        <v>10.6</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3241,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3256,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3268,50 +3281,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35813-2026</t>
+          <t>A 14442-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3325,10 +3338,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46264</v>
+        <v>46100</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3341,7 +3354,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>23.7</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3353,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3365,10 +3378,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3381,42 +3394,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 64707-2023</t>
+          <t>A 14455-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3430,10 +3443,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45281</v>
+        <v>46100</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3445,13 +3458,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>11.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3463,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3475,10 +3483,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3491,46 +3499,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
-        <v/>
-      </c>
-      <c r="Z28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12238-2025</t>
+          <t>A 35813-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3544,10 +3548,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45729</v>
+        <v>46264</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3560,7 +3564,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>10.6</v>
+        <v>23.7</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3596,43 +3600,39 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
         <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>44865</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50202-2021</t>
+          <t>A 7329-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44457</v>
+        <v>44606</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4665,7 +4665,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7329-2022</t>
+          <t>A 46436-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4679,10 +4679,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44606</v>
+        <v>44848</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4694,8 +4694,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4738,7 +4743,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46436-2022</t>
+          <t>A 30731-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4752,10 +4757,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44848</v>
+        <v>44764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4767,13 +4772,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4833,7 +4833,7 @@
         <v>44865</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30731-2022</t>
+          <t>A 64020-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4903,10 +4903,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44764</v>
+        <v>44510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64020-2021</t>
+          <t>A 68392-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4976,10 +4976,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44510</v>
+        <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5035,7 +5035,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 68392-2021</t>
+          <t>A 46724-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44526</v>
+        <v>44851</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 46724-2022</t>
+          <t>A 23819-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44851</v>
+        <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 23819-2022</t>
+          <t>A 70164-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44722</v>
+        <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5254,7 +5254,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 70164-2021</t>
+          <t>A 59917-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44533</v>
+        <v>44494</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59917-2021</t>
+          <t>A 4395-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44494</v>
+        <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4395-2022</t>
+          <t>A 53761-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44588</v>
+        <v>45615</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31388-2022</t>
+          <t>A 3178-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44774</v>
+        <v>45316</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5502,8 +5502,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>8.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30701-2022</t>
+          <t>A 12945-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44763</v>
+        <v>45385</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5576,7 +5581,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5619,7 +5624,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55712-2022</t>
+          <t>A 61626-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5633,10 +5638,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44885</v>
+        <v>45646</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5649,7 +5654,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5692,7 +5697,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46371-2022</t>
+          <t>A 52262-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44848</v>
+        <v>45217</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5721,13 +5726,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 54374-2022</t>
+          <t>A 16989-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44879</v>
+        <v>45033</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5799,8 +5799,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5843,7 +5848,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44523-2023</t>
+          <t>A 55712-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5857,10 +5862,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45189</v>
+        <v>44885</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5873,7 +5878,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5916,7 +5921,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29327-2024</t>
+          <t>A 10470-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5930,10 +5935,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45483</v>
+        <v>45366</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5946,7 +5951,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5989,7 +5994,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41991-2022</t>
+          <t>A 11897-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6003,10 +6008,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44830</v>
+        <v>45728</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6019,7 +6024,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6062,7 +6067,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 72625-2021</t>
+          <t>A 29329-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6076,10 +6081,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44546</v>
+        <v>45483</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6092,7 +6097,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6135,7 +6140,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8060-2026</t>
+          <t>A 61252-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6149,10 +6154,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46063</v>
+        <v>45645</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6165,7 +6170,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6208,7 +6213,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8051-2026</t>
+          <t>A 39001-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6222,10 +6227,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46063</v>
+        <v>45548</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6238,7 +6243,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6281,7 +6286,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 8058-2026</t>
+          <t>A 30701-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6295,10 +6300,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46063</v>
+        <v>44763</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6354,7 +6359,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 33118-2023</t>
+          <t>A 52950-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6368,10 +6373,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45126</v>
+        <v>44875</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6384,7 +6389,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6427,7 +6432,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 33131-2023</t>
+          <t>A 40369-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6441,10 +6446,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45126</v>
+        <v>45555</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6457,7 +6462,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>14.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6500,7 +6505,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15695-2025</t>
+          <t>A 44529-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6514,10 +6519,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45748</v>
+        <v>45189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6530,7 +6535,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6573,7 +6578,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10850-2026</t>
+          <t>A 55733-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6587,10 +6592,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46078</v>
+        <v>45232</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6603,7 +6608,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6646,7 +6651,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45578-2024</t>
+          <t>A 52852-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6660,10 +6665,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45578</v>
+        <v>45610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6676,7 +6681,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6719,7 +6724,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13325-2022</t>
+          <t>A 25884-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6733,10 +6738,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44645</v>
+        <v>45085</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6749,7 +6754,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6792,7 +6797,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 33569-2025</t>
+          <t>A 50603-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6806,10 +6811,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45841</v>
+        <v>45600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6822,7 +6827,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6865,7 +6870,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 33586-2025</t>
+          <t>A 20476-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6879,10 +6884,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45841</v>
+        <v>45057</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6938,7 +6943,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 33580-2025</t>
+          <t>A 50401-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6952,10 +6957,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45841</v>
+        <v>44459</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6968,7 +6973,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7011,7 +7016,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26277-2025</t>
+          <t>A 50601-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7025,10 +7030,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45805</v>
+        <v>45600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7041,7 +7046,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7084,7 +7089,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33536-2025</t>
+          <t>A 56024-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7098,10 +7103,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45841</v>
+        <v>45240</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7114,7 +7119,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.3</v>
+        <v>3.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7157,7 +7162,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14440-2026</t>
+          <t>A 41991-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7171,10 +7176,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46100</v>
+        <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7187,7 +7192,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7230,7 +7235,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14456-2026</t>
+          <t>A 3187-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7244,10 +7249,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46100</v>
+        <v>45316</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7259,8 +7264,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7303,7 +7313,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14465-2026</t>
+          <t>A 29308-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7317,10 +7327,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46100</v>
+        <v>45824</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7333,7 +7343,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7376,7 +7386,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14462-2026</t>
+          <t>A 33559-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7390,10 +7400,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46100</v>
+        <v>45841</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7406,7 +7416,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7449,7 +7459,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59383-2024</t>
+          <t>A 46371-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7463,10 +7473,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45638</v>
+        <v>44848</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7484,7 +7494,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7527,7 +7537,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14437-2026</t>
+          <t>A 59383-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7541,10 +7551,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46100</v>
+        <v>45638</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7556,8 +7566,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7600,7 +7615,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10457-2023</t>
+          <t>A 33745-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7614,10 +7629,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44987</v>
+        <v>45133</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7630,7 +7645,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7673,7 +7688,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 16223-2025</t>
+          <t>A 48688-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7687,10 +7702,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45750</v>
+        <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7703,7 +7718,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7746,7 +7761,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 53761-2024</t>
+          <t>A 5326-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7760,10 +7775,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45615</v>
+        <v>45331</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7776,7 +7791,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7819,7 +7834,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16989-2023</t>
+          <t>A 2982-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7833,10 +7848,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45033</v>
+        <v>45678</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7848,13 +7863,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7897,7 +7907,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14833-2026</t>
+          <t>A 60768-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7911,10 +7921,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46103</v>
+        <v>44907</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7927,7 +7937,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7970,7 +7980,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 17525-2025</t>
+          <t>A 29300-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7984,10 +7994,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45757</v>
+        <v>45824</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8000,7 +8010,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8043,7 +8053,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44529-2023</t>
+          <t>A 37311-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8057,10 +8067,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45189</v>
+        <v>45876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8073,7 +8083,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8116,7 +8126,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 44319-2025</t>
+          <t>A 20888-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8130,10 +8140,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45916</v>
+        <v>44701</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8189,7 +8199,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33745-2023</t>
+          <t>A 44319-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8203,10 +8213,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45133</v>
+        <v>45916</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8219,7 +8229,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8262,7 +8272,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 31917-2025</t>
+          <t>A 56196-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8276,10 +8286,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45834</v>
+        <v>45974</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8292,7 +8302,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8335,7 +8345,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29329-2024</t>
+          <t>A 45617-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8349,10 +8359,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45483</v>
+        <v>45579</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8365,7 +8375,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8408,7 +8418,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 29308-2025</t>
+          <t>A 21355-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8422,10 +8432,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45824</v>
+        <v>46142</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8438,7 +8448,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8481,7 +8491,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 2982-2025</t>
+          <t>A 9983-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8495,10 +8505,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45678</v>
+        <v>44621</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8511,7 +8521,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8554,7 +8564,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 20476-2023</t>
+          <t>A 33131-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8568,10 +8578,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45057</v>
+        <v>45126</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8584,7 +8594,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8627,7 +8637,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29300-2025</t>
+          <t>A 31388-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8641,10 +8651,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45824</v>
+        <v>44774</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8657,7 +8667,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8700,7 +8710,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19134-2025</t>
+          <t>A 29195-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8710,14 +8720,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45764</v>
+        <v>45482</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8730,7 +8740,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8773,7 +8783,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50401-2021</t>
+          <t>A 50626-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8787,10 +8797,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44459</v>
+        <v>45945</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8802,8 +8812,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>14</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8846,7 +8861,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11897-2025</t>
+          <t>A 994-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8860,10 +8875,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45728</v>
+        <v>45301</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8876,7 +8891,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8919,7 +8934,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 33559-2025</t>
+          <t>A 50578-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8933,10 +8948,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45841</v>
+        <v>45945</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8949,7 +8964,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8992,7 +9007,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 56196-2025</t>
+          <t>A 21755-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9006,10 +9021,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45974</v>
+        <v>46149</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9022,7 +9037,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9065,7 +9080,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 22560-2023</t>
+          <t>A 50797-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9079,10 +9094,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45071</v>
+        <v>45946</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9095,7 +9110,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9138,7 +9153,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48688-2025</t>
+          <t>A 21819-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9152,10 +9167,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45936</v>
+        <v>46150</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9168,7 +9183,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9211,7 +9226,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 37311-2025</t>
+          <t>A 21826-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9225,10 +9240,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45876</v>
+        <v>46150</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9241,7 +9256,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9284,7 +9299,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 50034-2022</t>
+          <t>A 21828-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9298,10 +9313,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44865</v>
+        <v>46150</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9314,7 +9329,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9357,7 +9372,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21355-2026</t>
+          <t>A 21839-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9371,10 +9386,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9387,7 +9402,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9430,7 +9445,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 12945-2024</t>
+          <t>A 21833-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9444,10 +9459,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45385</v>
+        <v>46150</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9460,7 +9475,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.1</v>
+        <v>3.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9503,7 +9518,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 21819-2026</t>
+          <t>A 54126-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9517,10 +9532,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46150</v>
+        <v>45964</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9533,7 +9548,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9576,7 +9591,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21833-2026</t>
+          <t>A 10457-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9590,10 +9605,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46150</v>
+        <v>44987</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9606,7 +9621,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9649,7 +9664,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 994-2024</t>
+          <t>A 50034-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9663,10 +9678,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45301</v>
+        <v>44865</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9679,7 +9694,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9722,7 +9737,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21839-2026</t>
+          <t>A 55830-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9736,10 +9751,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46150</v>
+        <v>45972</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9752,7 +9767,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9795,7 +9810,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21755-2026</t>
+          <t>A 57768-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9809,10 +9824,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46149</v>
+        <v>44892</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9825,7 +9840,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9868,7 +9883,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21826-2026</t>
+          <t>A 58226-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9882,10 +9897,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46150</v>
+        <v>45985</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9898,7 +9913,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9941,7 +9956,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21828-2026</t>
+          <t>A 22321-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9955,10 +9970,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9971,7 +9986,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10014,7 +10029,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 3187-2024</t>
+          <t>A 23027-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10028,10 +10043,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45316</v>
+        <v>46161</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10043,13 +10058,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10092,7 +10102,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 22321-2026</t>
+          <t>A 16363-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10106,10 +10116,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46154</v>
+        <v>45407</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10122,7 +10132,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10165,7 +10175,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 39001-2024</t>
+          <t>A 15704-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10179,10 +10189,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45548</v>
+        <v>45748</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10195,7 +10205,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10238,7 +10248,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 38983-2024</t>
+          <t>A 72625-2021</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10252,10 +10262,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45548</v>
+        <v>44546</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10268,7 +10278,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10311,7 +10321,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 23027-2026</t>
+          <t>A 19134-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10321,14 +10331,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46161</v>
+        <v>45764</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10341,7 +10351,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10384,7 +10394,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 13109-2023</t>
+          <t>A 33118-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10398,10 +10408,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45002</v>
+        <v>45126</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10414,7 +10424,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10457,7 +10467,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28586-2025</t>
+          <t>A 38988-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10471,10 +10481,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45819</v>
+        <v>45548</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10487,7 +10497,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10530,7 +10540,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 56130-2022</t>
+          <t>A 60220-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10540,14 +10550,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44886</v>
+        <v>44903</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10560,7 +10570,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10603,7 +10613,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 33747-2023</t>
+          <t>A 11891-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10617,10 +10627,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45133</v>
+        <v>45728</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10633,7 +10643,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10676,7 +10686,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21333-2024</t>
+          <t>A 15559-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10690,10 +10700,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45440</v>
+        <v>45019</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10706,7 +10716,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10749,7 +10759,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 50626-2025</t>
+          <t>A 57663-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10763,10 +10773,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45945</v>
+        <v>45981</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10778,13 +10788,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10827,7 +10832,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 29195-2024</t>
+          <t>A 54007-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10841,10 +10846,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45482</v>
+        <v>45615</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10857,7 +10862,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10900,7 +10905,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56602-2023</t>
+          <t>A 61898-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10914,10 +10919,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45243</v>
+        <v>46003</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10930,7 +10935,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10973,7 +10978,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 50578-2025</t>
+          <t>A 33747-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10987,10 +10992,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45945</v>
+        <v>45133</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11003,7 +11008,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11046,7 +11051,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 50797-2025</t>
+          <t>A 28586-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11060,10 +11065,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45946</v>
+        <v>45819</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11076,7 +11081,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11119,7 +11124,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 7136-2022</t>
+          <t>A 44523-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11133,10 +11138,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44603</v>
+        <v>45189</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11149,7 +11154,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11192,7 +11197,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26409-2026</t>
+          <t>A 880-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11206,10 +11211,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46182</v>
+        <v>46029</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11222,7 +11227,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11265,7 +11270,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 50601-2024</t>
+          <t>A 1945-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11279,10 +11284,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45600</v>
+        <v>46035</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11295,7 +11300,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11338,7 +11343,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 67875-2021</t>
+          <t>A 1608-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11352,10 +11357,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44525</v>
+        <v>46034</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11368,7 +11373,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>15.5</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11411,7 +11416,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 16363-2024</t>
+          <t>A 2322-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11425,10 +11430,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45407</v>
+        <v>46036</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11441,7 +11446,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11484,7 +11489,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 41072-2023</t>
+          <t>A 2324-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11498,10 +11503,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45170</v>
+        <v>46036</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11514,7 +11519,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11557,7 +11562,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 10470-2024</t>
+          <t>A 8047-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11567,14 +11572,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45366</v>
+        <v>45351</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11587,7 +11592,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11630,7 +11635,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 40369-2024</t>
+          <t>A 13109-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11644,10 +11649,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45555</v>
+        <v>45002</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11660,7 +11665,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>14.5</v>
+        <v>2.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11703,7 +11708,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 54126-2025</t>
+          <t>A 6379-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11717,10 +11722,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45964</v>
+        <v>46055</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11733,7 +11738,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11776,7 +11781,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 28319-2026</t>
+          <t>A 21333-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11790,10 +11795,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46196</v>
+        <v>45440</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11806,7 +11811,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11849,7 +11854,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22693-2026</t>
+          <t>A 7545-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11863,10 +11868,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46156</v>
+        <v>46059</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11879,7 +11884,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11922,7 +11927,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 55830-2025</t>
+          <t>A 7466-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11936,10 +11941,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45972</v>
+        <v>46059</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11951,8 +11956,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11995,7 +12005,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 52262-2023</t>
+          <t>A 8051-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12009,10 +12019,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45217</v>
+        <v>46063</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12025,7 +12035,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12068,7 +12078,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 38818-2024</t>
+          <t>A 8058-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12082,10 +12092,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45547</v>
+        <v>46063</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12098,7 +12108,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12141,7 +12151,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 8047-2024</t>
+          <t>A 8060-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12151,14 +12161,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45351</v>
+        <v>46063</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12171,7 +12181,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12214,7 +12224,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 25884-2023</t>
+          <t>A 29192-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12228,10 +12238,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45085</v>
+        <v>45482</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12244,7 +12254,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12287,7 +12297,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 54007-2024</t>
+          <t>A 67875-2021</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12301,10 +12311,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45615</v>
+        <v>44525</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12317,7 +12327,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>15.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12360,7 +12370,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 20888-2022</t>
+          <t>A 26409-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12374,10 +12384,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44701</v>
+        <v>46182</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12390,7 +12400,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12433,7 +12443,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 29587-2026</t>
+          <t>A 10850-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12447,10 +12457,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46204</v>
+        <v>46078</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12463,7 +12473,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12506,7 +12516,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 58226-2025</t>
+          <t>A 38983-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12520,10 +12530,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45985</v>
+        <v>45548</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12536,7 +12546,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12579,7 +12589,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 54792-2023</t>
+          <t>A 29327-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12593,10 +12603,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45236</v>
+        <v>45483</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12609,7 +12619,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12652,7 +12662,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 11891-2025</t>
+          <t>A 14465-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12666,10 +12676,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45728</v>
+        <v>46100</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12682,7 +12692,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12725,7 +12735,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 3391-2024</t>
+          <t>A 14440-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12739,10 +12749,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45318</v>
+        <v>46100</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12754,13 +12764,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12803,7 +12808,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 21061-2022</t>
+          <t>A 14456-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12817,10 +12822,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44704</v>
+        <v>46100</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12833,7 +12838,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12876,7 +12881,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 55733-2023</t>
+          <t>A 28319-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12890,10 +12895,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45232</v>
+        <v>46196</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12949,7 +12954,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 35205-2026</t>
+          <t>A 14462-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12963,10 +12968,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46260</v>
+        <v>46100</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12979,7 +12984,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13022,7 +13027,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 57663-2025</t>
+          <t>A 22693-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13036,10 +13041,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45981</v>
+        <v>46156</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13052,7 +13057,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13095,7 +13100,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 989-2024</t>
+          <t>A 56602-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13109,10 +13114,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45301</v>
+        <v>45243</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13125,7 +13130,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13168,7 +13173,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 35946-2026</t>
+          <t>A 41072-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13182,10 +13187,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46266</v>
+        <v>45170</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13198,7 +13203,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13241,7 +13246,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 61898-2025</t>
+          <t>A 14437-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13255,10 +13260,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46003</v>
+        <v>46100</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13271,7 +13276,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13314,7 +13319,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 31837-2026</t>
+          <t>A 3391-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13328,10 +13333,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46230</v>
+        <v>45318</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13343,8 +13348,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13387,7 +13397,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 29192-2024</t>
+          <t>A 20968-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13401,10 +13411,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45482</v>
+        <v>45061</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13417,7 +13427,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13460,7 +13470,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 57768-2022</t>
+          <t>A 22560-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13474,10 +13484,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44892</v>
+        <v>45071</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13490,7 +13500,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13533,7 +13543,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 37822-2026</t>
+          <t>A 29587-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13547,10 +13557,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46279</v>
+        <v>46204</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13563,7 +13573,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13606,7 +13616,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 880-2026</t>
+          <t>A 54792-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13620,10 +13630,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46029</v>
+        <v>45236</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13636,7 +13646,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13679,7 +13689,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37058-2026</t>
+          <t>A 14833-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13693,10 +13703,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46273</v>
+        <v>46103</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13709,7 +13719,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13752,7 +13762,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 15559-2023</t>
+          <t>A 45578-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13766,10 +13776,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45019</v>
+        <v>45578</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13782,7 +13792,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13825,7 +13835,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 1608-2026</t>
+          <t>A 31917-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13839,10 +13849,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46034</v>
+        <v>45834</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13855,7 +13865,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13898,7 +13908,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 38350-2026</t>
+          <t>A 61249-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13912,10 +13922,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46282</v>
+        <v>45645</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13927,13 +13937,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13976,7 +13981,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 9983-2022</t>
+          <t>A 38818-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13990,10 +13995,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44621</v>
+        <v>45547</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14006,7 +14011,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14049,7 +14054,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 20968-2023</t>
+          <t>A 45632-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14063,10 +14068,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45061</v>
+        <v>45579</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14078,8 +14083,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>5.1</v>
+        <v>9.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14122,7 +14132,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 1945-2026</t>
+          <t>A 7136-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14136,10 +14146,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46035</v>
+        <v>44603</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14152,7 +14162,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14195,7 +14205,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 2322-2026</t>
+          <t>A 24991-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14209,10 +14219,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46036</v>
+        <v>45085</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14225,7 +14235,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14268,7 +14278,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 2324-2026</t>
+          <t>A 989-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14282,10 +14292,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46036</v>
+        <v>45301</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14298,7 +14308,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14341,7 +14351,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 60220-2022</t>
+          <t>A 61250-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14355,10 +14365,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44903</v>
+        <v>45645</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14371,7 +14381,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>8.300000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14414,7 +14424,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 6379-2026</t>
+          <t>A 13325-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14428,10 +14438,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46055</v>
+        <v>44645</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14444,7 +14454,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14487,7 +14497,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 45617-2024</t>
+          <t>A 35205-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14501,10 +14511,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45579</v>
+        <v>46260</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14517,7 +14527,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14560,7 +14570,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 7466-2026</t>
+          <t>A 56677-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14574,10 +14584,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46059</v>
+        <v>45243</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14589,13 +14599,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14638,7 +14643,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 7545-2026</t>
+          <t>A 56130-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14648,14 +14653,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46059</v>
+        <v>44886</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14668,7 +14673,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14711,7 +14716,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 61252-2024</t>
+          <t>A 21061-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14725,10 +14730,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45645</v>
+        <v>44704</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14741,7 +14746,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14784,7 +14789,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 56024-2023</t>
+          <t>A 54374-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14798,10 +14803,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45240</v>
+        <v>44879</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14814,7 +14819,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14857,7 +14862,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 5326-2024</t>
+          <t>A 35946-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14871,10 +14876,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45331</v>
+        <v>46266</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14887,7 +14892,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14930,7 +14935,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 56677-2023</t>
+          <t>A 15695-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14944,10 +14949,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45243</v>
+        <v>45748</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14960,7 +14965,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15003,7 +15008,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 60768-2022</t>
+          <t>A 49551-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15017,10 +15022,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44907</v>
+        <v>45596</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15033,7 +15038,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15076,7 +15081,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 52950-2022</t>
+          <t>A 46532-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15090,10 +15095,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44875</v>
+        <v>45582</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15106,7 +15111,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15149,7 +15154,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 52852-2024</t>
+          <t>A 31837-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15163,10 +15168,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45610</v>
+        <v>46230</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15179,7 +15184,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15222,7 +15227,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 15704-2025</t>
+          <t>A 37822-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15236,10 +15241,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45748</v>
+        <v>46279</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15252,7 +15257,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15295,7 +15300,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 61626-2024</t>
+          <t>A 11931-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15309,10 +15314,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45646</v>
+        <v>45728</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15325,7 +15330,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>7.3</v>
+        <v>1.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15368,7 +15373,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 3178-2024</t>
+          <t>A 14087-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15382,10 +15387,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45316</v>
+        <v>45739</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15397,13 +15402,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>8.6</v>
+        <v>1.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15446,7 +15446,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 61249-2024</t>
+          <t>A 9695-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15460,10 +15460,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45645</v>
+        <v>45716</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15519,7 +15519,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 38988-2024</t>
+          <t>A 14079-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15533,10 +15533,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45548</v>
+        <v>45739</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15592,7 +15592,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 45632-2024</t>
+          <t>A 38350-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15606,10 +15606,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45579</v>
+        <v>46282</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15670,7 +15670,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 50603-2024</t>
+          <t>A 38537-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15684,10 +15684,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45600</v>
+        <v>46283</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15699,8 +15699,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.4</v>
+        <v>5.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15743,7 +15748,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 61250-2024</t>
+          <t>A 37058-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15757,10 +15762,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45645</v>
+        <v>46273</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15773,7 +15778,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15816,7 +15821,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 24991-2023</t>
+          <t>A 49554-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15830,10 +15835,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45085</v>
+        <v>45596</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15846,7 +15851,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15889,7 +15894,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 46532-2024</t>
+          <t>A 26233-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15903,10 +15908,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45582</v>
+        <v>45805</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15918,8 +15923,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15962,7 +15972,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 49551-2024</t>
+          <t>A 26270-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15976,10 +15986,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45596</v>
+        <v>45805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15992,7 +16002,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16035,7 +16045,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 9695-2025</t>
+          <t>A 15552-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16049,10 +16059,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45716</v>
+        <v>45018</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16065,7 +16075,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16108,7 +16118,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 14079-2025</t>
+          <t>A 13890-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16122,10 +16132,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45739</v>
+        <v>44649</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16138,7 +16148,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16181,7 +16191,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 11931-2025</t>
+          <t>A 33569-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16195,10 +16205,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45728</v>
+        <v>45841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16211,7 +16221,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16254,7 +16264,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 14087-2025</t>
+          <t>A 33586-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16268,10 +16278,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45739</v>
+        <v>45841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16284,7 +16294,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16327,7 +16337,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 49554-2024</t>
+          <t>A 33536-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16341,10 +16351,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45596</v>
+        <v>45841</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16357,7 +16367,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16400,7 +16410,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 26233-2025</t>
+          <t>A 33580-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16414,10 +16424,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45805</v>
+        <v>45841</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16429,13 +16439,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16478,7 +16483,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 26270-2025</t>
+          <t>A 26277-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16495,7 +16500,7 @@
         <v>45805</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16508,7 +16513,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16551,7 +16556,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 13890-2022</t>
+          <t>A 16223-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16565,10 +16570,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44649</v>
+        <v>45750</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16581,7 +16586,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16624,7 +16629,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 15552-2023</t>
+          <t>A 17525-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16638,10 +16643,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45018</v>
+        <v>45757</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16654,7 +16659,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16714,7 +16719,7 @@
         <v>45194</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16787,7 +16792,7 @@
         <v>44788</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16860,7 +16865,7 @@
         <v>46036</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45944</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45336</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>46006</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>44588</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44571</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>45713</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>46072</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>45936</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>45133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45404</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45369</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>45458</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>45945</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>46054</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45729</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>46100</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>46100</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>46264</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>44865</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44606</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44848</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44865</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44851</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44494</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45615</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>45316</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>45385</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>45646</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>45217</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45033</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>44885</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>45366</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         <v>45728</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45483</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>45645</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45548</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>44763</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>44875</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>45555</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>45189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45232</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>45610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>45085</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>45600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>45057</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>44459</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>45600</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>45240</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>45316</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45824</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45841</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>44848</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45638</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>45133</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45936</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45331</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>45678</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>44907</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45824</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>44701</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45916</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45974</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45579</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>46142</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44621</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45126</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>44774</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45482</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45945</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>45301</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45945</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>46149</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>45946</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>46150</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>46150</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>46150</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>46150</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>46150</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>45964</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>44987</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44865</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45972</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>44892</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45985</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>46154</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>46161</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45407</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45748</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>44546</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45764</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>45126</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45548</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>44903</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45728</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45019</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45981</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45615</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>46003</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45133</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>45819</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45189</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>46029</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>46035</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>46034</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>46036</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>46036</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>45351</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>45002</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>46055</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>45440</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>46059</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46059</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>46063</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>46063</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>46063</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45482</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>44525</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>46182</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>46078</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45548</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>45483</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>46100</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>46100</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>46100</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>46196</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>46100</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>46156</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45243</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45170</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>46100</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45318</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45061</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45071</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>46204</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45236</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>46103</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>45578</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45834</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45645</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45547</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45579</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44603</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45085</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45301</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45645</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>44645</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46260</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45243</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>44886</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>44704</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44879</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>46266</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45748</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>45596</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>45582</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>46230</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>46279</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45728</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>45739</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>45716</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45739</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>46282</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>46283</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>46273</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45596</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45805</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45018</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>44649</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45841</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45841</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45805</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>45750</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45757</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45194</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44788</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>46036</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE209"/>
+  <dimension ref="A1:AE208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45944</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6043-2024</t>
+          <t>A 62152-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45336</v>
+        <v>46006</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1323,249 +1323,249 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 6043-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>7</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>7</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Grönpyrola
 Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 62152-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46006</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J9" t="n">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 4173-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44588</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 4173-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44588</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>5</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
       <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
         <v/>
@@ -1619,7 +1619,7 @@
         <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44571</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 8291-2023</t>
+          <t>A 48687-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44974</v>
+        <v>45936</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>17.3</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1992,366 +1992,366 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 8291-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 9001-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>45713</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>4</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="Z15">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 9839-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>46072</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 48687-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Backstarr
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
         <v/>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
         <v>45133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 64707-2023</t>
+          <t>A 15667-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45281</v>
+        <v>45404</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2496,25 +2496,20 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>11.9</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2529,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2538,50 +2533,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
-        <v/>
-      </c>
-      <c r="Z19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15667-2024</t>
+          <t>A 64707-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2595,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45404</v>
+        <v>45281</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2610,20 +2601,25 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>11.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2638,7 +2634,7 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2647,39 +2643,43 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>45369</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24514-2024</t>
+          <t>A 50607-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45458</v>
+        <v>45945</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>14.5</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2970,42 +2970,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 50607-2025</t>
+          <t>A 24514-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45945</v>
+        <v>45458</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>14.5</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3075,35 +3075,35 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
         <v>46054</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>45729</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>46100</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>46100</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>46264</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>44865</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44606</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44848</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30731-2022</t>
+          <t>A 50020-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44764</v>
+        <v>44865</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50020-2022</t>
+          <t>A 30731-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44865</v>
+        <v>44764</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4906,7 +4906,7 @@
         <v>44510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44851</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44494</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>45615</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3178-2024</t>
+          <t>A 61626-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45316</v>
+        <v>45646</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5502,13 +5502,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12945-2024</t>
+          <t>A 3178-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45385</v>
+        <v>45316</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5580,8 +5575,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>6.1</v>
+        <v>8.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61626-2024</t>
+          <t>A 52262-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45646</v>
+        <v>45217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.3</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52262-2023</t>
+          <t>A 12945-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45217</v>
+        <v>45385</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5787,7 +5787,7 @@
         <v>45033</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55712-2022</t>
+          <t>A 10470-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44885</v>
+        <v>45366</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5921,7 +5921,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10470-2024</t>
+          <t>A 55712-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45366</v>
+        <v>44885</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
         <v>45728</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45483</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>45645</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45548</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         <v>44763</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>44875</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>45555</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>45189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45232</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52852-2024</t>
+          <t>A 25884-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45610</v>
+        <v>45085</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6724,7 +6724,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25884-2023</t>
+          <t>A 52852-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45085</v>
+        <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6814,7 +6814,7 @@
         <v>45600</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>45057</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 50401-2021</t>
+          <t>A 16223-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44459</v>
+        <v>45750</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7016,7 +7016,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 50601-2024</t>
+          <t>A 56024-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45600</v>
+        <v>45240</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 56024-2023</t>
+          <t>A 50601-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45240</v>
+        <v>45600</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7162,7 +7162,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 41991-2022</t>
+          <t>A 17525-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44830</v>
+        <v>45757</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7235,7 +7235,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3187-2024</t>
+          <t>A 31917-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7249,10 +7249,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45316</v>
+        <v>45834</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7264,13 +7264,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7330,7 +7325,7 @@
         <v>45824</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7403,7 +7398,7 @@
         <v>45841</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7459,7 +7454,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46371-2022</t>
+          <t>A 41991-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7473,10 +7468,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44848</v>
+        <v>44830</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7488,13 +7483,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7537,7 +7527,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59383-2024</t>
+          <t>A 3187-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7551,10 +7541,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45638</v>
+        <v>45316</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7572,7 +7562,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7615,7 +7605,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33745-2023</t>
+          <t>A 48688-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7629,10 +7619,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45133</v>
+        <v>45936</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7645,7 +7635,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7688,7 +7678,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48688-2025</t>
+          <t>A 46371-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7702,10 +7692,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45936</v>
+        <v>44848</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7717,8 +7707,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7761,7 +7756,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5326-2024</t>
+          <t>A 59383-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7775,10 +7770,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45331</v>
+        <v>45638</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7790,8 +7785,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7834,7 +7834,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2982-2025</t>
+          <t>A 33745-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7848,10 +7848,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45678</v>
+        <v>45133</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7907,7 +7907,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 60768-2022</t>
+          <t>A 44319-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44907</v>
+        <v>45916</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7980,7 +7980,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 29300-2025</t>
+          <t>A 5326-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45824</v>
+        <v>45331</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8053,7 +8053,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37311-2025</t>
+          <t>A 29300-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8067,10 +8067,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45876</v>
+        <v>45824</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8126,7 +8126,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20888-2022</t>
+          <t>A 37311-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8140,10 +8140,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44701</v>
+        <v>45876</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44319-2025</t>
+          <t>A 56196-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45916</v>
+        <v>45974</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>6.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8272,7 +8272,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56196-2025</t>
+          <t>A 2982-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45974</v>
+        <v>45678</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8345,7 +8345,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 45617-2024</t>
+          <t>A 21355-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8359,10 +8359,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45579</v>
+        <v>46142</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8418,7 +8418,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21355-2026</t>
+          <t>A 21755-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8491,7 +8491,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 9983-2022</t>
+          <t>A 60768-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8505,10 +8505,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44621</v>
+        <v>44907</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8564,7 +8564,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33131-2023</t>
+          <t>A 21819-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45126</v>
+        <v>46150</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 31388-2022</t>
+          <t>A 21826-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8651,10 +8651,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44774</v>
+        <v>46150</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8710,7 +8710,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29195-2024</t>
+          <t>A 21828-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45482</v>
+        <v>46150</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8783,7 +8783,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50626-2025</t>
+          <t>A 21839-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8797,10 +8797,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45945</v>
+        <v>46150</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8812,13 +8812,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>14</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8861,7 +8856,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 994-2024</t>
+          <t>A 21833-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8875,10 +8870,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45301</v>
+        <v>46150</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8891,7 +8886,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8934,7 +8929,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50578-2025</t>
+          <t>A 50626-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8951,7 +8946,7 @@
         <v>45945</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8963,8 +8958,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2.8</v>
+        <v>14</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9007,7 +9007,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21755-2026</t>
+          <t>A 20888-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46149</v>
+        <v>44701</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9080,7 +9080,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 50797-2025</t>
+          <t>A 50578-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45946</v>
+        <v>45945</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 21819-2026</t>
+          <t>A 50797-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9167,10 +9167,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46150</v>
+        <v>45946</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9226,7 +9226,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21826-2026</t>
+          <t>A 22321-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21828-2026</t>
+          <t>A 23027-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9313,10 +9313,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46150</v>
+        <v>46161</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21839-2026</t>
+          <t>A 45617-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46150</v>
+        <v>45579</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>5.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9445,7 +9445,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 21833-2026</t>
+          <t>A 54126-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46150</v>
+        <v>45964</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 54126-2025</t>
+          <t>A 55830-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45964</v>
+        <v>45972</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 10457-2023</t>
+          <t>A 9983-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44987</v>
+        <v>44621</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9664,7 +9664,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 50034-2022</t>
+          <t>A 33131-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44865</v>
+        <v>45126</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9737,7 +9737,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 55830-2025</t>
+          <t>A 31388-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45972</v>
+        <v>44774</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 57768-2022</t>
+          <t>A 29195-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9824,10 +9824,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44892</v>
+        <v>45482</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9900,7 +9900,7 @@
         <v>45985</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22321-2026</t>
+          <t>A 994-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46154</v>
+        <v>45301</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10029,7 +10029,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 23027-2026</t>
+          <t>A 28586-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10043,10 +10043,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46161</v>
+        <v>45819</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 16363-2024</t>
+          <t>A 57663-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45407</v>
+        <v>45981</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10175,7 +10175,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 15704-2025</t>
+          <t>A 61898-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45748</v>
+        <v>46003</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10248,7 +10248,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 72625-2021</t>
+          <t>A 10457-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10262,10 +10262,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44546</v>
+        <v>44987</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 19134-2025</t>
+          <t>A 50034-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10331,14 +10331,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45764</v>
+        <v>44865</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10394,7 +10394,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 33118-2023</t>
+          <t>A 57768-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45126</v>
+        <v>44892</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38988-2024</t>
+          <t>A 880-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45548</v>
+        <v>46029</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10540,7 +10540,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60220-2022</t>
+          <t>A 26409-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10554,10 +10554,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44903</v>
+        <v>46182</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10613,7 +10613,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 11891-2025</t>
+          <t>A 1945-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45728</v>
+        <v>46035</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 15559-2023</t>
+          <t>A 1608-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45019</v>
+        <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10759,7 +10759,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 57663-2025</t>
+          <t>A 2322-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10773,10 +10773,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45981</v>
+        <v>46036</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10832,7 +10832,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 54007-2024</t>
+          <t>A 2324-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10846,10 +10846,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45615</v>
+        <v>46036</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10905,7 +10905,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61898-2025</t>
+          <t>A 16363-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10919,10 +10919,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46003</v>
+        <v>45407</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10978,7 +10978,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33747-2023</t>
+          <t>A 15704-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10992,10 +10992,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45133</v>
+        <v>45748</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11051,7 +11051,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 28586-2025</t>
+          <t>A 72625-2021</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11065,10 +11065,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45819</v>
+        <v>44546</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11124,7 +11124,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 44523-2023</t>
+          <t>A 19134-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11134,14 +11134,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45189</v>
+        <v>45764</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11197,7 +11197,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 880-2026</t>
+          <t>A 33118-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46029</v>
+        <v>45126</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11270,7 +11270,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 1945-2026</t>
+          <t>A 6379-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11284,10 +11284,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46035</v>
+        <v>46055</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11343,7 +11343,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1608-2026</t>
+          <t>A 28319-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11357,10 +11357,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46034</v>
+        <v>46196</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 2322-2026</t>
+          <t>A 38988-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11430,10 +11430,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46036</v>
+        <v>45548</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11489,7 +11489,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 2324-2026</t>
+          <t>A 60220-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46036</v>
+        <v>44903</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11562,7 +11562,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 8047-2024</t>
+          <t>A 11891-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11572,14 +11572,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45351</v>
+        <v>45728</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11635,7 +11635,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 13109-2023</t>
+          <t>A 7545-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11649,10 +11649,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45002</v>
+        <v>46059</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 6379-2026</t>
+          <t>A 7466-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11722,10 +11722,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11737,8 +11737,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11781,7 +11786,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 21333-2024</t>
+          <t>A 15559-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11795,10 +11800,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45440</v>
+        <v>45019</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11811,7 +11816,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11854,7 +11859,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 7545-2026</t>
+          <t>A 8051-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11868,10 +11873,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11884,7 +11889,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11927,7 +11932,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 7466-2026</t>
+          <t>A 8058-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11941,10 +11946,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11956,13 +11961,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>6.4</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12005,7 +12005,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 8051-2026</t>
+          <t>A 8060-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12022,7 +12022,7 @@
         <v>46063</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 8058-2026</t>
+          <t>A 54007-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12092,10 +12092,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46063</v>
+        <v>45615</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12151,7 +12151,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 8060-2026</t>
+          <t>A 22693-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12165,10 +12165,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46063</v>
+        <v>46156</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12224,7 +12224,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 29192-2024</t>
+          <t>A 33747-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45482</v>
+        <v>45133</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12297,7 +12297,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 67875-2021</t>
+          <t>A 10850-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12311,10 +12311,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44525</v>
+        <v>46078</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>15.5</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12370,7 +12370,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 26409-2026</t>
+          <t>A 44523-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12384,10 +12384,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46182</v>
+        <v>45189</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12443,7 +12443,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 10850-2026</t>
+          <t>A 29587-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12457,10 +12457,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46078</v>
+        <v>46204</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12516,7 +12516,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 38983-2024</t>
+          <t>A 14465-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12530,10 +12530,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45548</v>
+        <v>46100</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12589,7 +12589,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 29327-2024</t>
+          <t>A 14440-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12603,10 +12603,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45483</v>
+        <v>46100</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12662,7 +12662,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 14465-2026</t>
+          <t>A 14456-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12679,7 +12679,7 @@
         <v>46100</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12735,7 +12735,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14440-2026</t>
+          <t>A 14462-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12752,7 +12752,7 @@
         <v>46100</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12808,7 +12808,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 14456-2026</t>
+          <t>A 14437-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12825,7 +12825,7 @@
         <v>46100</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12881,7 +12881,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 28319-2026</t>
+          <t>A 8047-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12891,14 +12891,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46196</v>
+        <v>45351</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12954,7 +12954,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 14462-2026</t>
+          <t>A 13109-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12968,10 +12968,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46100</v>
+        <v>45002</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13027,7 +13027,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22693-2026</t>
+          <t>A 21333-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13041,10 +13041,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46156</v>
+        <v>45440</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 56602-2023</t>
+          <t>A 29192-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13114,10 +13114,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45243</v>
+        <v>45482</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13173,7 +13173,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 41072-2023</t>
+          <t>A 67875-2021</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45170</v>
+        <v>44525</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13246,7 +13246,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 14437-2026</t>
+          <t>A 14833-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13260,10 +13260,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46100</v>
+        <v>46103</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13319,7 +13319,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 3391-2024</t>
+          <t>A 38983-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45318</v>
+        <v>45548</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13348,13 +13348,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13397,7 +13392,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 20968-2023</t>
+          <t>A 29327-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13411,10 +13406,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45061</v>
+        <v>45483</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13427,7 +13422,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13470,7 +13465,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 22560-2023</t>
+          <t>A 56602-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13484,10 +13479,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45071</v>
+        <v>45243</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13500,7 +13495,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13543,7 +13538,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 29587-2026</t>
+          <t>A 41072-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13557,10 +13552,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46204</v>
+        <v>45170</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13573,7 +13568,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13616,7 +13611,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 54792-2023</t>
+          <t>A 35205-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13630,10 +13625,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45236</v>
+        <v>46260</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13646,7 +13641,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5.9</v>
+        <v>3.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13689,7 +13684,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 14833-2026</t>
+          <t>A 3391-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13703,10 +13698,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46103</v>
+        <v>45318</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13718,8 +13713,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13762,7 +13762,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 45578-2024</t>
+          <t>A 20968-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13776,10 +13776,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45578</v>
+        <v>45061</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13835,7 +13835,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 31917-2025</t>
+          <t>A 22560-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13849,10 +13849,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45834</v>
+        <v>45071</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13908,7 +13908,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 61249-2024</t>
+          <t>A 35946-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13922,10 +13922,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45645</v>
+        <v>46266</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 38818-2024</t>
+          <t>A 54792-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13995,10 +13995,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45547</v>
+        <v>45236</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14054,7 +14054,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 45632-2024</t>
+          <t>A 45578-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14068,10 +14068,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45579</v>
+        <v>45578</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14083,13 +14083,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>9.5</v>
+        <v>1.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14132,7 +14127,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 7136-2022</t>
+          <t>A 31837-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14146,10 +14141,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44603</v>
+        <v>46230</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14162,7 +14157,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14205,7 +14200,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 24991-2023</t>
+          <t>A 61249-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14219,10 +14214,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45085</v>
+        <v>45645</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14235,7 +14230,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14278,7 +14273,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 989-2024</t>
+          <t>A 37822-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14292,10 +14287,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45301</v>
+        <v>46279</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14308,7 +14303,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14351,7 +14346,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 61250-2024</t>
+          <t>A 38818-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14365,10 +14360,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45645</v>
+        <v>45547</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14381,7 +14376,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14424,7 +14419,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 13325-2022</t>
+          <t>A 45632-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14438,10 +14433,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44645</v>
+        <v>45579</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14453,8 +14448,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>3.7</v>
+        <v>9.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14497,7 +14497,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 35205-2026</t>
+          <t>A 7136-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14511,10 +14511,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46260</v>
+        <v>44603</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14570,7 +14570,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 56677-2023</t>
+          <t>A 38350-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14584,10 +14584,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45243</v>
+        <v>46282</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14599,8 +14599,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14643,7 +14648,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 56130-2022</t>
+          <t>A 38537-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14653,14 +14658,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44886</v>
+        <v>46283</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14672,8 +14677,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14716,7 +14726,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 21061-2022</t>
+          <t>A 24991-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14730,10 +14740,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44704</v>
+        <v>45085</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14746,7 +14756,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14789,7 +14799,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 54374-2022</t>
+          <t>A 37058-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14803,10 +14813,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44879</v>
+        <v>46273</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14819,7 +14829,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14862,7 +14872,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35946-2026</t>
+          <t>A 989-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14876,10 +14886,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46266</v>
+        <v>45301</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14892,7 +14902,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14935,7 +14945,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 15695-2025</t>
+          <t>A 61250-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14949,10 +14959,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45748</v>
+        <v>45645</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14965,7 +14975,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15008,7 +15018,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 49551-2024</t>
+          <t>A 13325-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15022,10 +15032,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45596</v>
+        <v>44645</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15038,7 +15048,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15081,7 +15091,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 46532-2024</t>
+          <t>A 56677-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15095,10 +15105,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45582</v>
+        <v>45243</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15111,7 +15121,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15154,7 +15164,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 31837-2026</t>
+          <t>A 56130-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15164,14 +15174,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46230</v>
+        <v>44886</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15184,7 +15194,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15227,7 +15237,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37822-2026</t>
+          <t>A 21061-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15241,10 +15251,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46279</v>
+        <v>44704</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15257,7 +15267,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15300,7 +15310,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 11931-2025</t>
+          <t>A 54374-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15314,10 +15324,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45728</v>
+        <v>44879</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15330,7 +15340,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15373,7 +15383,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 14087-2025</t>
+          <t>A 15695-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15387,10 +15397,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45739</v>
+        <v>45748</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15403,7 +15413,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15446,7 +15456,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 9695-2025</t>
+          <t>A 49551-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15460,10 +15470,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45716</v>
+        <v>45596</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15476,7 +15486,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15519,7 +15529,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 14079-2025</t>
+          <t>A 46532-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15533,10 +15543,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45739</v>
+        <v>45582</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15549,7 +15559,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15592,7 +15602,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 38350-2026</t>
+          <t>A 11931-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15606,10 +15616,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46282</v>
+        <v>45728</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15621,13 +15631,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15670,7 +15675,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 38537-2026</t>
+          <t>A 14087-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15684,10 +15689,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46283</v>
+        <v>45739</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15699,13 +15704,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15748,7 +15748,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 37058-2026</t>
+          <t>A 9695-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46273</v>
+        <v>45716</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 49554-2024</t>
+          <t>A 14079-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15835,10 +15835,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45596</v>
+        <v>45739</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15894,7 +15894,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 26233-2025</t>
+          <t>A 49554-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15908,10 +15908,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45805</v>
+        <v>45596</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15923,13 +15923,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15972,7 +15967,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 26270-2025</t>
+          <t>A 26233-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15989,7 +15984,7 @@
         <v>45805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16001,8 +15996,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16045,7 +16045,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 15552-2023</t>
+          <t>A 26270-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16059,10 +16059,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45018</v>
+        <v>45805</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16118,7 +16118,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 13890-2022</t>
+          <t>A 15552-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16132,10 +16132,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44649</v>
+        <v>45018</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16191,7 +16191,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 33569-2025</t>
+          <t>A 13890-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16205,10 +16205,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45841</v>
+        <v>44649</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16264,7 +16264,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 33586-2025</t>
+          <t>A 33569-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16281,7 +16281,7 @@
         <v>45841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 33536-2025</t>
+          <t>A 33586-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16354,7 +16354,7 @@
         <v>45841</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16410,7 +16410,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 33580-2025</t>
+          <t>A 33536-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16427,7 +16427,7 @@
         <v>45841</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16483,7 +16483,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 26277-2025</t>
+          <t>A 33580-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16497,10 +16497,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45805</v>
+        <v>45841</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 16223-2025</t>
+          <t>A 26277-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16570,10 +16570,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45750</v>
+        <v>45805</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>7.2</v>
+        <v>1.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16629,24 +16629,24 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 17525-2025</t>
+          <t>S 3201-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45757</v>
+        <v>45194</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16702,7 +16702,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>S 3201-2023</t>
+          <t>S 4468-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16712,87 +16712,87 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>44788</v>
+      </c>
+      <c r="E207" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="n">
+        <v>0</v>
+      </c>
+      <c r="V207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>S 85-2026</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D207" s="1" t="n">
-        <v>45194</v>
-      </c>
-      <c r="E207" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I207" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" t="n">
-        <v>0</v>
-      </c>
-      <c r="L207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M207" t="n">
-        <v>0</v>
-      </c>
-      <c r="N207" t="n">
-        <v>0</v>
-      </c>
-      <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="n">
-        <v>0</v>
-      </c>
-      <c r="T207" t="n">
-        <v>0</v>
-      </c>
-      <c r="U207" t="n">
-        <v>0</v>
-      </c>
-      <c r="V207" s="2" t="inlineStr"/>
-    </row>
-    <row r="208" ht="15" customHeight="1">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>S 4468-2022</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
-      </c>
       <c r="D208" s="1" t="n">
-        <v>44788</v>
+        <v>46036</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16844,79 +16844,6 @@
         <v>0</v>
       </c>
       <c r="V208" s="2" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>S 85-2026</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D209" s="1" t="n">
-        <v>46036</v>
-      </c>
-      <c r="E209" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I209" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J209" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" t="n">
-        <v>0</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0</v>
-      </c>
-      <c r="M209" t="n">
-        <v>0</v>
-      </c>
-      <c r="N209" t="n">
-        <v>0</v>
-      </c>
-      <c r="O209" t="n">
-        <v>0</v>
-      </c>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="n">
-        <v>0</v>
-      </c>
-      <c r="T209" t="n">
-        <v>0</v>
-      </c>
-      <c r="U209" t="n">
-        <v>0</v>
-      </c>
-      <c r="V209" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE208"/>
+  <dimension ref="A1:AE209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50432-2025</t>
+          <t>A 4173-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45944</v>
+        <v>44588</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1110,492 +1110,492 @@
         <v>3</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 50432-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Älg
 Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50432-2025 artfynd.xlsx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50432-2025 karta.png", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50432-2025 georefererad karta.tif", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50432-2025 FSC-klagomål.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50432-2025 FSC-klagomål mail.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50432-2025 tillsynsbegäran.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50432-2025 tillsynsbegäran mail.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50432-2025 prioriterade fågelarter.docx", "A 50432-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 50437-2025</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>45944</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>3.6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>3</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>5</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Älg
 Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50437-2025 artfynd.xlsx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50437-2025 karta.png", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50437-2025 georefererad karta.tif", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50437-2025 FSC-klagomål.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50437-2025 FSC-klagomål mail.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50437-2025 tillsynsbegäran.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50437-2025 tillsynsbegäran mail.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50437-2025 prioriterade fågelarter.docx", "A 50437-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 6043-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönpyrola
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 62152-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>46006</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>3.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U10" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 6043-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45336</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönpyrola
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 4173-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44588</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>5</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
         <v/>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44571</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 48687-2025</t>
+          <t>A 9001-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45936</v>
+        <v>45713</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1983,382 +1983,382 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9839-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 8291-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 48687-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Blåsippa</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 8291-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9001-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45713</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9839-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33772-2023</t>
+          <t>A 15667-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45133</v>
+        <v>45404</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2424,50 +2424,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15667-2024</t>
+          <t>A 12779-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2477,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45404</v>
+        <v>45733</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,16 +2493,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>10.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2521,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2533,46 +2529,50 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12779-2025 artfynd.xlsx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12779-2025 karta.png", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12779-2025 georefererad karta.tif", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12779-2025 FSC-klagomål.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12779-2025 FSC-klagomål mail.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12779-2025 tillsynsbegäran.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12779-2025 tillsynsbegäran mail.docx", "A 12779-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12779-2025 prioriterade fågelarter.docx", "A 12779-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 64707-2023</t>
+          <t>A 10764-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45281</v>
+        <v>45369</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2601,13 +2601,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>11.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2619,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2631,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2647,46 +2642,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 53485-2023</t>
+          <t>A 24514-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2700,10 +2691,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45230</v>
+        <v>45458</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2716,7 +2707,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2756,46 +2747,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10764-2024</t>
+          <t>A 53485-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2809,10 +2796,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45369</v>
+        <v>45230</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2825,7 +2812,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>8.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2861,39 +2848,43 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
         <v/>
       </c>
     </row>
@@ -2917,7 +2908,7 @@
         <v>45945</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +2996,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24514-2024</t>
+          <t>A 33772-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3019,10 +3010,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45458</v>
+        <v>45133</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3035,7 +3026,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3044,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3059,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3071,46 +3062,50 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 6128-2026</t>
+          <t>A 64707-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3124,10 +3119,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46054</v>
+        <v>45281</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3139,8 +3134,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3152,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3164,10 +3164,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3180,35 +3180,39 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
     </row>
@@ -3232,7 +3236,7 @@
         <v>45729</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3341,7 +3345,7 @@
         <v>46100</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3446,7 +3450,7 @@
         <v>46100</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3534,7 +3538,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35813-2026</t>
+          <t>A 6128-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3548,10 +3552,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46264</v>
+        <v>46054</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3564,7 +3568,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>23.7</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3604,42 +3608,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12779-2025</t>
+          <t>A 35813-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3653,10 +3657,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45733</v>
+        <v>46264</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3669,7 +3673,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.1</v>
+        <v>23.7</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3709,39 +3713,35 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12779-2025 artfynd.xlsx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12779-2025 karta.png", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12779-2025 georefererad karta.tif", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12779-2025 FSC-klagomål.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12779-2025 FSC-klagomål mail.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12779-2025 tillsynsbegäran.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12779-2025 tillsynsbegäran mail.docx", "A 12779-2025")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12779-2025 prioriterade fågelarter.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
         <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>44865</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44606</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44848</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44865</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44764</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44851</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 70164-2021</t>
+          <t>A 53761-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44533</v>
+        <v>45615</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5254,7 +5254,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59917-2021</t>
+          <t>A 16989-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44494</v>
+        <v>45033</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5283,8 +5283,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5327,7 +5332,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4395-2022</t>
+          <t>A 70164-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5341,10 +5346,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44588</v>
+        <v>44533</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5357,7 +5362,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5400,7 +5405,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53761-2024</t>
+          <t>A 44529-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5414,10 +5419,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45615</v>
+        <v>45189</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5430,7 +5435,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5473,7 +5478,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61626-2024</t>
+          <t>A 59917-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5487,10 +5492,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45646</v>
+        <v>44494</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5503,7 +5508,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.3</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5546,7 +5551,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3178-2024</t>
+          <t>A 33745-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5560,10 +5565,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45316</v>
+        <v>45133</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5575,13 +5580,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>8.6</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52262-2023</t>
+          <t>A 4395-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45217</v>
+        <v>44588</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12945-2024</t>
+          <t>A 30701-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45385</v>
+        <v>44763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.1</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16989-2023</t>
+          <t>A 31388-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45033</v>
+        <v>44774</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5799,13 +5799,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5848,7 +5843,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10470-2024</t>
+          <t>A 29329-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5862,10 +5857,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45366</v>
+        <v>45483</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5878,7 +5873,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5921,7 +5916,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55712-2022</t>
+          <t>A 2982-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5935,10 +5930,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44885</v>
+        <v>45678</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5951,7 +5946,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5994,7 +5989,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11897-2025</t>
+          <t>A 17525-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6008,10 +6003,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45728</v>
+        <v>45757</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6024,7 +6019,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6067,7 +6062,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29329-2024</t>
+          <t>A 9695-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6081,10 +6076,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45483</v>
+        <v>45716</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6097,7 +6092,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6140,7 +6135,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 61252-2024</t>
+          <t>A 20476-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6154,10 +6149,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45645</v>
+        <v>45057</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6170,7 +6165,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6213,7 +6208,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39001-2024</t>
+          <t>A 14079-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6227,10 +6222,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45548</v>
+        <v>45739</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6243,7 +6238,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6286,7 +6281,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30701-2022</t>
+          <t>A 19134-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6296,14 +6291,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44763</v>
+        <v>45764</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6316,7 +6311,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6359,7 +6354,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52950-2022</t>
+          <t>A 11897-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6373,10 +6368,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44875</v>
+        <v>45728</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6389,7 +6384,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6432,7 +6427,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40369-2024</t>
+          <t>A 55712-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6446,10 +6441,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45555</v>
+        <v>44885</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6462,7 +6457,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>14.5</v>
+        <v>2.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6505,7 +6500,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44529-2023</t>
+          <t>A 11931-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6519,10 +6514,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45189</v>
+        <v>45728</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6535,7 +6530,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6578,7 +6573,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55733-2023</t>
+          <t>A 14087-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6592,10 +6587,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45232</v>
+        <v>45739</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6608,7 +6603,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6651,7 +6646,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25884-2023</t>
+          <t>A 22560-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6665,10 +6660,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45085</v>
+        <v>45071</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6681,7 +6676,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6724,7 +6719,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52852-2024</t>
+          <t>A 46371-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6738,10 +6733,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45610</v>
+        <v>44848</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6753,8 +6748,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 50603-2024</t>
+          <t>A 54374-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45600</v>
+        <v>44879</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6870,7 +6870,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20476-2023</t>
+          <t>A 50034-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45057</v>
+        <v>44865</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6943,7 +6943,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16223-2025</t>
+          <t>A 12945-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45750</v>
+        <v>45385</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7016,7 +7016,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56024-2023</t>
+          <t>A 49554-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45240</v>
+        <v>45596</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50601-2024</t>
+          <t>A 994-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45600</v>
+        <v>45301</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7162,7 +7162,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17525-2025</t>
+          <t>A 3187-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45757</v>
+        <v>45316</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7191,8 +7191,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7235,7 +7240,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31917-2025</t>
+          <t>A 39001-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7249,10 +7254,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45834</v>
+        <v>45548</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7265,7 +7270,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7308,7 +7313,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 29308-2025</t>
+          <t>A 38983-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7322,10 +7327,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45824</v>
+        <v>45548</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7338,7 +7343,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7381,7 +7386,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33559-2025</t>
+          <t>A 72625-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7395,10 +7400,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45841</v>
+        <v>44546</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7411,7 +7416,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7454,7 +7459,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41991-2022</t>
+          <t>A 13109-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7468,10 +7473,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44830</v>
+        <v>45002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7484,7 +7489,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7527,7 +7532,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3187-2024</t>
+          <t>A 56130-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7537,14 +7542,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45316</v>
+        <v>44886</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7556,13 +7561,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7605,7 +7605,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48688-2025</t>
+          <t>A 33747-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45936</v>
+        <v>45133</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7678,7 +7678,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46371-2022</t>
+          <t>A 29327-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44848</v>
+        <v>45483</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7707,13 +7707,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7756,7 +7751,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 59383-2024</t>
+          <t>A 44319-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7770,10 +7765,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45638</v>
+        <v>45916</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7785,13 +7780,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7834,7 +7824,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33745-2023</t>
+          <t>A 21333-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7848,10 +7838,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45133</v>
+        <v>45440</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7864,7 +7854,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7907,7 +7897,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44319-2025</t>
+          <t>A 41991-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7921,10 +7911,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45916</v>
+        <v>44830</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7937,7 +7927,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7980,7 +7970,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 5326-2024</t>
+          <t>A 44523-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7994,10 +7984,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45331</v>
+        <v>45189</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8010,7 +8000,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8053,7 +8043,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 29300-2025</t>
+          <t>A 29195-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8067,10 +8057,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45824</v>
+        <v>45482</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8083,7 +8073,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8126,7 +8116,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37311-2025</t>
+          <t>A 56602-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8140,10 +8130,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45876</v>
+        <v>45243</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8156,7 +8146,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8199,7 +8189,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 56196-2025</t>
+          <t>A 26233-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8213,10 +8203,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45974</v>
+        <v>45805</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8228,8 +8218,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8272,7 +8267,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 2982-2025</t>
+          <t>A 26270-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8286,10 +8281,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45678</v>
+        <v>45805</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8302,7 +8297,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8345,7 +8340,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21355-2026</t>
+          <t>A 13890-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8359,10 +8354,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46142</v>
+        <v>44649</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8375,7 +8370,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8418,7 +8413,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21755-2026</t>
+          <t>A 7136-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8432,10 +8427,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46149</v>
+        <v>44603</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8448,7 +8443,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8491,7 +8486,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 60768-2022</t>
+          <t>A 15552-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8505,10 +8500,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44907</v>
+        <v>45018</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8521,7 +8516,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8564,7 +8559,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21819-2026</t>
+          <t>A 50601-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8578,10 +8573,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46150</v>
+        <v>45600</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8594,7 +8589,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8637,7 +8632,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21826-2026</t>
+          <t>A 67875-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8651,10 +8646,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46150</v>
+        <v>44525</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8667,7 +8662,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>15.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8710,7 +8705,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21828-2026</t>
+          <t>A 16363-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8724,10 +8719,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46150</v>
+        <v>45407</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8740,7 +8735,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8783,7 +8778,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21839-2026</t>
+          <t>A 33118-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8797,10 +8792,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46150</v>
+        <v>45126</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8813,7 +8808,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8856,7 +8851,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21833-2026</t>
+          <t>A 33131-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8870,10 +8865,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46150</v>
+        <v>45126</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8886,7 +8881,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8946,7 +8941,7 @@
         <v>45945</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9007,7 +9002,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20888-2022</t>
+          <t>A 41072-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9021,10 +9016,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44701</v>
+        <v>45170</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9037,7 +9032,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>7.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9080,7 +9075,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 50578-2025</t>
+          <t>A 10470-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9094,10 +9089,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45945</v>
+        <v>45366</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9110,7 +9105,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9153,7 +9148,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 50797-2025</t>
+          <t>A 50578-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9167,10 +9162,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45946</v>
+        <v>45945</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9183,7 +9178,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9226,7 +9221,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22321-2026</t>
+          <t>A 50797-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9240,10 +9235,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46154</v>
+        <v>45946</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9256,7 +9251,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9299,7 +9294,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23027-2026</t>
+          <t>A 40369-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9313,10 +9308,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46161</v>
+        <v>45555</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9329,7 +9324,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9372,7 +9367,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 45617-2024</t>
+          <t>A 15695-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9386,10 +9381,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45579</v>
+        <v>45748</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9402,7 +9397,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9445,7 +9440,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 54126-2025</t>
+          <t>A 45578-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9459,10 +9454,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45964</v>
+        <v>45578</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9475,7 +9470,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9518,7 +9513,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 55830-2025</t>
+          <t>A 13325-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9532,10 +9527,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45972</v>
+        <v>44645</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9548,7 +9543,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9591,7 +9586,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9983-2022</t>
+          <t>A 54126-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9605,10 +9600,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44621</v>
+        <v>45964</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9621,7 +9616,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9664,7 +9659,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 33131-2023</t>
+          <t>A 52262-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9678,10 +9673,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45126</v>
+        <v>45217</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9694,7 +9689,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9737,7 +9732,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31388-2022</t>
+          <t>A 38818-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9751,10 +9746,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44774</v>
+        <v>45547</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9767,7 +9762,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9810,7 +9805,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 29195-2024</t>
+          <t>A 8047-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9820,14 +9815,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45482</v>
+        <v>45351</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9840,7 +9835,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9883,7 +9878,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 58226-2025</t>
+          <t>A 55830-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9897,10 +9892,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45985</v>
+        <v>45972</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9913,7 +9908,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9956,7 +9951,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 994-2024</t>
+          <t>A 25884-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9970,10 +9965,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45301</v>
+        <v>45085</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9986,7 +9981,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10029,7 +10024,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28586-2025</t>
+          <t>A 54007-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10043,10 +10038,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45819</v>
+        <v>45615</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10059,7 +10054,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>7.1</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10102,7 +10097,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 57663-2025</t>
+          <t>A 20888-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10116,10 +10111,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45981</v>
+        <v>44701</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10175,7 +10170,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61898-2025</t>
+          <t>A 59383-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10189,10 +10184,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46003</v>
+        <v>45638</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10204,8 +10199,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10265,7 +10265,7 @@
         <v>44987</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 50034-2022</t>
+          <t>A 58226-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44865</v>
+        <v>45985</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10394,7 +10394,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 57768-2022</t>
+          <t>A 54792-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44892</v>
+        <v>45236</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>46029</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26409-2026</t>
+          <t>A 57663-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10554,10 +10554,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46182</v>
+        <v>45981</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10613,7 +10613,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1945-2026</t>
+          <t>A 11891-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46035</v>
+        <v>45728</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10703,7 +10703,7 @@
         <v>46034</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 2322-2026</t>
+          <t>A 3391-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10773,10 +10773,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46036</v>
+        <v>45318</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10788,8 +10788,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10832,7 +10837,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 2324-2026</t>
+          <t>A 21061-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10846,10 +10851,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46036</v>
+        <v>44704</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10862,7 +10867,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10905,7 +10910,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 16363-2024</t>
+          <t>A 1945-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10919,10 +10924,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45407</v>
+        <v>46035</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10935,7 +10940,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10978,7 +10983,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15704-2025</t>
+          <t>A 55733-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10992,10 +10997,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45748</v>
+        <v>45232</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11008,7 +11013,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11051,7 +11056,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 72625-2021</t>
+          <t>A 61898-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11065,10 +11070,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44546</v>
+        <v>46003</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11124,7 +11129,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19134-2025</t>
+          <t>A 2322-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11134,14 +11139,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45764</v>
+        <v>46036</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11154,7 +11159,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11197,7 +11202,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 33118-2023</t>
+          <t>A 2324-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11211,10 +11216,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45126</v>
+        <v>46036</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11227,7 +11232,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11270,7 +11275,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 6379-2026</t>
+          <t>A 989-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11284,10 +11289,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46055</v>
+        <v>45301</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11300,7 +11305,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11343,7 +11348,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28319-2026</t>
+          <t>A 6379-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11357,10 +11362,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46196</v>
+        <v>46055</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11373,7 +11378,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11416,7 +11421,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 38988-2024</t>
+          <t>A 38537-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11430,10 +11435,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45548</v>
+        <v>46283</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11445,8 +11450,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11489,7 +11499,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 60220-2022</t>
+          <t>A 7466-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11503,10 +11513,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44903</v>
+        <v>46059</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11518,8 +11528,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>8.300000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11562,7 +11577,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 11891-2025</t>
+          <t>A 7545-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11576,10 +11591,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45728</v>
+        <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11592,7 +11607,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11635,7 +11650,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7545-2026</t>
+          <t>A 8060-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11649,10 +11664,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11665,7 +11680,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11708,7 +11723,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7466-2026</t>
+          <t>A 8051-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11722,10 +11737,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11737,13 +11752,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11786,7 +11796,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 15559-2023</t>
+          <t>A 8058-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11800,10 +11810,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45019</v>
+        <v>46063</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11816,7 +11826,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11859,7 +11869,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 8051-2026</t>
+          <t>A 29192-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11873,10 +11883,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46063</v>
+        <v>45482</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11889,7 +11899,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11932,7 +11942,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8058-2026</t>
+          <t>A 57768-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11946,10 +11956,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46063</v>
+        <v>44892</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11962,7 +11972,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12005,7 +12015,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 8060-2026</t>
+          <t>A 33569-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12019,10 +12029,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46063</v>
+        <v>45841</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12035,7 +12045,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12078,7 +12088,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 54007-2024</t>
+          <t>A 33586-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12092,10 +12102,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45615</v>
+        <v>45841</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12108,7 +12118,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12151,7 +12161,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 22693-2026</t>
+          <t>A 10850-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12165,10 +12175,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46156</v>
+        <v>46078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12181,7 +12191,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12224,7 +12234,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33747-2023</t>
+          <t>A 39457-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12238,10 +12248,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45133</v>
+        <v>46288</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12254,7 +12264,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12297,7 +12307,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 10850-2026</t>
+          <t>A 33580-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12311,10 +12321,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46078</v>
+        <v>45841</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12327,7 +12337,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12370,7 +12380,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 44523-2023</t>
+          <t>A 26277-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12384,10 +12394,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45189</v>
+        <v>45805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12400,7 +12410,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12443,7 +12453,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 29587-2026</t>
+          <t>A 33536-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12457,10 +12467,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46204</v>
+        <v>45841</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12473,7 +12483,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.1</v>
+        <v>6.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12516,7 +12526,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 14465-2026</t>
+          <t>A 15559-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12530,10 +12540,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46100</v>
+        <v>45019</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12546,7 +12556,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12589,7 +12599,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 14440-2026</t>
+          <t>A 9983-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12603,10 +12613,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46100</v>
+        <v>44621</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12619,7 +12629,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12662,7 +12672,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 14456-2026</t>
+          <t>A 14440-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12679,7 +12689,7 @@
         <v>46100</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12692,7 +12702,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12735,7 +12745,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14462-2026</t>
+          <t>A 14456-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12752,7 +12762,7 @@
         <v>46100</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12765,7 +12775,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12808,7 +12818,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 14437-2026</t>
+          <t>A 14465-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12825,7 +12835,7 @@
         <v>46100</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12838,7 +12848,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12881,7 +12891,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8047-2024</t>
+          <t>A 20968-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12891,14 +12901,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45351</v>
+        <v>45061</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12911,7 +12921,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12954,7 +12964,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 13109-2023</t>
+          <t>A 14462-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12968,10 +12978,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45002</v>
+        <v>46100</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12984,7 +12994,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13027,7 +13037,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 21333-2024</t>
+          <t>A 14437-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13041,10 +13051,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45440</v>
+        <v>46100</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13057,7 +13067,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13100,7 +13110,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 29192-2024</t>
+          <t>A 60220-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13114,10 +13124,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45482</v>
+        <v>44903</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13130,7 +13140,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13173,7 +13183,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 67875-2021</t>
+          <t>A 16223-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13187,10 +13197,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44525</v>
+        <v>45750</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13203,7 +13213,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13246,7 +13256,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 14833-2026</t>
+          <t>A 45617-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13260,10 +13270,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46103</v>
+        <v>45579</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13276,7 +13286,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13319,7 +13329,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 38983-2024</t>
+          <t>A 14833-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13333,10 +13343,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45548</v>
+        <v>46103</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13349,7 +13359,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13392,7 +13402,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 29327-2024</t>
+          <t>A 31917-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13406,10 +13416,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45483</v>
+        <v>45834</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13422,7 +13432,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13465,7 +13475,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 56602-2023</t>
+          <t>A 61252-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13479,10 +13489,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45243</v>
+        <v>45645</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13495,7 +13505,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13538,7 +13548,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 41072-2023</t>
+          <t>A 56024-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13552,10 +13562,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45170</v>
+        <v>45240</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13568,7 +13578,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13611,7 +13621,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 35205-2026</t>
+          <t>A 5326-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13625,10 +13635,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46260</v>
+        <v>45331</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13641,7 +13651,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13684,7 +13694,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 3391-2024</t>
+          <t>A 56677-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13698,10 +13708,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45318</v>
+        <v>45243</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13713,13 +13723,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13762,7 +13767,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 20968-2023</t>
+          <t>A 29308-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13776,10 +13781,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45061</v>
+        <v>45824</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13792,7 +13797,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13835,7 +13840,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 22560-2023</t>
+          <t>A 29300-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13849,10 +13854,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45071</v>
+        <v>45824</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13865,7 +13870,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13908,7 +13913,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 35946-2026</t>
+          <t>A 60768-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13922,10 +13927,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46266</v>
+        <v>44907</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13938,7 +13943,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.7</v>
+        <v>10</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13981,7 +13986,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 54792-2023</t>
+          <t>A 52950-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13995,10 +14000,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45236</v>
+        <v>44875</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14011,7 +14016,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14054,7 +14059,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 45578-2024</t>
+          <t>A 33559-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14068,10 +14073,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45578</v>
+        <v>45841</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14127,7 +14132,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 31837-2026</t>
+          <t>A 52852-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14141,10 +14146,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46230</v>
+        <v>45610</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14157,7 +14162,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14200,7 +14205,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 61249-2024</t>
+          <t>A 15704-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14214,10 +14219,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45645</v>
+        <v>45748</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14230,7 +14235,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14273,7 +14278,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 37822-2026</t>
+          <t>A 61626-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14287,10 +14292,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46279</v>
+        <v>45646</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14303,7 +14308,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.7</v>
+        <v>7.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14346,7 +14351,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 38818-2024</t>
+          <t>A 3178-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14360,10 +14365,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45547</v>
+        <v>45316</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14375,8 +14380,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.9</v>
+        <v>8.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14419,7 +14429,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 45632-2024</t>
+          <t>A 61249-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14433,10 +14443,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45579</v>
+        <v>45645</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14448,13 +14458,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14497,7 +14502,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 7136-2022</t>
+          <t>A 56196-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14511,10 +14516,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44603</v>
+        <v>45974</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14527,7 +14532,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14570,7 +14575,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 38350-2026</t>
+          <t>A 38988-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14584,10 +14589,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46282</v>
+        <v>45548</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14599,13 +14604,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14648,7 +14648,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 38537-2026</t>
+          <t>A 48688-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14662,10 +14662,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46283</v>
+        <v>45936</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14677,13 +14677,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14726,7 +14721,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 24991-2023</t>
+          <t>A 45632-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14740,10 +14735,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45085</v>
+        <v>45579</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14755,8 +14750,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14799,7 +14799,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37058-2026</t>
+          <t>A 50603-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14813,10 +14813,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46273</v>
+        <v>45600</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14872,7 +14872,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 989-2024</t>
+          <t>A 37311-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45301</v>
+        <v>45876</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14945,7 +14945,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 61250-2024</t>
+          <t>A 21355-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14959,10 +14959,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45645</v>
+        <v>46142</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 13325-2022</t>
+          <t>A 61250-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15032,10 +15032,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44645</v>
+        <v>45645</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15091,7 +15091,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 56677-2023</t>
+          <t>A 24991-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15105,10 +15105,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45243</v>
+        <v>45085</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15164,7 +15164,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 56130-2022</t>
+          <t>A 21819-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15174,14 +15174,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44886</v>
+        <v>46150</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15237,7 +15237,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 21061-2022</t>
+          <t>A 46532-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44704</v>
+        <v>45582</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15310,7 +15310,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 54374-2022</t>
+          <t>A 21833-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15324,10 +15324,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44879</v>
+        <v>46150</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15383,7 +15383,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 15695-2025</t>
+          <t>A 49551-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15397,10 +15397,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45748</v>
+        <v>45596</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15456,7 +15456,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 49551-2024</t>
+          <t>A 21839-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15470,10 +15470,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45596</v>
+        <v>46150</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15529,7 +15529,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 46532-2024</t>
+          <t>A 21755-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15543,10 +15543,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45582</v>
+        <v>46149</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15602,7 +15602,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 11931-2025</t>
+          <t>A 21826-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15616,10 +15616,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45728</v>
+        <v>46150</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15675,7 +15675,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 14087-2025</t>
+          <t>A 21828-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15689,10 +15689,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45739</v>
+        <v>46150</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15748,7 +15748,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 9695-2025</t>
+          <t>A 22321-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45716</v>
+        <v>46154</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 14079-2025</t>
+          <t>A 23027-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15835,10 +15835,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45739</v>
+        <v>46161</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15894,7 +15894,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 49554-2024</t>
+          <t>A 28586-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15908,10 +15908,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45596</v>
+        <v>45819</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.3</v>
+        <v>7.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15967,7 +15967,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 26233-2025</t>
+          <t>A 26409-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15981,10 +15981,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45805</v>
+        <v>46182</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15996,13 +15996,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16045,7 +16040,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 26270-2025</t>
+          <t>A 28319-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16059,10 +16054,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45805</v>
+        <v>46196</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16075,7 +16070,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16118,7 +16113,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 15552-2023</t>
+          <t>A 22693-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16132,10 +16127,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45018</v>
+        <v>46156</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16148,7 +16143,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16191,7 +16186,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 13890-2022</t>
+          <t>A 29587-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16205,10 +16200,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44649</v>
+        <v>46204</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16221,7 +16216,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16264,7 +16259,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 33569-2025</t>
+          <t>A 35205-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16278,10 +16273,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45841</v>
+        <v>46260</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16294,7 +16289,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16337,7 +16332,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 33586-2025</t>
+          <t>A 35946-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16351,10 +16346,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45841</v>
+        <v>46266</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16367,7 +16362,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16410,7 +16405,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 33536-2025</t>
+          <t>A 31837-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16424,10 +16419,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45841</v>
+        <v>46230</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16440,7 +16435,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16483,7 +16478,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 33580-2025</t>
+          <t>A 37822-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16497,10 +16492,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45841</v>
+        <v>46279</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16513,7 +16508,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16556,7 +16551,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 26277-2025</t>
+          <t>A 37058-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16570,10 +16565,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45805</v>
+        <v>46273</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16586,7 +16581,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16629,24 +16624,24 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>S 3201-2023</t>
+          <t>A 38350-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45194</v>
+        <v>46282</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16658,8 +16653,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16702,148 +16702,221 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
+          <t>S 3201-2023</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>45194</v>
+      </c>
+      <c r="E207" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" t="n">
+        <v>0</v>
+      </c>
+      <c r="T207" t="n">
+        <v>0</v>
+      </c>
+      <c r="U207" t="n">
+        <v>0</v>
+      </c>
+      <c r="V207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208" ht="15" customHeight="1">
+      <c r="A208" t="inlineStr">
+        <is>
           <t>S 4468-2022</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>Skogsbilväg</t>
         </is>
       </c>
-      <c r="D207" s="1" t="n">
+      <c r="D208" s="1" t="n">
         <v>44788</v>
       </c>
-      <c r="E207" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I207" t="n">
+      <c r="E208" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
         <v>0.5</v>
       </c>
-      <c r="J207" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" t="n">
-        <v>0</v>
-      </c>
-      <c r="L207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M207" t="n">
-        <v>0</v>
-      </c>
-      <c r="N207" t="n">
-        <v>0</v>
-      </c>
-      <c r="O207" t="n">
-        <v>0</v>
-      </c>
-      <c r="P207" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="n">
-        <v>0</v>
-      </c>
-      <c r="T207" t="n">
-        <v>0</v>
-      </c>
-      <c r="U207" t="n">
-        <v>0</v>
-      </c>
-      <c r="V207" s="2" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
+      <c r="V208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>S 85-2026</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D208" s="1" t="n">
+      <c r="D209" s="1" t="n">
         <v>46036</v>
       </c>
-      <c r="E208" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I208" t="n">
+      <c r="E209" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
         <v>0.2</v>
       </c>
-      <c r="J208" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" t="n">
-        <v>0</v>
-      </c>
-      <c r="M208" t="n">
-        <v>0</v>
-      </c>
-      <c r="N208" t="n">
-        <v>0</v>
-      </c>
-      <c r="O208" t="n">
-        <v>0</v>
-      </c>
-      <c r="P208" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="n">
-        <v>0</v>
-      </c>
-      <c r="T208" t="n">
-        <v>0</v>
-      </c>
-      <c r="U208" t="n">
-        <v>0</v>
-      </c>
-      <c r="V208" s="2" t="inlineStr"/>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE209"/>
+  <dimension ref="A1:AE210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4173-2022</t>
+          <t>A 50432-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44588</v>
+        <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1110,270 +1110,270 @@
         <v>3</v>
       </c>
       <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50432-2025 artfynd.xlsx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50432-2025 karta.png", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50432-2025 georefererad karta.tif", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50432-2025 FSC-klagomål.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50432-2025 FSC-klagomål mail.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50432-2025 tillsynsbegäran.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50432-2025 tillsynsbegäran mail.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50432-2025 prioriterade fågelarter.docx", "A 50432-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 50437-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
         <v>5</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>5</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50437-2025 artfynd.xlsx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50437-2025 karta.png", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50437-2025 georefererad karta.tif", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50437-2025 FSC-klagomål.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50437-2025 FSC-klagomål mail.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50437-2025 tillsynsbegäran.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50437-2025 tillsynsbegäran mail.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50437-2025 prioriterade fågelarter.docx", "A 50437-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 62152-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 50432-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50432-2025 artfynd.xlsx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50432-2025 karta.png", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50432-2025 georefererad karta.tif", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50432-2025 FSC-klagomål.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50432-2025 FSC-klagomål mail.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50432-2025 tillsynsbegäran.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50432-2025 tillsynsbegäran mail.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50432-2025 prioriterade fågelarter.docx", "A 50432-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 50437-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45944</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>5</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50437-2025 artfynd.xlsx", "A 50437-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50437-2025 karta.png", "A 50437-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50437-2025 georefererad karta.tif", "A 50437-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50437-2025 FSC-klagomål.docx", "A 50437-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50437-2025 FSC-klagomål mail.docx", "A 50437-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50437-2025 tillsynsbegäran.docx", "A 50437-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50437-2025 tillsynsbegäran mail.docx", "A 50437-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50437-2025 prioriterade fågelarter.docx", "A 50437-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
         <v/>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
         <v>45336</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 62152-2025</t>
+          <t>A 4173-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46006</v>
+        <v>44588</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -1554,10 +1554,10 @@
         <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
@@ -1567,35 +1567,35 @@
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
         <v/>
       </c>
       <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
         <v/>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         <v>46266</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44571</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 9001-2025</t>
+          <t>A 48687-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45713</v>
+        <v>45936</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1983,382 +1983,382 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Backstarr
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 8291-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44974</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9001-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45713</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 9839-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>46072</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 8291-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 48687-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45936</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Backstarr
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 15667-2024</t>
+          <t>A 33772-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45404</v>
+        <v>45133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2424,46 +2424,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 12779-2025</t>
+          <t>A 15667-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45733</v>
+        <v>45404</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,17 +2497,17 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>10.1</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2517,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2529,50 +2533,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12779-2025 artfynd.xlsx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12779-2025 karta.png", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12779-2025 georefererad karta.tif", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12779-2025 FSC-klagomål.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12779-2025 FSC-klagomål mail.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12779-2025 tillsynsbegäran.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12779-2025 tillsynsbegäran mail.docx", "A 12779-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12779-2025 prioriterade fågelarter.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10764-2024</t>
+          <t>A 64707-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45369</v>
+        <v>45281</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2601,8 +2601,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>8.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2614,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2626,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2642,42 +2647,46 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24514-2024</t>
+          <t>A 53485-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2691,10 +2700,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45458</v>
+        <v>45230</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2707,7 +2716,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2747,42 +2756,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 53485-2023</t>
+          <t>A 10764-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2796,10 +2809,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45230</v>
+        <v>45369</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2812,7 +2825,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2848,43 +2861,39 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
     </row>
@@ -2908,7 +2917,7 @@
         <v>45945</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2996,7 +3005,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33772-2023</t>
+          <t>A 24514-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3010,10 +3019,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45133</v>
+        <v>45458</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3026,7 +3035,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3035,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3050,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3062,50 +3071,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 64707-2023</t>
+          <t>A 12238-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3119,10 +3124,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45281</v>
+        <v>45729</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3134,13 +3139,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>11.9</v>
+        <v>10.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3152,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3164,10 +3164,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3176,50 +3176,50 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
-        <v/>
-      </c>
-      <c r="Z25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 12238-2025</t>
+          <t>A 6128-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45729</v>
+        <v>46054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>10.6</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3285,43 +3285,39 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
     </row>
@@ -3345,7 +3341,7 @@
         <v>46100</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3450,7 +3446,7 @@
         <v>46100</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3538,7 +3534,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 6128-2026</t>
+          <t>A 35813-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3552,10 +3548,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46054</v>
+        <v>46264</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3568,7 +3564,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>23.7</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3608,42 +3604,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35813-2026</t>
+          <t>A 12779-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3657,10 +3653,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46264</v>
+        <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3673,7 +3669,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>23.7</v>
+        <v>10.1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3713,35 +3709,39 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12779-2025 artfynd.xlsx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12779-2025 karta.png", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12779-2025 georefererad karta.tif", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12779-2025 FSC-klagomål.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12779-2025 FSC-klagomål mail.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12779-2025 tillsynsbegäran.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12779-2025 tillsynsbegäran mail.docx", "A 12779-2025")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12779-2025 prioriterade fågelarter.docx", "A 12779-2025")</f>
         <v/>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
         <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26926-2022</t>
+          <t>A 50007-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44740</v>
+        <v>44865</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50007-2022</t>
+          <t>A 26926-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44865</v>
+        <v>44740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44606</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44848</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44865</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44764</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44851</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 53761-2024</t>
+          <t>A 70164-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45615</v>
+        <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5254,7 +5254,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 16989-2023</t>
+          <t>A 59917-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45033</v>
+        <v>44494</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5283,13 +5283,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5332,7 +5327,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 70164-2021</t>
+          <t>A 4395-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5346,10 +5341,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44533</v>
+        <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5362,7 +5357,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5405,7 +5400,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44529-2023</t>
+          <t>A 53761-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5419,10 +5414,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45189</v>
+        <v>45615</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5435,7 +5430,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5478,7 +5473,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59917-2021</t>
+          <t>A 3178-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5492,10 +5487,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44494</v>
+        <v>45316</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5507,8 +5502,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5551,7 +5551,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 33745-2023</t>
+          <t>A 61626-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45133</v>
+        <v>45646</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4395-2022</t>
+          <t>A 12945-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44588</v>
+        <v>45385</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 30701-2022</t>
+          <t>A 52262-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44763</v>
+        <v>45217</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 31388-2022</t>
+          <t>A 16989-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44774</v>
+        <v>45033</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5799,8 +5799,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5843,7 +5848,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29329-2024</t>
+          <t>A 55712-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5857,10 +5862,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45483</v>
+        <v>44885</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5873,7 +5878,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5916,7 +5921,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 2982-2025</t>
+          <t>A 10470-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5930,10 +5935,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45678</v>
+        <v>45366</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5946,7 +5951,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5989,7 +5994,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17525-2025</t>
+          <t>A 11897-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6003,10 +6008,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45757</v>
+        <v>45728</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6019,7 +6024,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6062,7 +6067,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 9695-2025</t>
+          <t>A 29329-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6076,10 +6081,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45716</v>
+        <v>45483</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6092,7 +6097,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6135,7 +6140,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 20476-2023</t>
+          <t>A 61252-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6149,10 +6154,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45057</v>
+        <v>45645</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6165,7 +6170,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6208,7 +6213,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14079-2025</t>
+          <t>A 39001-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6222,10 +6227,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45739</v>
+        <v>45548</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6238,7 +6243,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6281,7 +6286,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19134-2025</t>
+          <t>A 30701-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6291,14 +6296,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45764</v>
+        <v>44763</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6311,7 +6316,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6354,7 +6359,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11897-2025</t>
+          <t>A 52950-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6368,10 +6373,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45728</v>
+        <v>44875</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6384,7 +6389,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6427,7 +6432,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55712-2022</t>
+          <t>A 40369-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6441,10 +6446,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44885</v>
+        <v>45555</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6457,7 +6462,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.4</v>
+        <v>14.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6500,7 +6505,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11931-2025</t>
+          <t>A 44529-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6514,10 +6519,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45728</v>
+        <v>45189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6530,7 +6535,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6573,7 +6578,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 14087-2025</t>
+          <t>A 55733-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6587,10 +6592,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45739</v>
+        <v>45232</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6603,7 +6608,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6646,7 +6651,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22560-2023</t>
+          <t>A 52852-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6660,10 +6665,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45071</v>
+        <v>45610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6676,7 +6681,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6719,7 +6724,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 46371-2022</t>
+          <t>A 50603-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6733,10 +6738,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44848</v>
+        <v>45600</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6748,13 +6753,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 54374-2022</t>
+          <t>A 25884-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44879</v>
+        <v>45085</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6870,7 +6870,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50034-2022</t>
+          <t>A 20476-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44865</v>
+        <v>45057</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6943,7 +6943,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 12945-2024</t>
+          <t>A 16223-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45385</v>
+        <v>45750</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.1</v>
+        <v>7.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7016,7 +7016,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 49554-2024</t>
+          <t>A 56024-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45596</v>
+        <v>45240</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 994-2024</t>
+          <t>A 50601-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45301</v>
+        <v>45600</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7162,7 +7162,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3187-2024</t>
+          <t>A 17525-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45316</v>
+        <v>45757</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7191,13 +7191,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7240,7 +7235,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39001-2024</t>
+          <t>A 31917-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7254,10 +7249,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45548</v>
+        <v>45834</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7270,7 +7265,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7313,7 +7308,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38983-2024</t>
+          <t>A 41991-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7327,10 +7322,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45548</v>
+        <v>44830</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7343,7 +7338,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7386,7 +7381,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 72625-2021</t>
+          <t>A 29308-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7400,10 +7395,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44546</v>
+        <v>45824</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7416,7 +7411,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7459,7 +7454,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13109-2023</t>
+          <t>A 3187-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7473,10 +7468,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45002</v>
+        <v>45316</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7488,8 +7483,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56130-2022</t>
+          <t>A 33559-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7542,14 +7542,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44886</v>
+        <v>45841</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7605,7 +7605,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33747-2023</t>
+          <t>A 46371-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45133</v>
+        <v>44848</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7634,8 +7634,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7678,7 +7683,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 29327-2024</t>
+          <t>A 59383-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7692,10 +7697,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45483</v>
+        <v>45638</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7707,8 +7712,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7751,7 +7761,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 44319-2025</t>
+          <t>A 33745-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7765,10 +7775,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45916</v>
+        <v>45133</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7781,7 +7791,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7824,7 +7834,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21333-2024</t>
+          <t>A 44319-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7838,10 +7848,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45440</v>
+        <v>45916</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7854,7 +7864,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7897,7 +7907,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41991-2022</t>
+          <t>A 5326-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7911,10 +7921,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44830</v>
+        <v>45331</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7927,7 +7937,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7970,7 +7980,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44523-2023</t>
+          <t>A 48688-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7984,10 +7994,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45189</v>
+        <v>45936</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8000,7 +8010,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8043,7 +8053,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 29195-2024</t>
+          <t>A 2982-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8057,10 +8067,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45482</v>
+        <v>45678</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8073,7 +8083,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8116,7 +8126,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56602-2023</t>
+          <t>A 60768-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8130,10 +8140,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45243</v>
+        <v>44907</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8146,7 +8156,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8189,7 +8199,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26233-2025</t>
+          <t>A 20888-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8203,10 +8213,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45805</v>
+        <v>44701</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8216,11 +8226,6 @@
       <c r="G91" t="inlineStr">
         <is>
           <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -8267,7 +8272,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 26270-2025</t>
+          <t>A 50626-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8281,10 +8286,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45805</v>
+        <v>45945</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8296,8 +8301,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8340,7 +8350,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13890-2022</t>
+          <t>A 50578-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8354,10 +8364,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44649</v>
+        <v>45945</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8370,7 +8380,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8413,7 +8423,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 7136-2022</t>
+          <t>A 50797-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8427,10 +8437,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44603</v>
+        <v>45946</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8443,7 +8453,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8486,7 +8496,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 15552-2023</t>
+          <t>A 45617-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8500,10 +8510,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45018</v>
+        <v>45579</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8516,7 +8526,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8559,7 +8569,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 50601-2024</t>
+          <t>A 54126-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8573,10 +8583,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45600</v>
+        <v>45964</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8589,7 +8599,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8632,7 +8642,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 67875-2021</t>
+          <t>A 9983-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8646,10 +8656,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44525</v>
+        <v>44621</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8662,7 +8672,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>15.5</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8705,7 +8715,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16363-2024</t>
+          <t>A 29300-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8719,10 +8729,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45407</v>
+        <v>45824</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8735,7 +8745,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8778,7 +8788,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33118-2023</t>
+          <t>A 33131-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8795,7 +8805,7 @@
         <v>45126</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8808,7 +8818,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8851,7 +8861,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 33131-2023</t>
+          <t>A 31388-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8865,10 +8875,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45126</v>
+        <v>44774</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8881,7 +8891,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8924,7 +8934,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50626-2025</t>
+          <t>A 55830-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8938,10 +8948,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45945</v>
+        <v>45972</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8953,13 +8963,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>14</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9002,7 +9007,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 41072-2023</t>
+          <t>A 29195-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9016,10 +9021,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45170</v>
+        <v>45482</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9032,7 +9037,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9075,7 +9080,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 10470-2024</t>
+          <t>A 37311-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9089,10 +9094,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45366</v>
+        <v>45876</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9105,7 +9110,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9148,7 +9153,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 50578-2025</t>
+          <t>A 994-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9162,10 +9167,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45945</v>
+        <v>45301</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9178,7 +9183,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9221,7 +9226,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 50797-2025</t>
+          <t>A 56196-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9235,10 +9240,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45946</v>
+        <v>45974</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9251,7 +9256,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9294,7 +9299,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 40369-2024</t>
+          <t>A 58226-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9308,10 +9313,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45555</v>
+        <v>45985</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9324,7 +9329,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>14.5</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9367,7 +9372,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15695-2025</t>
+          <t>A 21355-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9381,10 +9386,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45748</v>
+        <v>46142</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9397,7 +9402,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9440,7 +9445,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 45578-2024</t>
+          <t>A 21755-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9454,10 +9459,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45578</v>
+        <v>46149</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9470,7 +9475,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9513,7 +9518,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 13325-2022</t>
+          <t>A 21819-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9527,10 +9532,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44645</v>
+        <v>46150</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9543,7 +9548,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9586,7 +9591,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 54126-2025</t>
+          <t>A 21826-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9600,10 +9605,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45964</v>
+        <v>46150</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9616,7 +9621,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9659,7 +9664,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 52262-2023</t>
+          <t>A 21828-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9673,10 +9678,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45217</v>
+        <v>46150</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9689,7 +9694,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9732,7 +9737,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 38818-2024</t>
+          <t>A 21839-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9746,10 +9751,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45547</v>
+        <v>46150</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9762,7 +9767,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9805,7 +9810,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8047-2024</t>
+          <t>A 21833-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9815,14 +9820,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45351</v>
+        <v>46150</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9835,7 +9840,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9878,7 +9883,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 55830-2025</t>
+          <t>A 10457-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9892,10 +9897,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45972</v>
+        <v>44987</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9908,7 +9913,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9951,7 +9956,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 25884-2023</t>
+          <t>A 57663-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9965,10 +9970,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45085</v>
+        <v>45981</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10024,7 +10029,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 54007-2024</t>
+          <t>A 50034-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10038,10 +10043,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45615</v>
+        <v>44865</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10054,7 +10059,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10097,7 +10102,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20888-2022</t>
+          <t>A 61898-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10111,10 +10116,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44701</v>
+        <v>46003</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10127,7 +10132,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10170,7 +10175,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59383-2024</t>
+          <t>A 22321-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10184,10 +10189,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45638</v>
+        <v>46154</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10199,13 +10204,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10248,7 +10248,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 10457-2023</t>
+          <t>A 57768-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10262,10 +10262,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44987</v>
+        <v>44892</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 58226-2025</t>
+          <t>A 23027-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45985</v>
+        <v>46161</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10394,7 +10394,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 54792-2023</t>
+          <t>A 880-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45236</v>
+        <v>46029</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 880-2026</t>
+          <t>A 16363-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46029</v>
+        <v>45407</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10540,7 +10540,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 57663-2025</t>
+          <t>A 1945-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10554,10 +10554,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45981</v>
+        <v>46035</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10613,7 +10613,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 11891-2025</t>
+          <t>A 1608-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45728</v>
+        <v>46034</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1608-2026</t>
+          <t>A 15704-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46034</v>
+        <v>45748</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10759,7 +10759,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 3391-2024</t>
+          <t>A 72625-2021</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10773,10 +10773,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45318</v>
+        <v>44546</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10788,13 +10788,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10837,7 +10832,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 21061-2022</t>
+          <t>A 2322-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10851,10 +10846,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44704</v>
+        <v>46036</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10867,7 +10862,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10910,7 +10905,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 1945-2026</t>
+          <t>A 2324-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10924,10 +10919,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10940,7 +10935,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10983,7 +10978,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 55733-2023</t>
+          <t>A 19134-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10993,14 +10988,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45232</v>
+        <v>45764</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11013,7 +11008,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11056,7 +11051,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61898-2025</t>
+          <t>A 33118-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11070,10 +11065,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46003</v>
+        <v>45126</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11086,7 +11081,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11129,7 +11124,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 2322-2026</t>
+          <t>A 38988-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11143,10 +11138,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46036</v>
+        <v>45548</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11159,7 +11154,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11202,7 +11197,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 2324-2026</t>
+          <t>A 60220-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11216,10 +11211,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46036</v>
+        <v>44903</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11232,7 +11227,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11275,7 +11270,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 989-2024</t>
+          <t>A 11891-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11289,10 +11284,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45301</v>
+        <v>45728</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11348,7 +11343,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 6379-2026</t>
+          <t>A 15559-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11362,10 +11357,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46055</v>
+        <v>45019</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11378,7 +11373,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11421,7 +11416,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 38537-2026</t>
+          <t>A 54007-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11435,10 +11430,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46283</v>
+        <v>45615</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11450,13 +11445,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>5.9</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11499,7 +11489,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7466-2026</t>
+          <t>A 6379-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11513,10 +11503,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46059</v>
+        <v>46055</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11528,13 +11518,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11577,7 +11562,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 7545-2026</t>
+          <t>A 33747-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11591,10 +11576,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46059</v>
+        <v>45133</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11607,7 +11592,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11650,7 +11635,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 8060-2026</t>
+          <t>A 7545-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11664,10 +11649,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46063</v>
+        <v>46059</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11680,7 +11665,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11723,7 +11708,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 8051-2026</t>
+          <t>A 7466-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11737,10 +11722,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46063</v>
+        <v>46059</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11752,8 +11737,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11796,7 +11786,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 8058-2026</t>
+          <t>A 28586-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11810,10 +11800,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46063</v>
+        <v>45819</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11826,7 +11816,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11869,7 +11859,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 29192-2024</t>
+          <t>A 8051-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11883,10 +11873,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45482</v>
+        <v>46063</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11899,7 +11889,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11942,7 +11932,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 57768-2022</t>
+          <t>A 8058-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11956,10 +11946,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44892</v>
+        <v>46063</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11972,7 +11962,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12015,7 +12005,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 33569-2025</t>
+          <t>A 8060-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12029,10 +12019,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45841</v>
+        <v>46063</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12045,7 +12035,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12088,7 +12078,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 33586-2025</t>
+          <t>A 44523-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12102,10 +12092,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45841</v>
+        <v>45189</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12118,7 +12108,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12178,7 +12168,7 @@
         <v>46078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12234,7 +12224,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 39457-2026</t>
+          <t>A 14465-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12248,10 +12238,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46288</v>
+        <v>46100</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12264,7 +12254,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12307,7 +12297,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 33580-2025</t>
+          <t>A 14440-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12321,10 +12311,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45841</v>
+        <v>46100</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12337,7 +12327,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12380,7 +12370,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 26277-2025</t>
+          <t>A 14456-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12394,10 +12384,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45805</v>
+        <v>46100</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12410,7 +12400,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12453,7 +12443,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33536-2025</t>
+          <t>A 14462-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12467,10 +12457,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45841</v>
+        <v>46100</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12483,7 +12473,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12526,7 +12516,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 15559-2023</t>
+          <t>A 8047-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12536,14 +12526,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45019</v>
+        <v>45351</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12556,7 +12546,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12599,7 +12589,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 9983-2022</t>
+          <t>A 26409-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12613,10 +12603,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44621</v>
+        <v>46182</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12672,7 +12662,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 14440-2026</t>
+          <t>A 13109-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12686,10 +12676,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46100</v>
+        <v>45002</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12702,7 +12692,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12745,7 +12735,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14456-2026</t>
+          <t>A 21333-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12759,10 +12749,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46100</v>
+        <v>45440</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12775,7 +12765,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12818,7 +12808,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 14465-2026</t>
+          <t>A 14437-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12835,7 +12825,7 @@
         <v>46100</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12848,7 +12838,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12891,7 +12881,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 20968-2023</t>
+          <t>A 29192-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12905,10 +12895,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45061</v>
+        <v>45482</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12921,7 +12911,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12964,7 +12954,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 14462-2026</t>
+          <t>A 67875-2021</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12978,10 +12968,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46100</v>
+        <v>44525</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12994,7 +12984,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13037,7 +13027,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 14437-2026</t>
+          <t>A 28319-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13051,10 +13041,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46100</v>
+        <v>46196</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13067,7 +13057,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13110,7 +13100,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 60220-2022</t>
+          <t>A 14833-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13124,10 +13114,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44903</v>
+        <v>46103</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13140,7 +13130,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>8.300000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13183,7 +13173,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 16223-2025</t>
+          <t>A 38983-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13197,10 +13187,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45750</v>
+        <v>45548</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13213,7 +13203,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13256,7 +13246,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 45617-2024</t>
+          <t>A 22693-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13270,10 +13260,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45579</v>
+        <v>46156</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13286,7 +13276,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13329,7 +13319,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 14833-2026</t>
+          <t>A 29327-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13343,10 +13333,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46103</v>
+        <v>45483</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13359,7 +13349,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13402,7 +13392,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 31917-2025</t>
+          <t>A 29587-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13416,10 +13406,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45834</v>
+        <v>46204</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13432,7 +13422,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13475,7 +13465,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 61252-2024</t>
+          <t>A 56602-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13489,10 +13479,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45645</v>
+        <v>45243</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13505,7 +13495,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13548,7 +13538,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 56024-2023</t>
+          <t>A 41072-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13562,10 +13552,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45240</v>
+        <v>45170</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13578,7 +13568,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13621,7 +13611,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 5326-2024</t>
+          <t>A 3391-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13635,10 +13625,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45331</v>
+        <v>45318</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13650,8 +13640,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13694,7 +13689,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 56677-2023</t>
+          <t>A 20968-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13708,10 +13703,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45243</v>
+        <v>45061</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13724,7 +13719,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13767,7 +13762,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 29308-2025</t>
+          <t>A 22560-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13781,10 +13776,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45824</v>
+        <v>45071</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13797,7 +13792,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13840,7 +13835,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 29300-2025</t>
+          <t>A 54792-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13854,10 +13849,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45824</v>
+        <v>45236</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13870,7 +13865,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13913,7 +13908,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 60768-2022</t>
+          <t>A 45578-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13927,10 +13922,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44907</v>
+        <v>45578</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13943,7 +13938,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13986,7 +13981,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 52950-2022</t>
+          <t>A 35205-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14000,10 +13995,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44875</v>
+        <v>46260</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14016,7 +14011,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14059,7 +14054,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 33559-2025</t>
+          <t>A 61249-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14073,10 +14068,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45841</v>
+        <v>45645</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14089,7 +14084,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14132,7 +14127,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 52852-2024</t>
+          <t>A 38818-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14146,10 +14141,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45610</v>
+        <v>45547</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14162,7 +14157,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14205,7 +14200,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 15704-2025</t>
+          <t>A 35946-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14219,10 +14214,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45748</v>
+        <v>46266</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14278,7 +14273,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 61626-2024</t>
+          <t>A 45632-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14292,10 +14287,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45646</v>
+        <v>45579</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14307,8 +14302,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>7.3</v>
+        <v>9.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14351,7 +14351,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 3178-2024</t>
+          <t>A 7136-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14365,10 +14365,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45316</v>
+        <v>44603</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14380,13 +14380,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>8.6</v>
+        <v>1.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14429,7 +14424,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 61249-2024</t>
+          <t>A 24991-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14443,10 +14438,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45645</v>
+        <v>45085</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14459,7 +14454,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14502,7 +14497,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 56196-2025</t>
+          <t>A 989-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14516,10 +14511,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45974</v>
+        <v>45301</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14532,7 +14527,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14575,7 +14570,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 38988-2024</t>
+          <t>A 61250-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14589,10 +14584,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45548</v>
+        <v>45645</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14605,7 +14600,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14648,7 +14643,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 48688-2025</t>
+          <t>A 31837-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14662,10 +14657,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45936</v>
+        <v>46230</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14678,7 +14673,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14721,7 +14716,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 45632-2024</t>
+          <t>A 13325-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14735,10 +14730,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45579</v>
+        <v>44645</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14750,13 +14745,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>9.5</v>
+        <v>3.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14799,7 +14789,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 50603-2024</t>
+          <t>A 37822-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14813,10 +14803,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45600</v>
+        <v>46279</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14829,7 +14819,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14872,7 +14862,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 37311-2025</t>
+          <t>A 56677-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14886,10 +14876,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45876</v>
+        <v>45243</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14902,7 +14892,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14945,7 +14935,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 21355-2026</t>
+          <t>A 56130-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14955,14 +14945,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46142</v>
+        <v>44886</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14975,7 +14965,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15018,7 +15008,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 61250-2024</t>
+          <t>A 21061-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15032,10 +15022,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45645</v>
+        <v>44704</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15048,7 +15038,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15091,7 +15081,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 24991-2023</t>
+          <t>A 54374-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15105,10 +15095,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45085</v>
+        <v>44879</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15121,7 +15111,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15164,7 +15154,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 21819-2026</t>
+          <t>A 38350-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15178,10 +15168,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46150</v>
+        <v>46282</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15193,8 +15183,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15237,7 +15232,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 46532-2024</t>
+          <t>A 38537-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15251,10 +15246,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45582</v>
+        <v>46283</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15266,8 +15261,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15310,7 +15310,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 21833-2026</t>
+          <t>A 37058-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15324,10 +15324,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46150</v>
+        <v>46273</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15383,7 +15383,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 49551-2024</t>
+          <t>A 15695-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15397,10 +15397,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45596</v>
+        <v>45748</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15456,7 +15456,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 21839-2026</t>
+          <t>A 49551-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15470,10 +15470,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46150</v>
+        <v>45596</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15529,7 +15529,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 21755-2026</t>
+          <t>A 46532-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15543,10 +15543,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46149</v>
+        <v>45582</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15602,7 +15602,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 21826-2026</t>
+          <t>A 11931-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15616,10 +15616,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46150</v>
+        <v>45728</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15675,7 +15675,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 21828-2026</t>
+          <t>A 14087-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15689,10 +15689,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46150</v>
+        <v>45739</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15748,7 +15748,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 22321-2026</t>
+          <t>A 9695-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46154</v>
+        <v>45716</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15821,7 +15821,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 23027-2026</t>
+          <t>A 14079-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15835,10 +15835,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46161</v>
+        <v>45739</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15894,7 +15894,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 28586-2025</t>
+          <t>A 39504-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15908,10 +15908,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45819</v>
+        <v>46289</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15967,7 +15967,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 26409-2026</t>
+          <t>A 39457-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15981,10 +15981,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46182</v>
+        <v>46288</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28319-2026</t>
+          <t>A 49554-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16054,10 +16054,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46196</v>
+        <v>45596</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 22693-2026</t>
+          <t>A 26233-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16127,10 +16127,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46156</v>
+        <v>45805</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16142,8 +16142,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16186,7 +16191,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 29587-2026</t>
+          <t>A 26270-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16200,10 +16205,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46204</v>
+        <v>45805</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16216,7 +16221,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16259,7 +16264,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 35205-2026</t>
+          <t>A 15552-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16273,10 +16278,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46260</v>
+        <v>45018</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16289,7 +16294,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16332,7 +16337,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 35946-2026</t>
+          <t>A 13890-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16346,10 +16351,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46266</v>
+        <v>44649</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16362,7 +16367,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16405,7 +16410,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 31837-2026</t>
+          <t>A 33569-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16419,10 +16424,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46230</v>
+        <v>45841</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16435,7 +16440,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16478,7 +16483,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37822-2026</t>
+          <t>A 33586-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16492,10 +16497,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46279</v>
+        <v>45841</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16508,7 +16513,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16551,7 +16556,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37058-2026</t>
+          <t>A 33536-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16565,10 +16570,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46273</v>
+        <v>45841</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16581,7 +16586,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16624,7 +16629,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 38350-2026</t>
+          <t>A 33580-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16638,10 +16643,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46282</v>
+        <v>45841</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16653,13 +16658,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16702,24 +16702,24 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>S 3201-2023</t>
+          <t>A 26277-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45194</v>
+        <v>45805</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16775,148 +16775,221 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
+          <t>S 3201-2023</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D208" s="1" t="n">
+        <v>45194</v>
+      </c>
+      <c r="E208" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>0</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
+      <c r="V208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209" ht="15" customHeight="1">
+      <c r="A209" t="inlineStr">
+        <is>
           <t>S 4468-2022</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Skogsbilväg</t>
         </is>
       </c>
-      <c r="D208" s="1" t="n">
+      <c r="D209" s="1" t="n">
         <v>44788</v>
       </c>
-      <c r="E208" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I208" t="n">
+      <c r="E209" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
         <v>0.5</v>
       </c>
-      <c r="J208" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" t="n">
-        <v>0</v>
-      </c>
-      <c r="M208" t="n">
-        <v>0</v>
-      </c>
-      <c r="N208" t="n">
-        <v>0</v>
-      </c>
-      <c r="O208" t="n">
-        <v>0</v>
-      </c>
-      <c r="P208" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="n">
-        <v>0</v>
-      </c>
-      <c r="T208" t="n">
-        <v>0</v>
-      </c>
-      <c r="U208" t="n">
-        <v>0</v>
-      </c>
-      <c r="V208" s="2" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" t="n">
+        <v>0</v>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
         <is>
           <t>S 85-2026</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D209" s="1" t="n">
+      <c r="D210" s="1" t="n">
         <v>46036</v>
       </c>
-      <c r="E209" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I209" t="n">
+      <c r="E210" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
         <v>0.2</v>
       </c>
-      <c r="J209" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" t="n">
-        <v>0</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0</v>
-      </c>
-      <c r="M209" t="n">
-        <v>0</v>
-      </c>
-      <c r="N209" t="n">
-        <v>0</v>
-      </c>
-      <c r="O209" t="n">
-        <v>0</v>
-      </c>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="n">
-        <v>0</v>
-      </c>
-      <c r="T209" t="n">
-        <v>0</v>
-      </c>
-      <c r="U209" t="n">
-        <v>0</v>
-      </c>
-      <c r="V209" s="2" t="inlineStr"/>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0</v>
+      </c>
+      <c r="V210" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50432-2025</t>
+          <t>A 4173-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45944</v>
+        <v>44588</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1110,599 +1110,599 @@
         <v>3</v>
       </c>
       <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 50432-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="U6" t="n">
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Älg
 Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50432-2025 artfynd.xlsx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50432-2025 karta.png", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50432-2025 georefererad karta.tif", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50432-2025 FSC-klagomål.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50432-2025 FSC-klagomål mail.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50432-2025 tillsynsbegäran.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50432-2025 tillsynsbegäran mail.docx", "A 50432-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50432-2025 prioriterade fågelarter.docx", "A 50432-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 50437-2025</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>45944</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>3.6</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>3</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>5</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Älg
 Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50437-2025 artfynd.xlsx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50437-2025 karta.png", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50437-2025 georefererad karta.tif", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50437-2025 FSC-klagomål.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50437-2025 FSC-klagomål mail.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50437-2025 tillsynsbegäran.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50437-2025 tillsynsbegäran mail.docx", "A 50437-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 50437-2025 prioriterade fågelarter.docx", "A 50437-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 62152-2025</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
         <v>46006</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>3.7</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>4</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>4</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35974-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa
+Klippfrullania
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35974-2026 artfynd.xlsx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35974-2026 karta.png", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35974-2026 georefererad karta.tif", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35974-2026 FSC-klagomål.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35974-2026 FSC-klagomål mail.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35974-2026 tillsynsbegäran.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35974-2026 tillsynsbegäran mail.docx", "A 35974-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 6043-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45336</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.7</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U11" t="n">
         <v>7</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Grönpyrola
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 4173-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44588</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>5</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 35974-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grov fjädermossa
-Klippfrullania
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35974-2026 artfynd.xlsx", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35974-2026 karta.png", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35974-2026 georefererad karta.tif", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35974-2026 FSC-klagomål.docx", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35974-2026 FSC-klagomål mail.docx", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35974-2026 tillsynsbegäran.docx", "A 35974-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35974-2026 tillsynsbegäran mail.docx", "A 35974-2026")</f>
         <v/>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44571</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 48687-2025</t>
+          <t>A 9001-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45936</v>
+        <v>45713</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1983,382 +1983,382 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9839-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 48687-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Blåsippa</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 8291-2023</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>44974</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>17.3</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9001-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45713</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9001-2025 artfynd.xlsx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9001-2025 karta.png", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9001-2025 georefererad karta.tif", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 9001-2025 karta knärot.png", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9001-2025 FSC-klagomål.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9001-2025 FSC-klagomål mail.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9001-2025 tillsynsbegäran.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9001-2025 tillsynsbegäran mail.docx", "A 9001-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9839-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 9839-2026 artfynd.xlsx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 9839-2026 karta.png", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 9839-2026 georefererad karta.tif", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 9839-2026 FSC-klagomål.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 9839-2026 FSC-klagomål mail.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 9839-2026 tillsynsbegäran.docx", "A 9839-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 9839-2026 tillsynsbegäran mail.docx", "A 9839-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33772-2023</t>
+          <t>A 15667-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45133</v>
+        <v>45404</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2424,50 +2424,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15667-2024</t>
+          <t>A 10764-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2481,10 +2477,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45404</v>
+        <v>45369</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2497,16 +2493,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2521,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2533,46 +2529,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 64707-2023</t>
+          <t>A 24514-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2586,10 +2582,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45281</v>
+        <v>45458</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2601,13 +2597,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>11.9</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2619,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2631,10 +2622,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2643,50 +2634,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 53485-2023</t>
+          <t>A 12238-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2700,10 +2687,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45230</v>
+        <v>45729</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2716,7 +2703,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>10.6</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2756,46 +2743,46 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10764-2024</t>
+          <t>A 14442-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2809,10 +2796,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45369</v>
+        <v>46100</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2825,7 +2812,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>8.300000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2837,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2849,10 +2836,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2865,35 +2852,35 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
     </row>
@@ -2917,7 +2904,7 @@
         <v>45945</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +2992,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24514-2024</t>
+          <t>A 14455-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3019,10 +3006,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45458</v>
+        <v>46100</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3035,7 +3022,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3071,46 +3058,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 12238-2025</t>
+          <t>A 53485-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3124,10 +3111,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45729</v>
+        <v>45230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3140,7 +3127,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>10.6</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3180,39 +3167,39 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3223,7 @@
         <v>46054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3324,7 +3311,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14442-2026</t>
+          <t>A 33772-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3338,10 +3325,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46100</v>
+        <v>45133</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3354,7 +3341,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3363,10 +3350,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3381,7 +3368,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3394,42 +3381,46 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14455-2026</t>
+          <t>A 35813-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3443,10 +3434,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46100</v>
+        <v>46264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3459,7 +3450,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>8.199999999999999</v>
+        <v>23.7</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3503,38 +3494,38 @@
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35813-2026</t>
+          <t>A 64707-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3548,10 +3539,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46264</v>
+        <v>45281</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,8 +3554,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>23.7</v>
+        <v>11.9</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3576,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3588,10 +3584,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3604,35 +3600,39 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
         <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50007-2022</t>
+          <t>A 26926-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44865</v>
+        <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26926-2022</t>
+          <t>A 50007-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44740</v>
+        <v>44865</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44606</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44848</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50020-2022</t>
+          <t>A 30731-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44865</v>
+        <v>44764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 30731-2022</t>
+          <t>A 50020-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44764</v>
+        <v>44865</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4906,7 +4906,7 @@
         <v>44510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44851</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44494</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 53761-2024</t>
+          <t>A 31388-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45615</v>
+        <v>44774</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3178-2024</t>
+          <t>A 30701-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45316</v>
+        <v>44763</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5502,13 +5502,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>8.6</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5551,7 +5546,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61626-2024</t>
+          <t>A 55712-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5565,10 +5560,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45646</v>
+        <v>44885</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5581,7 +5576,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5624,7 +5619,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12945-2024</t>
+          <t>A 46371-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45385</v>
+        <v>44848</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5653,8 +5648,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52262-2023</t>
+          <t>A 54374-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45217</v>
+        <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16989-2023</t>
+          <t>A 72625-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45033</v>
+        <v>44546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5799,13 +5799,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5848,7 +5843,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 55712-2022</t>
+          <t>A 880-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5862,10 +5857,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44885</v>
+        <v>46029</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5878,7 +5873,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5921,7 +5916,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10470-2024</t>
+          <t>A 49554-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5935,10 +5930,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45366</v>
+        <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5951,7 +5946,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5994,7 +5989,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11897-2025</t>
+          <t>A 1608-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6008,10 +6003,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45728</v>
+        <v>46034</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6024,7 +6019,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6067,7 +6062,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29329-2024</t>
+          <t>A 1945-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6081,10 +6076,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45483</v>
+        <v>46035</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6097,7 +6092,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6140,7 +6135,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 61252-2024</t>
+          <t>A 29327-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6154,10 +6149,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45645</v>
+        <v>45483</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6170,7 +6165,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6213,7 +6208,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39001-2024</t>
+          <t>A 2322-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6227,10 +6222,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45548</v>
+        <v>46036</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6243,7 +6238,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6286,7 +6281,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30701-2022</t>
+          <t>A 2324-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6300,10 +6295,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44763</v>
+        <v>46036</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6316,7 +6311,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6359,7 +6354,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52950-2022</t>
+          <t>A 41991-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6373,10 +6368,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44875</v>
+        <v>44830</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6389,7 +6384,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6432,7 +6427,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 40369-2024</t>
+          <t>A 44523-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6446,10 +6441,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45555</v>
+        <v>45189</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6462,7 +6457,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6505,7 +6500,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44529-2023</t>
+          <t>A 6379-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6519,10 +6514,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45189</v>
+        <v>46055</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6535,7 +6530,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6578,7 +6573,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55733-2023</t>
+          <t>A 44319-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6592,10 +6587,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45232</v>
+        <v>45916</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6608,7 +6603,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6651,7 +6646,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52852-2024</t>
+          <t>A 7466-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6665,10 +6660,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45610</v>
+        <v>46059</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6680,8 +6675,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>2.9</v>
+        <v>6.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6724,7 +6724,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 50603-2024</t>
+          <t>A 7545-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45600</v>
+        <v>46059</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25884-2023</t>
+          <t>A 8060-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45085</v>
+        <v>46063</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6870,7 +6870,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 20476-2023</t>
+          <t>A 8051-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6884,10 +6884,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45057</v>
+        <v>46063</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16223-2025</t>
+          <t>A 8058-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45750</v>
+        <v>46063</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7016,7 +7016,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56024-2023</t>
+          <t>A 26233-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45240</v>
+        <v>45805</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7045,8 +7045,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7089,7 +7094,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 50601-2024</t>
+          <t>A 26270-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7103,10 +7108,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45600</v>
+        <v>45805</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7119,7 +7124,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7162,7 +7167,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17525-2025</t>
+          <t>A 33118-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7176,10 +7181,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45757</v>
+        <v>45126</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7192,7 +7197,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7235,7 +7240,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31917-2025</t>
+          <t>A 33131-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7249,10 +7254,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45834</v>
+        <v>45126</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7265,7 +7270,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7308,7 +7313,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41991-2022</t>
+          <t>A 10850-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7322,10 +7327,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44830</v>
+        <v>46078</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7338,7 +7343,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7381,7 +7386,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29308-2025</t>
+          <t>A 13890-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7395,10 +7400,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45824</v>
+        <v>44649</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7411,7 +7416,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7454,7 +7459,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 3187-2024</t>
+          <t>A 15552-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7468,10 +7473,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45316</v>
+        <v>45018</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7483,13 +7488,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33559-2025</t>
+          <t>A 15695-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7546,10 +7546,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45841</v>
+        <v>45748</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7605,7 +7605,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46371-2022</t>
+          <t>A 45578-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44848</v>
+        <v>45578</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7634,13 +7634,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7683,7 +7678,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59383-2024</t>
+          <t>A 50626-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7697,10 +7692,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45638</v>
+        <v>45945</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7714,11 +7709,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>14</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7761,7 +7756,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33745-2023</t>
+          <t>A 14440-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7775,10 +7770,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45133</v>
+        <v>46100</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7791,7 +7786,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7834,7 +7829,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 44319-2025</t>
+          <t>A 14456-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7848,10 +7843,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45916</v>
+        <v>46100</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7864,7 +7859,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7907,7 +7902,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5326-2024</t>
+          <t>A 14465-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7921,10 +7916,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45331</v>
+        <v>46100</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7937,7 +7932,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7980,7 +7975,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 48688-2025</t>
+          <t>A 13325-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7994,10 +7989,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45936</v>
+        <v>44645</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8010,7 +8005,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8053,7 +8048,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2982-2025</t>
+          <t>A 14462-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8067,10 +8062,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45678</v>
+        <v>46100</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8083,7 +8078,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>6.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8126,7 +8121,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60768-2022</t>
+          <t>A 50578-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8140,10 +8135,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44907</v>
+        <v>45945</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8156,7 +8151,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8199,7 +8194,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20888-2022</t>
+          <t>A 50797-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8213,10 +8208,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44701</v>
+        <v>45946</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8229,7 +8224,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8272,7 +8267,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 50626-2025</t>
+          <t>A 14437-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8286,10 +8281,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45945</v>
+        <v>46100</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8301,13 +8296,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8350,7 +8340,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50578-2025</t>
+          <t>A 54126-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8364,10 +8354,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45945</v>
+        <v>45964</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8380,7 +8370,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8423,7 +8413,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50797-2025</t>
+          <t>A 59383-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8437,10 +8427,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45946</v>
+        <v>45638</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8452,8 +8442,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8496,7 +8491,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 45617-2024</t>
+          <t>A 10457-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8510,10 +8505,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45579</v>
+        <v>44987</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8526,7 +8521,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8569,7 +8564,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 54126-2025</t>
+          <t>A 55830-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8583,10 +8578,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45964</v>
+        <v>45972</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8599,7 +8594,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8642,7 +8637,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9983-2022</t>
+          <t>A 14833-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8656,10 +8651,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44621</v>
+        <v>46103</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8672,7 +8667,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8715,7 +8710,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29300-2025</t>
+          <t>A 58226-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8729,10 +8724,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45824</v>
+        <v>45985</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8745,7 +8740,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8788,7 +8783,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33131-2023</t>
+          <t>A 53761-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8802,10 +8797,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45126</v>
+        <v>45615</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8818,7 +8813,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8861,7 +8856,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 31388-2022</t>
+          <t>A 16989-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8875,10 +8870,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44774</v>
+        <v>45033</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8890,8 +8885,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8934,7 +8934,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 55830-2025</t>
+          <t>A 31917-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45972</v>
+        <v>45834</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9007,7 +9007,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 29195-2024</t>
+          <t>A 44529-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45482</v>
+        <v>45189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9080,7 +9080,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37311-2025</t>
+          <t>A 33745-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9094,10 +9094,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45876</v>
+        <v>45133</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9153,7 +9153,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 994-2024</t>
+          <t>A 57663-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9167,10 +9167,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45301</v>
+        <v>45981</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9226,7 +9226,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56196-2025</t>
+          <t>A 29308-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45974</v>
+        <v>45824</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9299,7 +9299,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 58226-2025</t>
+          <t>A 61898-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9313,10 +9313,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45985</v>
+        <v>46003</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21355-2026</t>
+          <t>A 29300-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46142</v>
+        <v>45824</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9445,7 +9445,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 21755-2026</t>
+          <t>A 29329-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9459,10 +9459,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46149</v>
+        <v>45483</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9518,7 +9518,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 21819-2026</t>
+          <t>A 33559-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46150</v>
+        <v>45841</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21826-2026</t>
+          <t>A 2982-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46150</v>
+        <v>45678</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 21828-2026</t>
+          <t>A 56196-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46150</v>
+        <v>45974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9737,7 +9737,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21839-2026</t>
+          <t>A 20476-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46150</v>
+        <v>45057</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9810,7 +9810,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21833-2026</t>
+          <t>A 19134-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9820,14 +9820,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46150</v>
+        <v>45764</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9883,7 +9883,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10457-2023</t>
+          <t>A 48688-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9897,10 +9897,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44987</v>
+        <v>45936</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9956,7 +9956,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 57663-2025</t>
+          <t>A 11897-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9970,10 +9970,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45981</v>
+        <v>45728</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10029,7 +10029,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 50034-2022</t>
+          <t>A 37311-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10043,10 +10043,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44865</v>
+        <v>45876</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61898-2025</t>
+          <t>A 21355-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46003</v>
+        <v>46142</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10175,7 +10175,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22321-2026</t>
+          <t>A 22560-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46154</v>
+        <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10248,7 +10248,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57768-2022</t>
+          <t>A 50034-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10262,10 +10262,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44892</v>
+        <v>44865</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 23027-2026</t>
+          <t>A 21819-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46161</v>
+        <v>46150</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10394,7 +10394,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 880-2026</t>
+          <t>A 21833-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46029</v>
+        <v>46150</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10467,7 +10467,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16363-2024</t>
+          <t>A 21839-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45407</v>
+        <v>46150</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10540,7 +10540,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 1945-2026</t>
+          <t>A 21755-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10554,10 +10554,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46035</v>
+        <v>46149</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10613,7 +10613,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1608-2026</t>
+          <t>A 21826-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46034</v>
+        <v>46150</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 15704-2025</t>
+          <t>A 21828-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10700,10 +10700,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45748</v>
+        <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10759,7 +10759,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 72625-2021</t>
+          <t>A 22321-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10773,10 +10773,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44546</v>
+        <v>46154</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10832,7 +10832,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 2322-2026</t>
+          <t>A 12945-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10846,10 +10846,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46036</v>
+        <v>45385</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10905,7 +10905,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 2324-2026</t>
+          <t>A 994-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10919,10 +10919,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46036</v>
+        <v>45301</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10978,7 +10978,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 19134-2025</t>
+          <t>A 3187-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10988,14 +10988,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45764</v>
+        <v>45316</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11007,8 +11007,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11051,7 +11056,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 33118-2023</t>
+          <t>A 23027-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11065,10 +11070,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45126</v>
+        <v>46161</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11081,7 +11086,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11124,7 +11129,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 38988-2024</t>
+          <t>A 33569-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11138,10 +11143,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45548</v>
+        <v>45841</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11154,7 +11159,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11197,7 +11202,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 60220-2022</t>
+          <t>A 33586-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11211,10 +11216,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44903</v>
+        <v>45841</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11227,7 +11232,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>8.300000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11270,7 +11275,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11891-2025</t>
+          <t>A 33580-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11284,10 +11289,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45728</v>
+        <v>45841</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11300,7 +11305,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11343,7 +11348,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 15559-2023</t>
+          <t>A 26277-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11357,10 +11362,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45019</v>
+        <v>45805</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11373,7 +11378,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11416,7 +11421,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 54007-2024</t>
+          <t>A 33536-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11430,10 +11435,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45615</v>
+        <v>45841</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11446,7 +11451,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11489,7 +11494,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 6379-2026</t>
+          <t>A 39001-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11503,10 +11508,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46055</v>
+        <v>45548</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11519,7 +11524,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11562,7 +11567,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 33747-2023</t>
+          <t>A 28586-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11576,10 +11581,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45133</v>
+        <v>45819</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11592,7 +11597,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11635,7 +11640,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7545-2026</t>
+          <t>A 38983-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11649,10 +11654,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46059</v>
+        <v>45548</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11665,7 +11670,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11708,7 +11713,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7466-2026</t>
+          <t>A 13109-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11722,10 +11727,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46059</v>
+        <v>45002</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11737,13 +11742,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>6.4</v>
+        <v>2.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11786,7 +11786,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 28586-2025</t>
+          <t>A 56130-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11796,14 +11796,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45819</v>
+        <v>44886</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11859,7 +11859,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 8051-2026</t>
+          <t>A 33747-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46063</v>
+        <v>45133</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11932,7 +11932,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8058-2026</t>
+          <t>A 21333-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11946,10 +11946,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46063</v>
+        <v>45440</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12005,7 +12005,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 8060-2026</t>
+          <t>A 29195-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12019,10 +12019,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46063</v>
+        <v>45482</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 44523-2023</t>
+          <t>A 26409-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12092,10 +12092,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45189</v>
+        <v>46182</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12151,7 +12151,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 10850-2026</t>
+          <t>A 56602-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12165,10 +12165,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46078</v>
+        <v>45243</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12224,7 +12224,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 14465-2026</t>
+          <t>A 7136-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12238,10 +12238,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46100</v>
+        <v>44603</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12297,7 +12297,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 14440-2026</t>
+          <t>A 16223-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12311,10 +12311,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46100</v>
+        <v>45750</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12370,7 +12370,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 14456-2026</t>
+          <t>A 50601-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12384,10 +12384,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46100</v>
+        <v>45600</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12443,7 +12443,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 14462-2026</t>
+          <t>A 67875-2021</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12457,10 +12457,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46100</v>
+        <v>44525</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12516,7 +12516,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 8047-2024</t>
+          <t>A 16363-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12526,14 +12526,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45351</v>
+        <v>45407</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12589,7 +12589,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 26409-2026</t>
+          <t>A 28319-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12603,10 +12603,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46182</v>
+        <v>46196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12662,7 +12662,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 13109-2023</t>
+          <t>A 22693-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12676,10 +12676,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45002</v>
+        <v>46156</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12735,7 +12735,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 21333-2024</t>
+          <t>A 41072-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12749,10 +12749,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45440</v>
+        <v>45170</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12808,7 +12808,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 14437-2026</t>
+          <t>A 10470-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12822,10 +12822,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46100</v>
+        <v>45366</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12881,7 +12881,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 29192-2024</t>
+          <t>A 40369-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12895,10 +12895,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45482</v>
+        <v>45555</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12954,7 +12954,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 67875-2021</t>
+          <t>A 17525-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12968,10 +12968,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44525</v>
+        <v>45757</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>15.5</v>
+        <v>2.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13027,7 +13027,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 28319-2026</t>
+          <t>A 29587-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13041,10 +13041,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46196</v>
+        <v>46204</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13100,7 +13100,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 14833-2026</t>
+          <t>A 52262-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13114,10 +13114,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46103</v>
+        <v>45217</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13173,7 +13173,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 38983-2024</t>
+          <t>A 38818-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45548</v>
+        <v>45547</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 22693-2026</t>
+          <t>A 8047-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13256,14 +13256,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46156</v>
+        <v>45351</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13319,7 +13319,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 29327-2024</t>
+          <t>A 25884-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45483</v>
+        <v>45085</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13392,7 +13392,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 29587-2026</t>
+          <t>A 54007-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46204</v>
+        <v>45615</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13465,7 +13465,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 56602-2023</t>
+          <t>A 20888-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13479,10 +13479,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45243</v>
+        <v>44701</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13538,7 +13538,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 41072-2023</t>
+          <t>A 35205-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13552,10 +13552,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45170</v>
+        <v>46260</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13611,7 +13611,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 3391-2024</t>
+          <t>A 54792-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13625,10 +13625,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45318</v>
+        <v>45236</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13640,13 +13640,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1.8</v>
+        <v>5.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13689,7 +13684,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 20968-2023</t>
+          <t>A 35946-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13703,10 +13698,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45061</v>
+        <v>46266</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13719,7 +13714,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13762,7 +13757,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 22560-2023</t>
+          <t>A 11891-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13776,10 +13771,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45071</v>
+        <v>45728</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13835,7 +13830,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 54792-2023</t>
+          <t>A 3391-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13849,10 +13844,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45236</v>
+        <v>45318</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13864,8 +13859,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13908,7 +13908,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 45578-2024</t>
+          <t>A 21061-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13922,10 +13922,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45578</v>
+        <v>44704</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 35205-2026</t>
+          <t>A 55733-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13995,10 +13995,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46260</v>
+        <v>45232</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14054,7 +14054,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 61249-2024</t>
+          <t>A 31837-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14068,10 +14068,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45645</v>
+        <v>46230</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14127,7 +14127,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 38818-2024</t>
+          <t>A 989-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14141,10 +14141,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45547</v>
+        <v>45301</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14200,7 +14200,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 35946-2026</t>
+          <t>A 37822-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14214,10 +14214,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46266</v>
+        <v>46279</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14273,7 +14273,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 45632-2024</t>
+          <t>A 37058-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14287,10 +14287,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45579</v>
+        <v>46273</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14302,13 +14302,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>9.5</v>
+        <v>2.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14351,7 +14346,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 7136-2022</t>
+          <t>A 38350-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14365,10 +14360,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44603</v>
+        <v>46282</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14380,8 +14375,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14424,7 +14424,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 24991-2023</t>
+          <t>A 29192-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14438,10 +14438,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45085</v>
+        <v>45482</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14497,7 +14497,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 989-2024</t>
+          <t>A 57768-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14511,10 +14511,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45301</v>
+        <v>44892</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14570,7 +14570,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 61250-2024</t>
+          <t>A 38537-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14584,10 +14584,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45645</v>
+        <v>46283</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14599,8 +14599,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14643,7 +14648,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 31837-2026</t>
+          <t>A 39457-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14657,10 +14662,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46230</v>
+        <v>46288</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14673,7 +14678,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14716,7 +14721,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 13325-2022</t>
+          <t>A 39504-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14730,10 +14735,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44645</v>
+        <v>46289</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14746,7 +14751,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14789,7 +14794,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37822-2026</t>
+          <t>A 15559-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14803,10 +14808,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46279</v>
+        <v>45019</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14819,7 +14824,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14862,7 +14867,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 56677-2023</t>
+          <t>A 9983-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14876,10 +14881,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45243</v>
+        <v>44621</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14935,7 +14940,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 56130-2022</t>
+          <t>A 20968-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14945,14 +14950,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44886</v>
+        <v>45061</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14965,7 +14970,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15008,7 +15013,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 21061-2022</t>
+          <t>A 60220-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15022,10 +15027,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44704</v>
+        <v>44903</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15038,7 +15043,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15081,7 +15086,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 54374-2022</t>
+          <t>A 45617-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15095,10 +15100,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44879</v>
+        <v>45579</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15111,7 +15116,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15154,7 +15159,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 38350-2026</t>
+          <t>A 61252-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15168,10 +15173,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46282</v>
+        <v>45645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15183,13 +15188,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15232,7 +15232,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 38537-2026</t>
+          <t>A 56024-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15246,10 +15246,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46283</v>
+        <v>45240</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15261,13 +15261,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15310,7 +15305,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37058-2026</t>
+          <t>A 5326-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15324,10 +15319,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46273</v>
+        <v>45331</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15340,7 +15335,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15383,7 +15378,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 15695-2025</t>
+          <t>A 56677-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15397,10 +15392,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45748</v>
+        <v>45243</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15413,7 +15408,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15456,7 +15451,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 49551-2024</t>
+          <t>A 60768-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15470,10 +15465,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45596</v>
+        <v>44907</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15486,7 +15481,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.6</v>
+        <v>10</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15529,7 +15524,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 46532-2024</t>
+          <t>A 52950-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15543,10 +15538,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45582</v>
+        <v>44875</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15559,7 +15554,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15602,7 +15597,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 11931-2025</t>
+          <t>A 52852-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15616,10 +15611,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45728</v>
+        <v>45610</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15632,7 +15627,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15675,7 +15670,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 14087-2025</t>
+          <t>A 15704-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15689,10 +15684,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45739</v>
+        <v>45748</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15705,7 +15700,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15748,7 +15743,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 9695-2025</t>
+          <t>A 61626-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15762,10 +15757,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45716</v>
+        <v>45646</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15778,7 +15773,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.2</v>
+        <v>7.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15821,7 +15816,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 14079-2025</t>
+          <t>A 3178-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15835,10 +15830,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45739</v>
+        <v>45316</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15850,8 +15845,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15894,7 +15894,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 39504-2026</t>
+          <t>A 61249-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15908,10 +15908,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46289</v>
+        <v>45645</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15967,7 +15967,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 39457-2026</t>
+          <t>A 38988-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15981,10 +15981,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46288</v>
+        <v>45548</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 49554-2024</t>
+          <t>A 45632-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16054,10 +16054,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45596</v>
+        <v>45579</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16069,8 +16069,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>2.3</v>
+        <v>9.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16113,7 +16118,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 26233-2025</t>
+          <t>A 50603-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16127,10 +16132,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45805</v>
+        <v>45600</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16142,13 +16147,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16191,7 +16191,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 26270-2025</t>
+          <t>A 61250-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16205,10 +16205,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45805</v>
+        <v>45645</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16264,7 +16264,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 15552-2023</t>
+          <t>A 24991-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16278,10 +16278,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45018</v>
+        <v>45085</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16337,7 +16337,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 13890-2022</t>
+          <t>A 46532-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16351,10 +16351,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44649</v>
+        <v>45582</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16410,7 +16410,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 33569-2025</t>
+          <t>A 49551-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16424,10 +16424,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45841</v>
+        <v>45596</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16483,7 +16483,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 33586-2025</t>
+          <t>A 9695-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16497,10 +16497,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45841</v>
+        <v>45716</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 33536-2025</t>
+          <t>A 14079-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16570,10 +16570,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45841</v>
+        <v>45739</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>6.3</v>
+        <v>2.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 33580-2025</t>
+          <t>A 11931-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16643,10 +16643,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45841</v>
+        <v>45728</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16702,7 +16702,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 26277-2025</t>
+          <t>A 14087-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16716,10 +16716,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45805</v>
+        <v>45739</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16792,7 +16792,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>44788</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>46036</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>44588</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45944</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>46006</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>46266</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>45336</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44571</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>45713</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>46072</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45936</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44974</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>45404</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45369</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>45458</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45729</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>46100</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>45945</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>46100</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>46054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45133</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>46264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45281</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>44865</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44606</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44848</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44865</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44851</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44494</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44774</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44763</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44885</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44848</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>46029</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>46034</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>46035</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45483</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>46036</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>46036</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44830</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45189</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>46055</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>45916</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>46059</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>46059</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>46063</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>46063</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>46063</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>45805</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>45805</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45126</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>45126</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>46078</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>44649</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45018</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>45748</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>45578</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45945</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>46100</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>46100</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>46100</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44645</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>46100</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45945</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>45946</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>46100</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45964</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45638</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44987</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45972</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>46103</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45985</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45615</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45033</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45834</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>45133</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>45981</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45824</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>46003</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45824</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>45483</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>45841</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45678</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45057</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45764</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45936</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45728</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45876</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>46142</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>44865</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>46150</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>46150</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>46150</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46149</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>46150</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>46154</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45385</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45301</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45316</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>46161</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45841</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45841</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45841</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45805</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45841</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>45548</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45819</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45548</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45002</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44886</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45133</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45440</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45482</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>46182</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45243</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44603</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45750</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45600</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44525</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45407</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>46196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>46156</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>45170</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45366</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45555</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45757</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>46204</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45217</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45547</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45351</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45085</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45615</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44701</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46260</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45236</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>46266</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45728</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45318</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44704</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45232</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>46230</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45301</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>46279</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>46273</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>46282</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45482</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44892</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46283</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>46288</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>46289</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45019</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>44621</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45061</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44903</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45579</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>45645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45240</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45331</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45243</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44907</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44875</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45610</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45748</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45646</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>45316</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45645</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45548</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>45579</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45600</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45645</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45085</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45582</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45596</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45716</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>45739</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45728</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45739</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>44788</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>46036</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>44588</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45944</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>46006</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>46266</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>45336</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44571</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>45713</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>46072</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>45936</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44974</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>45404</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45369</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>45458</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45729</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>46100</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>45945</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>46100</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>45230</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>46054</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>45133</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>46264</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>45281</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>45733</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>44865</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44606</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44848</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>44865</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>44510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44851</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44494</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>44774</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44763</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>44885</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44848</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         <v>44879</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>44546</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>46029</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>46034</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>46035</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>45483</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>46036</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>46036</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44830</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>45189</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
         <v>46055</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>45916</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>46059</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>46059</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>46063</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>46063</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>46063</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>45805</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>45805</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45126</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>45126</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>46078</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>44649</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45018</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>45748</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>45578</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45945</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>46100</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>46100</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>46100</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44645</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>46100</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>45945</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>45946</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>46100</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>45964</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45638</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>44987</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>45972</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>46103</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45985</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45615</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45033</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45834</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>45133</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>45981</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45824</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>46003</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45824</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>45483</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>45841</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45678</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45057</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>45764</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45936</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45728</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45876</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>46142</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>45071</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>44865</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>46150</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>46150</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>46150</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46149</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>46150</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>46150</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>46154</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45385</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>45301</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45316</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>46161</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45841</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45841</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45841</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>45805</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45841</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>45548</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45819</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45548</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45002</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>44886</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45133</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45440</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45482</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>46182</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45243</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>44603</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45750</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>45600</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44525</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45407</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>46196</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>46156</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>45170</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45366</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45555</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>45757</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>46204</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>45217</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>45547</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>45351</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45085</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45615</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44701</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46260</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45236</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>46266</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45728</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45318</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44704</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45232</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>46230</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45301</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>46279</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>46273</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>46282</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45482</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>44892</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46283</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>46288</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>46289</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45019</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>44621</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45061</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>44903</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45579</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>45645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45240</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>45331</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45243</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>44907</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>44875</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45610</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45748</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45646</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>45316</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45645</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45548</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>45579</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45600</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45645</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45085</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45582</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45596</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45716</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>45739</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45728</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45739</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>44788</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>46036</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>

--- a/Översikt STRÖMSTAD.xlsx
+++ b/Översikt STRÖMSTAD.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE210"/>
+  <dimension ref="A1:AE211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45720</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>45957</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45993</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>45638</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4173-2022</t>
+          <t>A 62152-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44588</v>
+        <v>46006</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1110,10 +1110,10 @@
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1123,35 +1123,35 @@
         </is>
       </c>
       <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
         <v/>
       </c>
       <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
         <v/>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v>45944</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>45944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 62152-2025</t>
+          <t>A 6043-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46006</v>
+        <v>45336</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1434,275 +1434,275 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grönpyrola
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 4173-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44588</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 62152-2025 artfynd.xlsx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 62152-2025 karta.png", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 62152-2025 georefererad karta.tif", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 62152-2025 FSC-klagomål.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 62152-2025 FSC-klagomål mail.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 62152-2025 tillsynsbegäran.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 62152-2025 tillsynsbegäran mail.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 62152-2025 prioriterade fågelarter.docx", "A 62152-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 4173-2022 artfynd.xlsx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 4173-2022 karta.png", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 4173-2022 georefererad karta.tif", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 4173-2022 FSC-klagomål.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 4173-2022 FSC-klagomål mail.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 4173-2022 tillsynsbegäran.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 4173-2022 tillsynsbegäran mail.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 4173-2022 prioriterade fågelarter.docx", "A 4173-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 35974-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>3.7</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>3</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grov fjädermossa
 Klippfrullania
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35974-2026 artfynd.xlsx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35974-2026 karta.png", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35974-2026 georefererad karta.tif", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35974-2026 FSC-klagomål.docx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35974-2026 FSC-klagomål mail.docx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35974-2026 tillsynsbegäran.docx", "A 35974-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35974-2026 tillsynsbegäran mail.docx", "A 35974-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 6043-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45336</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grönpyrola
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6043-2024 artfynd.xlsx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6043-2024 karta.png", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6043-2024 georefererad karta.tif", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 6043-2024 karta knärot.png", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6043-2024 FSC-klagomål.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6043-2024 FSC-klagomål mail.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6043-2024 tillsynsbegäran.docx", "A 6043-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6043-2024 tillsynsbegäran mail.docx", "A 6043-2024")</f>
         <v/>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
         <v>43962</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44571</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>45713</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>46072</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 48687-2025</t>
+          <t>A 8291-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45936</v>
+        <v>44974</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.4</v>
+        <v>17.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2208,157 +2208,157 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 48687-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>STRÖMSTAD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Backstarr
 Blåsippa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 48687-2025 artfynd.xlsx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 48687-2025 karta.png", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 48687-2025 georefererad karta.tif", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 48687-2025 FSC-klagomål.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 48687-2025 FSC-klagomål mail.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 48687-2025 tillsynsbegäran.docx", "A 48687-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 48687-2025 tillsynsbegäran mail.docx", "A 48687-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 8291-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44974</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>STRÖMSTAD</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 8291-2023 artfynd.xlsx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 8291-2023 karta.png", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 8291-2023 georefererad karta.tif", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 8291-2023 FSC-klagomål.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 8291-2023 FSC-klagomål mail.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 8291-2023 tillsynsbegäran.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 8291-2023 tillsynsbegäran mail.docx", "A 8291-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 8291-2023 prioriterade fågelarter.docx", "A 8291-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 15667-2024</t>
+          <t>A 33772-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45404</v>
+        <v>45133</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2424,46 +2424,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10764-2024</t>
+          <t>A 12779-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,10 +2481,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45369</v>
+        <v>45733</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,7 +2497,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2533,42 +2537,46 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12779-2025 artfynd.xlsx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12779-2025 karta.png", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12779-2025 georefererad karta.tif", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12779-2025 FSC-klagomål.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12779-2025 FSC-klagomål mail.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12779-2025 tillsynsbegäran.docx", "A 12779-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12779-2025 tillsynsbegäran mail.docx", "A 12779-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12779-2025 prioriterade fågelarter.docx", "A 12779-2025")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 24514-2024</t>
+          <t>A 50607-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2582,10 +2590,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45458</v>
+        <v>45945</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2598,7 +2606,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>14.5</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2638,42 +2646,42 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 12238-2025</t>
+          <t>A 15667-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2687,10 +2695,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45729</v>
+        <v>45404</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2703,17 +2711,17 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10.6</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
@@ -2727,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2743,46 +2751,42 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 15667-2024 artfynd.xlsx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 15667-2024 karta.png", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 15667-2024 georefererad karta.tif", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 15667-2024 FSC-klagomål.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 15667-2024 FSC-klagomål mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 15667-2024 tillsynsbegäran.docx", "A 15667-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 15667-2024 tillsynsbegäran mail.docx", "A 15667-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 14442-2026</t>
+          <t>A 64707-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2796,10 +2800,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46100</v>
+        <v>45281</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2811,8 +2815,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>11.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2852,42 +2861,46 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 50607-2025</t>
+          <t>A 12238-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2901,10 +2914,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45945</v>
+        <v>45729</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2917,7 +2930,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>14.5</v>
+        <v>10.6</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2957,42 +2970,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 50607-2025 artfynd.xlsx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12238-2025 artfynd.xlsx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 50607-2025 karta.png", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12238-2025 karta.png", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 50607-2025 georefererad karta.tif", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12238-2025 georefererad karta.tif", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 50607-2025 FSC-klagomål.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12238-2025 FSC-klagomål.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 50607-2025 FSC-klagomål mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12238-2025 FSC-klagomål mail.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 50607-2025 tillsynsbegäran.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12238-2025 tillsynsbegäran.docx", "A 12238-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 50607-2025 tillsynsbegäran mail.docx", "A 50607-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12238-2025 tillsynsbegäran mail.docx", "A 12238-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12238-2025 prioriterade fågelarter.docx", "A 12238-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14455-2026</t>
+          <t>A 53485-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3006,10 +3023,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46100</v>
+        <v>45230</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3022,7 +3039,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3058,46 +3075,50 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 53485-2023</t>
+          <t>A 10764-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3111,10 +3132,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45230</v>
+        <v>45369</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3127,7 +3148,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3163,50 +3184,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 53485-2023 artfynd.xlsx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 10764-2024 artfynd.xlsx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 53485-2023 karta.png", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 10764-2024 karta.png", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 53485-2023 georefererad karta.tif", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 10764-2024 georefererad karta.tif", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 53485-2023 FSC-klagomål.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 10764-2024 FSC-klagomål.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 53485-2023 FSC-klagomål mail.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 10764-2024 FSC-klagomål mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 53485-2023 tillsynsbegäran.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 10764-2024 tillsynsbegäran.docx", "A 10764-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 53485-2023 tillsynsbegäran mail.docx", "A 53485-2023")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 53485-2023 prioriterade fågelarter.docx", "A 53485-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 10764-2024 tillsynsbegäran mail.docx", "A 10764-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6128-2026</t>
+          <t>A 14442-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3220,10 +3237,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46054</v>
+        <v>46100</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3236,7 +3253,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -3248,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3260,10 +3277,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3276,42 +3293,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14442-2026 artfynd.xlsx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14442-2026 karta.png", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14442-2026 georefererad karta.tif", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14442-2026 FSC-klagomål.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14442-2026 FSC-klagomål mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14442-2026 tillsynsbegäran.docx", "A 14442-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14442-2026 tillsynsbegäran mail.docx", "A 14442-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33772-2023</t>
+          <t>A 14455-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3325,10 +3342,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45133</v>
+        <v>46100</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3341,7 +3358,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3350,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3365,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3381,46 +3398,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 33772-2023 artfynd.xlsx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 14455-2026 artfynd.xlsx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 33772-2023 karta.png", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 14455-2026 karta.png", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 33772-2023 georefererad karta.tif", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 14455-2026 georefererad karta.tif", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 33772-2023 FSC-klagomål.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 14455-2026 FSC-klagomål.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 33772-2023 FSC-klagomål mail.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 14455-2026 FSC-klagomål mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 33772-2023 tillsynsbegäran.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 14455-2026 tillsynsbegäran.docx", "A 14455-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 33772-2023 tillsynsbegäran mail.docx", "A 33772-2023")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 33772-2023 prioriterade fågelarter.docx", "A 33772-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 14455-2026 tillsynsbegäran mail.docx", "A 14455-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35813-2026</t>
+          <t>A 24514-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3434,10 +3447,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46264</v>
+        <v>45458</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3450,7 +3463,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>23.7</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3486,46 +3499,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 24514-2024 artfynd.xlsx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 24514-2024 karta.png", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 24514-2024 georefererad karta.tif", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 24514-2024 FSC-klagomål.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 24514-2024 FSC-klagomål mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 24514-2024 tillsynsbegäran.docx", "A 24514-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 24514-2024 tillsynsbegäran mail.docx", "A 24514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 64707-2023</t>
+          <t>A 6128-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3539,10 +3552,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45281</v>
+        <v>46054</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3554,13 +3567,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3572,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3584,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3600,46 +3608,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 64707-2023 artfynd.xlsx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 6128-2026 artfynd.xlsx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 64707-2023 karta.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 6128-2026 karta.png", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 64707-2023 georefererad karta.tif", "A 64707-2023")</f>
-        <v/>
-      </c>
-      <c r="Z29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/knärot/A 64707-2023 karta knärot.png", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 6128-2026 georefererad karta.tif", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 64707-2023 FSC-klagomål.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 6128-2026 FSC-klagomål.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 64707-2023 FSC-klagomål mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 6128-2026 FSC-klagomål mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 64707-2023 tillsynsbegäran.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 6128-2026 tillsynsbegäran.docx", "A 6128-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 64707-2023 tillsynsbegäran mail.docx", "A 64707-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 6128-2026 tillsynsbegäran mail.docx", "A 6128-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12779-2025</t>
+          <t>A 35813-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3653,10 +3657,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45733</v>
+        <v>46264</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3669,7 +3673,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.1</v>
+        <v>23.7</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3709,39 +3713,35 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 12779-2025 artfynd.xlsx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/artfynd/A 35813-2026 artfynd.xlsx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 12779-2025 karta.png", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor/A 35813-2026 karta.png", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 12779-2025 georefererad karta.tif", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/kartor_geotiff/A 35813-2026 georefererad karta.tif", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 12779-2025 FSC-klagomål.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomål/A 35813-2026 FSC-klagomål.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 12779-2025 FSC-klagomål mail.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/klagomålsmail/A 35813-2026 FSC-klagomål mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 12779-2025 tillsynsbegäran.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsyn/A 35813-2026 tillsynsbegäran.docx", "A 35813-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 12779-2025 tillsynsbegäran mail.docx", "A 12779-2025")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1486/fåglar/A 12779-2025 prioriterade fågelarter.docx", "A 12779-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1486/tillsynsmail/A 35813-2026 tillsynsbegäran mail.docx", "A 35813-2026")</f>
         <v/>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
         <v>45282</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>44865</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44533</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>44585</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>44865</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44499</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>44606</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>44848</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30731-2022</t>
+          <t>A 50020-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44764</v>
+        <v>44865</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4816,7 +4816,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50020-2022</t>
+          <t>A 30731-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44865</v>
+        <v>44764</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4906,7 +4906,7 @@
         <v>44510</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         <v>44526</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44851</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>44722</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>44533</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44494</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>44588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31388-2022</t>
+          <t>A 53761-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44774</v>
+        <v>45615</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30701-2022</t>
+          <t>A 61626-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44763</v>
+        <v>45646</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>7.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5546,7 +5546,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 55712-2022</t>
+          <t>A 52262-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44885</v>
+        <v>45217</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 46371-2022</t>
+          <t>A 16989-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44848</v>
+        <v>45033</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54374-2022</t>
+          <t>A 10470-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44879</v>
+        <v>45366</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 72625-2021</t>
+          <t>A 55712-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44546</v>
+        <v>44885</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 880-2026</t>
+          <t>A 3178-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46029</v>
+        <v>45316</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5872,8 +5872,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>8.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5916,7 +5921,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49554-2024</t>
+          <t>A 12945-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5930,10 +5935,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45596</v>
+        <v>45385</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5946,7 +5951,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5989,7 +5994,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1608-2026</t>
+          <t>A 57663-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6003,10 +6008,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46034</v>
+        <v>45981</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6019,7 +6024,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6062,7 +6067,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1945-2026</t>
+          <t>A 61898-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6076,10 +6081,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46035</v>
+        <v>46003</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6092,7 +6097,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6135,7 +6140,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29327-2024</t>
+          <t>A 11931-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6149,10 +6154,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45483</v>
+        <v>45728</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6165,7 +6170,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6208,7 +6213,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 2322-2026</t>
+          <t>A 14087-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6222,10 +6227,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46036</v>
+        <v>45739</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6238,7 +6243,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6281,7 +6286,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 2324-2026</t>
+          <t>A 9695-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6295,10 +6300,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46036</v>
+        <v>45716</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6311,7 +6316,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6354,7 +6359,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 41991-2022</t>
+          <t>A 14079-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6368,10 +6373,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44830</v>
+        <v>45739</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6384,7 +6389,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6427,7 +6432,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44523-2023</t>
+          <t>A 49554-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6441,10 +6446,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45189</v>
+        <v>45596</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6457,7 +6462,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6500,7 +6505,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6379-2026</t>
+          <t>A 11897-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6514,10 +6519,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46055</v>
+        <v>45728</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6530,7 +6535,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6573,7 +6578,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44319-2025</t>
+          <t>A 29329-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6587,10 +6592,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45916</v>
+        <v>45483</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6603,7 +6608,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6646,7 +6651,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7466-2026</t>
+          <t>A 61252-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6660,10 +6665,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46059</v>
+        <v>45645</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6675,13 +6680,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6724,7 +6724,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7545-2026</t>
+          <t>A 39001-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46059</v>
+        <v>45548</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8060-2026</t>
+          <t>A 26233-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46063</v>
+        <v>45805</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6826,8 +6826,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6870,7 +6875,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8051-2026</t>
+          <t>A 26270-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6884,10 +6889,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46063</v>
+        <v>45805</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6900,7 +6905,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6943,7 +6948,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8058-2026</t>
+          <t>A 30701-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6957,10 +6962,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46063</v>
+        <v>44763</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7016,7 +7021,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26233-2025</t>
+          <t>A 15552-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7030,10 +7035,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45805</v>
+        <v>45018</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7045,13 +7050,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7094,7 +7094,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26270-2025</t>
+          <t>A 13890-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7108,10 +7108,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45805</v>
+        <v>44649</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7167,7 +7167,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33118-2023</t>
+          <t>A 44319-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7181,10 +7181,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45126</v>
+        <v>45916</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 33131-2023</t>
+          <t>A 52950-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45126</v>
+        <v>44875</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7313,7 +7313,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10850-2026</t>
+          <t>A 40369-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7327,10 +7327,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46078</v>
+        <v>45555</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>14.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7386,7 +7386,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13890-2022</t>
+          <t>A 44529-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44649</v>
+        <v>45189</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7459,7 +7459,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 15552-2023</t>
+          <t>A 55733-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45018</v>
+        <v>45232</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 15695-2025</t>
+          <t>A 33569-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7546,10 +7546,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45748</v>
+        <v>45841</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7605,7 +7605,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 45578-2024</t>
+          <t>A 33586-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45578</v>
+        <v>45841</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7678,7 +7678,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50626-2025</t>
+          <t>A 33536-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45945</v>
+        <v>45841</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7707,13 +7707,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>14</v>
+        <v>6.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7756,7 +7751,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14440-2026</t>
+          <t>A 33580-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7770,10 +7765,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46100</v>
+        <v>45841</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7786,7 +7781,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7829,7 +7824,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 14456-2026</t>
+          <t>A 50626-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7843,10 +7838,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46100</v>
+        <v>45945</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7858,8 +7853,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7902,7 +7902,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14465-2026</t>
+          <t>A 26277-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7916,10 +7916,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46100</v>
+        <v>45805</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13325-2022</t>
+          <t>A 50578-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44645</v>
+        <v>45945</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8048,7 +8048,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14462-2026</t>
+          <t>A 50797-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8062,10 +8062,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46100</v>
+        <v>45946</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8121,7 +8121,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50578-2025</t>
+          <t>A 52852-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45945</v>
+        <v>45610</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8194,7 +8194,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 50797-2025</t>
+          <t>A 880-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45946</v>
+        <v>46029</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14437-2026</t>
+          <t>A 25884-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46100</v>
+        <v>45085</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8340,7 +8340,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 54126-2025</t>
+          <t>A 16223-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45964</v>
+        <v>45750</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8413,7 +8413,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59383-2024</t>
+          <t>A 54126-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45638</v>
+        <v>45964</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8442,13 +8442,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8491,7 +8486,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 10457-2023</t>
+          <t>A 50603-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8505,10 +8500,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44987</v>
+        <v>45600</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8521,7 +8516,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.6</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8564,7 +8559,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 55830-2025</t>
+          <t>A 1945-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8578,10 +8573,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45972</v>
+        <v>46035</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8594,7 +8589,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8637,7 +8632,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14833-2026</t>
+          <t>A 1608-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8651,10 +8646,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46103</v>
+        <v>46034</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8667,7 +8662,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8710,7 +8705,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 58226-2025</t>
+          <t>A 17525-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8724,10 +8719,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45985</v>
+        <v>45757</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8740,7 +8735,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8783,7 +8778,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 53761-2024</t>
+          <t>A 2322-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8797,10 +8792,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45615</v>
+        <v>46036</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8813,7 +8808,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8856,7 +8851,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16989-2023</t>
+          <t>A 2324-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8870,10 +8865,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45033</v>
+        <v>46036</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8885,13 +8880,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8934,7 +8924,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31917-2025</t>
+          <t>A 55830-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8948,10 +8938,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45834</v>
+        <v>45972</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8964,7 +8954,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9007,7 +8997,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44529-2023</t>
+          <t>A 20476-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9021,10 +9011,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45189</v>
+        <v>45057</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9037,7 +9027,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9080,7 +9070,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33745-2023</t>
+          <t>A 58226-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9094,10 +9084,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45133</v>
+        <v>45985</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9110,7 +9100,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9153,7 +9143,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 57663-2025</t>
+          <t>A 56024-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9167,10 +9157,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45981</v>
+        <v>45240</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9183,7 +9173,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9226,7 +9216,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 29308-2025</t>
+          <t>A 50601-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9240,10 +9230,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45824</v>
+        <v>45600</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9256,7 +9246,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9299,7 +9289,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61898-2025</t>
+          <t>A 41991-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9313,10 +9303,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46003</v>
+        <v>44830</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9329,7 +9319,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9372,7 +9362,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 29300-2025</t>
+          <t>A 6379-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9386,10 +9376,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45824</v>
+        <v>46055</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9402,7 +9392,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9445,7 +9435,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 29329-2024</t>
+          <t>A 3187-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9459,10 +9449,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45483</v>
+        <v>45316</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9474,8 +9464,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9518,7 +9513,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33559-2025</t>
+          <t>A 7545-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9532,10 +9527,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45841</v>
+        <v>46059</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9548,7 +9543,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9591,7 +9586,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 2982-2025</t>
+          <t>A 46371-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9605,10 +9600,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45678</v>
+        <v>44848</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9620,8 +9615,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9664,7 +9664,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 56196-2025</t>
+          <t>A 7466-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9678,10 +9678,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45974</v>
+        <v>46059</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9693,8 +9693,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9737,7 +9742,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 20476-2023</t>
+          <t>A 59383-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9751,10 +9756,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45057</v>
+        <v>45638</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9766,8 +9771,13 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9810,7 +9820,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 19134-2025</t>
+          <t>A 33745-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9820,14 +9830,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45764</v>
+        <v>45133</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9840,7 +9850,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9883,7 +9893,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 48688-2025</t>
+          <t>A 8051-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9897,10 +9907,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45936</v>
+        <v>46063</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9913,7 +9923,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9956,7 +9966,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 11897-2025</t>
+          <t>A 8058-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9970,10 +9980,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45728</v>
+        <v>46063</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9986,7 +9996,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10029,7 +10039,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 37311-2025</t>
+          <t>A 8060-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10043,10 +10053,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45876</v>
+        <v>46063</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10059,7 +10069,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10102,7 +10112,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21355-2026</t>
+          <t>A 5326-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10116,10 +10126,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46142</v>
+        <v>45331</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10132,7 +10142,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10175,7 +10185,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22560-2023</t>
+          <t>A 10850-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10189,10 +10199,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45071</v>
+        <v>46078</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10205,7 +10215,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10248,7 +10258,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 50034-2022</t>
+          <t>A 2982-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10262,10 +10272,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44865</v>
+        <v>45678</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10278,7 +10288,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10321,7 +10331,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 21819-2026</t>
+          <t>A 60768-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10335,10 +10345,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46150</v>
+        <v>44907</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10351,7 +10361,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10394,7 +10404,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 21833-2026</t>
+          <t>A 20888-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10408,10 +10418,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46150</v>
+        <v>44701</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10424,7 +10434,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10467,7 +10477,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 21839-2026</t>
+          <t>A 14465-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10481,10 +10491,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46150</v>
+        <v>46100</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10497,7 +10507,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10540,7 +10550,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 21755-2026</t>
+          <t>A 14440-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10554,10 +10564,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46149</v>
+        <v>46100</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10570,7 +10580,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10613,7 +10623,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21826-2026</t>
+          <t>A 14456-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10627,10 +10637,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46150</v>
+        <v>46100</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10643,7 +10653,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10686,7 +10696,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21828-2026</t>
+          <t>A 14462-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10700,10 +10710,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46150</v>
+        <v>46100</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10716,7 +10726,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10759,7 +10769,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 22321-2026</t>
+          <t>A 45617-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10773,10 +10783,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46154</v>
+        <v>45579</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10789,7 +10799,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10832,7 +10842,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 12945-2024</t>
+          <t>A 14437-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10846,10 +10856,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45385</v>
+        <v>46100</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10862,7 +10872,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10905,7 +10915,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 994-2024</t>
+          <t>A 9983-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10919,10 +10929,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45301</v>
+        <v>44621</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10935,7 +10945,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10978,7 +10988,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 3187-2024</t>
+          <t>A 33131-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10992,10 +11002,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45316</v>
+        <v>45126</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11007,13 +11017,8 @@
           <t>STRÖMSTAD</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11056,7 +11061,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 23027-2026</t>
+          <t>A 31388-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11070,10 +11075,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46161</v>
+        <v>44774</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11086,7 +11091,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11129,7 +11134,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 33569-2025</t>
+          <t>A 29195-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11143,10 +11148,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45841</v>
+        <v>45482</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11159,7 +11164,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11202,7 +11207,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 33586-2025</t>
+          <t>A 994-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11216,10 +11221,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45841</v>
+        <v>45301</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11232,7 +11237,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11275,7 +11280,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 33580-2025</t>
+          <t>A 14833-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11289,10 +11294,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45841</v>
+        <v>46103</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11305,7 +11310,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11348,7 +11353,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26277-2025</t>
+          <t>A 31917-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11362,10 +11367,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45805</v>
+        <v>45834</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11378,7 +11383,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11421,7 +11426,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33536-2025</t>
+          <t>A 29308-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11435,10 +11440,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45841</v>
+        <v>45824</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11451,7 +11456,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11494,7 +11499,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 39001-2024</t>
+          <t>A 10457-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11508,10 +11513,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45548</v>
+        <v>44987</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11524,7 +11529,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11567,7 +11572,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28586-2025</t>
+          <t>A 33559-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11581,10 +11586,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45819</v>
+        <v>45841</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11597,7 +11602,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11640,7 +11645,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 38983-2024</t>
+          <t>A 50034-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11654,10 +11659,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45548</v>
+        <v>44865</v